--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,11 +499,13 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,25 +668,35 @@
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
+          <t>Соинвест, %</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>Соинвест ₽</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="Y11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -757,24 +769,31 @@
         <f>C12*$B$3</f>
         <v/>
       </c>
-      <c r="S12" s="12">
-        <f>C12-H12-I12-J12-K12-L12-O12-Q12-F12</f>
-        <v/>
-      </c>
-      <c r="T12" s="14">
-        <f>S12-R12</f>
-        <v/>
-      </c>
-      <c r="U12" s="15">
-        <f>T12/C12</f>
-        <v/>
-      </c>
-      <c r="V12" s="16">
-        <f>T12/F12</f>
-        <v/>
-      </c>
-      <c r="W12" s="12">
-        <f>(I12+J12+O12+Q12+F12)/(1-(G12+$B$5+$B$4+$B$3))</f>
+      <c r="S12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <f>C12*S12</f>
+        <v/>
+      </c>
+      <c r="U12" s="12">
+        <f>C12-H12-I12-J12-K12-L12-O12-Q12-F12+T12</f>
+        <v/>
+      </c>
+      <c r="V12" s="14">
+        <f>U12-R12</f>
+        <v/>
+      </c>
+      <c r="W12" s="15">
+        <f>V12/C12</f>
+        <v/>
+      </c>
+      <c r="X12" s="16">
+        <f>V12/F12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="12">
+        <f>(I12+J12+O12+Q12+F12)/(1-(G12+$B$5+$B$4+$B$3-S12))</f>
         <v/>
       </c>
     </row>
@@ -845,24 +864,31 @@
         <f>C13*$B$3</f>
         <v/>
       </c>
-      <c r="S13" s="12">
-        <f>C13-H13-I13-J13-K13-L13-O13-Q13-F13</f>
-        <v/>
-      </c>
-      <c r="T13" s="14">
-        <f>S13-R13</f>
-        <v/>
-      </c>
-      <c r="U13" s="15">
-        <f>T13/C13</f>
-        <v/>
-      </c>
-      <c r="V13" s="16">
-        <f>T13/F13</f>
-        <v/>
-      </c>
-      <c r="W13" s="12">
-        <f>(I13+J13+O13+Q13+F13)/(1-(G13+$B$5+$B$4+$B$3))</f>
+      <c r="S13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <f>C13*S13</f>
+        <v/>
+      </c>
+      <c r="U13" s="12">
+        <f>C13-H13-I13-J13-K13-L13-O13-Q13-F13+T13</f>
+        <v/>
+      </c>
+      <c r="V13" s="14">
+        <f>U13-R13</f>
+        <v/>
+      </c>
+      <c r="W13" s="15">
+        <f>V13/C13</f>
+        <v/>
+      </c>
+      <c r="X13" s="16">
+        <f>V13/F13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="12">
+        <f>(I13+J13+O13+Q13+F13)/(1-(G13+$B$5+$B$4+$B$3-S13))</f>
         <v/>
       </c>
     </row>
@@ -933,24 +959,31 @@
         <f>C14*$B$3</f>
         <v/>
       </c>
-      <c r="S14" s="12">
-        <f>C14-H14-I14-J14-K14-L14-O14-Q14-F14</f>
-        <v/>
-      </c>
-      <c r="T14" s="14">
-        <f>S14-R14</f>
-        <v/>
-      </c>
-      <c r="U14" s="15">
-        <f>T14/C14</f>
-        <v/>
-      </c>
-      <c r="V14" s="16">
-        <f>T14/F14</f>
-        <v/>
-      </c>
-      <c r="W14" s="12">
-        <f>(I14+J14+O14+Q14+F14)/(1-(G14+$B$5+$B$4+$B$3))</f>
+      <c r="S14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <f>C14*S14</f>
+        <v/>
+      </c>
+      <c r="U14" s="12">
+        <f>C14-H14-I14-J14-K14-L14-O14-Q14-F14+T14</f>
+        <v/>
+      </c>
+      <c r="V14" s="14">
+        <f>U14-R14</f>
+        <v/>
+      </c>
+      <c r="W14" s="15">
+        <f>V14/C14</f>
+        <v/>
+      </c>
+      <c r="X14" s="16">
+        <f>V14/F14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="12">
+        <f>(I14+J14+O14+Q14+F14)/(1-(G14+$B$5+$B$4+$B$3-S14))</f>
         <v/>
       </c>
     </row>
@@ -1021,24 +1054,31 @@
         <f>C15*$B$3</f>
         <v/>
       </c>
-      <c r="S15" s="12">
-        <f>C15-H15-I15-J15-K15-L15-O15-Q15-F15</f>
-        <v/>
-      </c>
-      <c r="T15" s="14">
-        <f>S15-R15</f>
-        <v/>
-      </c>
-      <c r="U15" s="15">
-        <f>T15/C15</f>
-        <v/>
-      </c>
-      <c r="V15" s="16">
-        <f>T15/F15</f>
-        <v/>
-      </c>
-      <c r="W15" s="12">
-        <f>(I15+J15+O15+Q15+F15)/(1-(G15+$B$5+$B$4+$B$3))</f>
+      <c r="S15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <f>C15*S15</f>
+        <v/>
+      </c>
+      <c r="U15" s="12">
+        <f>C15-H15-I15-J15-K15-L15-O15-Q15-F15+T15</f>
+        <v/>
+      </c>
+      <c r="V15" s="14">
+        <f>U15-R15</f>
+        <v/>
+      </c>
+      <c r="W15" s="15">
+        <f>V15/C15</f>
+        <v/>
+      </c>
+      <c r="X15" s="16">
+        <f>V15/F15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="12">
+        <f>(I15+J15+O15+Q15+F15)/(1-(G15+$B$5+$B$4+$B$3-S15))</f>
         <v/>
       </c>
     </row>
@@ -1109,24 +1149,31 @@
         <f>C16*$B$3</f>
         <v/>
       </c>
-      <c r="S16" s="12">
-        <f>C16-H16-I16-J16-K16-L16-O16-Q16-F16</f>
-        <v/>
-      </c>
-      <c r="T16" s="14">
-        <f>S16-R16</f>
-        <v/>
-      </c>
-      <c r="U16" s="15">
-        <f>T16/C16</f>
-        <v/>
-      </c>
-      <c r="V16" s="16">
-        <f>T16/F16</f>
-        <v/>
-      </c>
-      <c r="W16" s="12">
-        <f>(I16+J16+O16+Q16+F16)/(1-(G16+$B$5+$B$4+$B$3))</f>
+      <c r="S16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <f>C16*S16</f>
+        <v/>
+      </c>
+      <c r="U16" s="12">
+        <f>C16-H16-I16-J16-K16-L16-O16-Q16-F16+T16</f>
+        <v/>
+      </c>
+      <c r="V16" s="14">
+        <f>U16-R16</f>
+        <v/>
+      </c>
+      <c r="W16" s="15">
+        <f>V16/C16</f>
+        <v/>
+      </c>
+      <c r="X16" s="16">
+        <f>V16/F16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="12">
+        <f>(I16+J16+O16+Q16+F16)/(1-(G16+$B$5+$B$4+$B$3-S16))</f>
         <v/>
       </c>
     </row>
@@ -1197,31 +1244,38 @@
         <f>C17*$B$3</f>
         <v/>
       </c>
-      <c r="S17" s="12">
-        <f>C17-H17-I17-J17-K17-L17-O17-Q17-F17</f>
-        <v/>
-      </c>
-      <c r="T17" s="14">
-        <f>S17-R17</f>
-        <v/>
-      </c>
-      <c r="U17" s="15">
-        <f>T17/C17</f>
-        <v/>
-      </c>
-      <c r="V17" s="16">
-        <f>T17/F17</f>
-        <v/>
-      </c>
-      <c r="W17" s="12">
-        <f>(I17+J17+O17+Q17+F17)/(1-(G17+$B$5+$B$4+$B$3))</f>
+      <c r="S17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <f>C17*S17</f>
+        <v/>
+      </c>
+      <c r="U17" s="12">
+        <f>C17-H17-I17-J17-K17-L17-O17-Q17-F17+T17</f>
+        <v/>
+      </c>
+      <c r="V17" s="14">
+        <f>U17-R17</f>
+        <v/>
+      </c>
+      <c r="W17" s="15">
+        <f>V17/C17</f>
+        <v/>
+      </c>
+      <c r="X17" s="16">
+        <f>V17/F17</f>
+        <v/>
+      </c>
+      <c r="Y17" s="12">
+        <f>(I17+J17+O17+Q17+F17)/(1-(G17+$B$5+$B$4+$B$3-S17))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — вход (цена, себест., комиссия, логистика, выкуп, объём) и параметры B3:B8. Остальное — формулы. Меняешь цену в колонке C → маржа и ROI пересчитываются.</t>
+          <t>Жёлтые ячейки — вход (цена, себест., комиссия, логистика, выкуп, объём, соинвест %) и параметры B3:B8. Остальное — формулы. Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки, поэтому прибавляются к марже. Меняешь цену в колонке C → маржа и ROI пересчитываются.</t>
         </is>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -491,21 +491,26 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,60 +523,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ДРР (доля рекламы)</t>
+          <t>Налог с оборота</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Налог с оборота</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0.08</v>
+          <t>Эквайринг</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.015</v>
+          <t>Фулфилмент, ₽/шт</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Фулфилмент, ₽/шт</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>60</v>
+          <t>Хранение, ₽/л/день</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Хранение, ₽/л/день</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>Дней хранения</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -628,75 +623,100 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
+          <t>Обработка отправл.</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
           <t>Эквайринг</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Налог</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Выкуп %</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог база</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Объём, л</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Хранение</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Реклама (ДРР)</t>
-        </is>
-      </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
+          <t>Трафареты, %</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>Трафареты ₽</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>Продв. в поиске, %</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>Продв. в поиске ₽</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>Реклама всего ₽</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
           <t>Соинвест, %</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="Y11" s="6" t="inlineStr">
         <is>
           <t>Соинвест ₽</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="Z11" s="6" t="inlineStr">
         <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="AA11" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="AB11" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="AC11" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -720,7 +740,7 @@
         <v>663.86</v>
       </c>
       <c r="E12" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F12" s="10">
@@ -740,60 +760,77 @@
       <c r="J12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K12" s="12">
-        <f>C12*$B$5</f>
-        <v/>
+      <c r="K12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L12" s="12">
         <f>C12*$B$4</f>
         <v/>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="12">
+        <f>C12*$B$3</f>
+        <v/>
+      </c>
+      <c r="N12" s="11" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="O12" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="O12" s="12">
-        <f>N12*(1-M12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="12">
+        <f>O12*(1-N12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q12" s="12">
-        <f>$B$7*$B$8*P12</f>
-        <v/>
-      </c>
       <c r="R12" s="12">
-        <f>C12*$B$3</f>
+        <f>$B$6*$B$7*Q12</f>
         <v/>
       </c>
       <c r="S12" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T12" s="12">
         <f>C12*S12</f>
         <v/>
       </c>
-      <c r="U12" s="12">
-        <f>C12-H12-I12-J12-K12-L12-O12-Q12-F12+T12</f>
-        <v/>
-      </c>
-      <c r="V12" s="14">
-        <f>U12-R12</f>
-        <v/>
-      </c>
-      <c r="W12" s="15">
-        <f>V12/C12</f>
-        <v/>
-      </c>
-      <c r="X12" s="16">
-        <f>V12/F12</f>
-        <v/>
+      <c r="U12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
+        <f>C12*U12</f>
+        <v/>
+      </c>
+      <c r="W12" s="12">
+        <f>T12+V12</f>
+        <v/>
+      </c>
+      <c r="X12" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y12" s="12">
-        <f>(I12+J12+O12+Q12+F12)/(1-(G12+$B$5+$B$4+$B$3-S12))</f>
+        <f>C12*X12</f>
+        <v/>
+      </c>
+      <c r="Z12" s="12">
+        <f>C12-H12-I12-J12-K12-L12-M12-P12-R12-F12+Y12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="14">
+        <f>Z12-W12</f>
+        <v/>
+      </c>
+      <c r="AB12" s="15">
+        <f>AA12/C12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="16">
+        <f>AA12/F12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="12">
+        <f>(I12+J12+K12+P12+R12+F12)/(1-(G12+$B$4+$B$3+S12+U12-X12))</f>
         <v/>
       </c>
     </row>
@@ -815,7 +852,7 @@
         <v>663.86</v>
       </c>
       <c r="E13" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F13" s="10">
@@ -835,60 +872,77 @@
       <c r="J13" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K13" s="12">
-        <f>C13*$B$5</f>
-        <v/>
+      <c r="K13" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="12">
         <f>C13*$B$4</f>
         <v/>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="12">
+        <f>C13*$B$3</f>
+        <v/>
+      </c>
+      <c r="N13" s="11" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="O13" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="O13" s="12">
-        <f>N13*(1-M13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="13" t="n">
+      <c r="P13" s="12">
+        <f>O13*(1-N13)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q13" s="12">
-        <f>$B$7*$B$8*P13</f>
-        <v/>
-      </c>
       <c r="R13" s="12">
-        <f>C13*$B$3</f>
+        <f>$B$6*$B$7*Q13</f>
         <v/>
       </c>
       <c r="S13" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T13" s="12">
         <f>C13*S13</f>
         <v/>
       </c>
-      <c r="U13" s="12">
-        <f>C13-H13-I13-J13-K13-L13-O13-Q13-F13+T13</f>
-        <v/>
-      </c>
-      <c r="V13" s="14">
-        <f>U13-R13</f>
-        <v/>
-      </c>
-      <c r="W13" s="15">
-        <f>V13/C13</f>
-        <v/>
-      </c>
-      <c r="X13" s="16">
-        <f>V13/F13</f>
-        <v/>
+      <c r="U13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
+        <f>C13*U13</f>
+        <v/>
+      </c>
+      <c r="W13" s="12">
+        <f>T13+V13</f>
+        <v/>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y13" s="12">
-        <f>(I13+J13+O13+Q13+F13)/(1-(G13+$B$5+$B$4+$B$3-S13))</f>
+        <f>C13*X13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="12">
+        <f>C13-H13-I13-J13-K13-L13-M13-P13-R13-F13+Y13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="14">
+        <f>Z13-W13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="15">
+        <f>AA13/C13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="16">
+        <f>AA13/F13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="12">
+        <f>(I13+J13+K13+P13+R13+F13)/(1-(G13+$B$4+$B$3+S13+U13-X13))</f>
         <v/>
       </c>
     </row>
@@ -910,7 +964,7 @@
         <v>463.19</v>
       </c>
       <c r="E14" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F14" s="10">
@@ -930,60 +984,77 @@
       <c r="J14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K14" s="12">
-        <f>C14*$B$5</f>
-        <v/>
+      <c r="K14" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L14" s="12">
         <f>C14*$B$4</f>
         <v/>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="12">
+        <f>C14*$B$3</f>
+        <v/>
+      </c>
+      <c r="N14" s="11" t="n">
         <v>0.96</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="O14" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="O14" s="12">
-        <f>N14*(1-M14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="12">
+        <f>O14*(1-N14)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="12">
-        <f>$B$7*$B$8*P14</f>
-        <v/>
-      </c>
       <c r="R14" s="12">
-        <f>C14*$B$3</f>
+        <f>$B$6*$B$7*Q14</f>
         <v/>
       </c>
       <c r="S14" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T14" s="12">
         <f>C14*S14</f>
         <v/>
       </c>
-      <c r="U14" s="12">
-        <f>C14-H14-I14-J14-K14-L14-O14-Q14-F14+T14</f>
-        <v/>
-      </c>
-      <c r="V14" s="14">
-        <f>U14-R14</f>
-        <v/>
-      </c>
-      <c r="W14" s="15">
-        <f>V14/C14</f>
-        <v/>
-      </c>
-      <c r="X14" s="16">
-        <f>V14/F14</f>
-        <v/>
+      <c r="U14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12">
+        <f>C14*U14</f>
+        <v/>
+      </c>
+      <c r="W14" s="12">
+        <f>T14+V14</f>
+        <v/>
+      </c>
+      <c r="X14" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y14" s="12">
-        <f>(I14+J14+O14+Q14+F14)/(1-(G14+$B$5+$B$4+$B$3-S14))</f>
+        <f>C14*X14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="12">
+        <f>C14-H14-I14-J14-K14-L14-M14-P14-R14-F14+Y14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="14">
+        <f>Z14-W14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="15">
+        <f>AA14/C14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="16">
+        <f>AA14/F14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="12">
+        <f>(I14+J14+K14+P14+R14+F14)/(1-(G14+$B$4+$B$3+S14+U14-X14))</f>
         <v/>
       </c>
     </row>
@@ -1005,7 +1076,7 @@
         <v>463.19</v>
       </c>
       <c r="E15" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F15" s="10">
@@ -1025,60 +1096,77 @@
       <c r="J15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K15" s="12">
-        <f>C15*$B$5</f>
-        <v/>
+      <c r="K15" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="12">
         <f>C15*$B$4</f>
         <v/>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12">
+        <f>C15*$B$3</f>
+        <v/>
+      </c>
+      <c r="N15" s="11" t="n">
         <v>0.96</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="O15" s="8" t="n">
         <v>218</v>
       </c>
-      <c r="O15" s="12">
-        <f>N15*(1-M15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="12">
+        <f>O15*(1-N15)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q15" s="12">
-        <f>$B$7*$B$8*P15</f>
-        <v/>
-      </c>
       <c r="R15" s="12">
-        <f>C15*$B$3</f>
+        <f>$B$6*$B$7*Q15</f>
         <v/>
       </c>
       <c r="S15" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T15" s="12">
         <f>C15*S15</f>
         <v/>
       </c>
-      <c r="U15" s="12">
-        <f>C15-H15-I15-J15-K15-L15-O15-Q15-F15+T15</f>
-        <v/>
-      </c>
-      <c r="V15" s="14">
-        <f>U15-R15</f>
-        <v/>
-      </c>
-      <c r="W15" s="15">
-        <f>V15/C15</f>
-        <v/>
-      </c>
-      <c r="X15" s="16">
-        <f>V15/F15</f>
-        <v/>
+      <c r="U15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12">
+        <f>C15*U15</f>
+        <v/>
+      </c>
+      <c r="W15" s="12">
+        <f>T15+V15</f>
+        <v/>
+      </c>
+      <c r="X15" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y15" s="12">
-        <f>(I15+J15+O15+Q15+F15)/(1-(G15+$B$5+$B$4+$B$3-S15))</f>
+        <f>C15*X15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="12">
+        <f>C15-H15-I15-J15-K15-L15-M15-P15-R15-F15+Y15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="14">
+        <f>Z15-W15</f>
+        <v/>
+      </c>
+      <c r="AB15" s="15">
+        <f>AA15/C15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="16">
+        <f>AA15/F15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="12">
+        <f>(I15+J15+K15+P15+R15+F15)/(1-(G15+$B$4+$B$3+S15+U15-X15))</f>
         <v/>
       </c>
     </row>
@@ -1100,7 +1188,7 @@
         <v>347.76</v>
       </c>
       <c r="E16" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F16" s="10">
@@ -1120,60 +1208,77 @@
       <c r="J16" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K16" s="12">
-        <f>C16*$B$5</f>
-        <v/>
+      <c r="K16" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L16" s="12">
         <f>C16*$B$4</f>
         <v/>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12">
+        <f>C16*$B$3</f>
+        <v/>
+      </c>
+      <c r="N16" s="11" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="O16" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="O16" s="12">
-        <f>N16*(1-M16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="12">
+        <f>O16*(1-N16)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q16" s="12">
-        <f>$B$7*$B$8*P16</f>
-        <v/>
-      </c>
       <c r="R16" s="12">
-        <f>C16*$B$3</f>
+        <f>$B$6*$B$7*Q16</f>
         <v/>
       </c>
       <c r="S16" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T16" s="12">
         <f>C16*S16</f>
         <v/>
       </c>
-      <c r="U16" s="12">
-        <f>C16-H16-I16-J16-K16-L16-O16-Q16-F16+T16</f>
-        <v/>
-      </c>
-      <c r="V16" s="14">
-        <f>U16-R16</f>
-        <v/>
-      </c>
-      <c r="W16" s="15">
-        <f>V16/C16</f>
-        <v/>
-      </c>
-      <c r="X16" s="16">
-        <f>V16/F16</f>
-        <v/>
+      <c r="U16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12">
+        <f>C16*U16</f>
+        <v/>
+      </c>
+      <c r="W16" s="12">
+        <f>T16+V16</f>
+        <v/>
+      </c>
+      <c r="X16" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y16" s="12">
-        <f>(I16+J16+O16+Q16+F16)/(1-(G16+$B$5+$B$4+$B$3-S16))</f>
+        <f>C16*X16</f>
+        <v/>
+      </c>
+      <c r="Z16" s="12">
+        <f>C16-H16-I16-J16-K16-L16-M16-P16-R16-F16+Y16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="14">
+        <f>Z16-W16</f>
+        <v/>
+      </c>
+      <c r="AB16" s="15">
+        <f>AA16/C16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="16">
+        <f>AA16/F16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="12">
+        <f>(I16+J16+K16+P16+R16+F16)/(1-(G16+$B$4+$B$3+S16+U16-X16))</f>
         <v/>
       </c>
     </row>
@@ -1195,7 +1300,7 @@
         <v>347.76</v>
       </c>
       <c r="E17" s="10">
-        <f>$B$6</f>
+        <f>$B$5</f>
         <v/>
       </c>
       <c r="F17" s="10">
@@ -1215,67 +1320,84 @@
       <c r="J17" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K17" s="12">
-        <f>C17*$B$5</f>
-        <v/>
+      <c r="K17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L17" s="12">
         <f>C17*$B$4</f>
         <v/>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12">
+        <f>C17*$B$3</f>
+        <v/>
+      </c>
+      <c r="N17" s="11" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="O17" s="8" t="n">
         <v>168</v>
       </c>
-      <c r="O17" s="12">
-        <f>N17*(1-M17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="12">
+        <f>O17*(1-N17)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="12">
-        <f>$B$7*$B$8*P17</f>
-        <v/>
-      </c>
       <c r="R17" s="12">
-        <f>C17*$B$3</f>
+        <f>$B$6*$B$7*Q17</f>
         <v/>
       </c>
       <c r="S17" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T17" s="12">
         <f>C17*S17</f>
         <v/>
       </c>
-      <c r="U17" s="12">
-        <f>C17-H17-I17-J17-K17-L17-O17-Q17-F17+T17</f>
-        <v/>
-      </c>
-      <c r="V17" s="14">
-        <f>U17-R17</f>
-        <v/>
-      </c>
-      <c r="W17" s="15">
-        <f>V17/C17</f>
-        <v/>
-      </c>
-      <c r="X17" s="16">
-        <f>V17/F17</f>
-        <v/>
+      <c r="U17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
+        <f>C17*U17</f>
+        <v/>
+      </c>
+      <c r="W17" s="12">
+        <f>T17+V17</f>
+        <v/>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="Y17" s="12">
-        <f>(I17+J17+O17+Q17+F17)/(1-(G17+$B$5+$B$4+$B$3-S17))</f>
+        <f>C17*X17</f>
+        <v/>
+      </c>
+      <c r="Z17" s="12">
+        <f>C17-H17-I17-J17-K17-L17-M17-P17-R17-F17+Y17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="14">
+        <f>Z17-W17</f>
+        <v/>
+      </c>
+      <c r="AB17" s="15">
+        <f>AA17/C17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="16">
+        <f>AA17/F17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="12">
+        <f>(I17+J17+K17+P17+R17+F17)/(1-(G17+$B$4+$B$3+S17+U17-X17))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — вход (цена, себест., комиссия, логистика, выкуп, объём, соинвест %) и параметры B3:B8. Остальное — формулы. Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки, поэтому прибавляются к марже. Меняешь цену в колонке C → маржа и ROI пересчитываются.</t>
+          <t>Жёлтые ячейки — вход (цена, себест., комиссия, логистика, обработка отправления, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Реклама разбита по тарифам: Трафареты % (доля от цены) и Продвижение в поиске % (ставка от продажи). Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки и прибавляются к марже. Меняешь цену в колонке C → маржа и ROI пересчитываются.</t>
         </is>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -478,39 +478,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,145 +576,135 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Схема</t>
+          <t>Цена</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Себест.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Себест.</t>
+          <t>Фулфилмент</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Фулфилмент</t>
+          <t>База затрат</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>База затрат</t>
+          <t>Комиссия %</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Комиссия %</t>
+          <t>Комиссия ₽</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Комиссия ₽</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Посл.миля</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Посл.миля</t>
+          <t>Эквайринг</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Обработка отправл.</t>
+          <t>Налог</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Эквайринг</t>
+          <t>Выкуп %</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>Налог</t>
+          <t>Обр.лог база</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>Выкуп %</t>
+          <t>Обр.лог</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>Обр.лог база</t>
+          <t>Объём, л</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Обр.лог</t>
+          <t>Хранение</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>Объём, л</t>
+          <t>Оплата за клик, %</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>Хранение</t>
+          <t>Оплата за клик ₽</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>Трафареты, %</t>
+          <t>Вывод в топ, %</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Трафареты ₽</t>
+          <t>Вывод в топ ₽</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
-          <t>Продв. в поиске, %</t>
+          <t>Реклама всего ₽</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>Продв. в поиске ₽</t>
+          <t>Соинвест, %</t>
         </is>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>Реклама всего ₽</t>
+          <t>Соинвест ₽</t>
         </is>
       </c>
       <c r="X11" s="6" t="inlineStr">
         <is>
-          <t>Соинвест, %</t>
+          <t>Маржа до рекл.</t>
         </is>
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>Соинвест ₽</t>
+          <t>Маржа/шт</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>Маржа до рекл.</t>
+          <t>Маржа % цены</t>
         </is>
       </c>
       <c r="AA11" s="6" t="inlineStr">
         <is>
-          <t>Маржа/шт</t>
+          <t>ROI %</t>
         </is>
       </c>
       <c r="AB11" s="6" t="inlineStr">
-        <is>
-          <t>Маржа % цены</t>
-        </is>
-      </c>
-      <c r="AC11" s="6" t="inlineStr">
-        <is>
-          <t>ROI %</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -728,676 +716,316 @@
           <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>FBO</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
+      <c r="B12" s="8" t="n">
         <v>2500</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="C12" s="9" t="n">
         <v>663.86</v>
       </c>
+      <c r="D12" s="10">
+        <f>$B$5</f>
+        <v/>
+      </c>
       <c r="E12" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>D12+E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="11" t="n">
+        <f>C12+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0.41</v>
       </c>
-      <c r="H12" s="12">
-        <f>C12*G12</f>
-        <v/>
+      <c r="G12" s="12">
+        <f>B12*F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>67</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="J12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="J12" s="12">
+        <f>B12*$B$4</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>B12*$B$3</f>
+        <v/>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>0.9219000000000001</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="N12" s="12">
+        <f>M12*(1-L12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P12" s="12">
+        <f>$B$6*$B$7*O12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R12" s="12">
+        <f>B12*Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="12">
-        <f>C12*$B$4</f>
-        <v/>
-      </c>
-      <c r="M12" s="12">
-        <f>C12*$B$3</f>
-        <v/>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="P12" s="12">
-        <f>O12*(1-N12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R12" s="12">
-        <f>$B$6*$B$7*Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="11" t="n">
-        <v>0.1</v>
-      </c>
       <c r="T12" s="12">
-        <f>C12*S12</f>
-        <v/>
-      </c>
-      <c r="U12" s="11" t="n">
+        <f>B12*S12</f>
+        <v/>
+      </c>
+      <c r="U12" s="12">
+        <f>R12+T12</f>
+        <v/>
+      </c>
+      <c r="V12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="12">
-        <f>C12*U12</f>
-        <v/>
-      </c>
       <c r="W12" s="12">
-        <f>T12+V12</f>
-        <v/>
-      </c>
-      <c r="X12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="12">
-        <f>C12*X12</f>
-        <v/>
-      </c>
-      <c r="Z12" s="12">
-        <f>C12-H12-I12-J12-K12-L12-M12-P12-R12-F12+Y12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="14">
-        <f>Z12-W12</f>
-        <v/>
-      </c>
-      <c r="AB12" s="15">
-        <f>AA12/C12</f>
-        <v/>
-      </c>
-      <c r="AC12" s="16">
-        <f>AA12/F12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="12">
-        <f>(I12+J12+K12+P12+R12+F12)/(1-(G12+$B$4+$B$3+S12+U12-X12))</f>
+        <f>B12*V12</f>
+        <v/>
+      </c>
+      <c r="X12" s="12">
+        <f>B12-G12-H12-I12-J12-K12-N12-P12-E12+W12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="14">
+        <f>X12-U12</f>
+        <v/>
+      </c>
+      <c r="Z12" s="15">
+        <f>Y12/B12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="16">
+        <f>Y12/E12</f>
+        <v/>
+      </c>
+      <c r="AB12" s="12">
+        <f>(H12+I12+N12+P12+E12)/(1-(F12+$B$4+$B$3+Q12+S12-V12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
         <v>2500</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>663.86</v>
+      <c r="C13" s="9" t="n">
+        <v>463.19</v>
+      </c>
+      <c r="D13" s="10">
+        <f>$B$5</f>
+        <v/>
       </c>
       <c r="E13" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>D13+E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H13" s="12">
-        <f>C13*G13</f>
-        <v/>
+        <f>C13+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G13" s="12">
+        <f>B13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="J13" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="J13" s="12">
+        <f>B13*$B$4</f>
+        <v/>
+      </c>
+      <c r="K13" s="12">
+        <f>B13*$B$3</f>
+        <v/>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="N13" s="12">
+        <f>M13*(1-L13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P13" s="12">
+        <f>$B$6*$B$7*O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R13" s="12">
+        <f>B13*Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="12">
-        <f>C13*$B$4</f>
-        <v/>
-      </c>
-      <c r="M13" s="12">
-        <f>C13*$B$3</f>
-        <v/>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>154</v>
-      </c>
-      <c r="P13" s="12">
-        <f>O13*(1-N13)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R13" s="12">
-        <f>$B$6*$B$7*Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="11" t="n">
-        <v>0.1</v>
-      </c>
       <c r="T13" s="12">
-        <f>C13*S13</f>
-        <v/>
-      </c>
-      <c r="U13" s="11" t="n">
+        <f>B13*S13</f>
+        <v/>
+      </c>
+      <c r="U13" s="12">
+        <f>R13+T13</f>
+        <v/>
+      </c>
+      <c r="V13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="12">
-        <f>C13*U13</f>
-        <v/>
-      </c>
       <c r="W13" s="12">
-        <f>T13+V13</f>
-        <v/>
-      </c>
-      <c r="X13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="12">
-        <f>C13*X13</f>
-        <v/>
-      </c>
-      <c r="Z13" s="12">
-        <f>C13-H13-I13-J13-K13-L13-M13-P13-R13-F13+Y13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="14">
-        <f>Z13-W13</f>
-        <v/>
-      </c>
-      <c r="AB13" s="15">
-        <f>AA13/C13</f>
-        <v/>
-      </c>
-      <c r="AC13" s="16">
-        <f>AA13/F13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="12">
-        <f>(I13+J13+K13+P13+R13+F13)/(1-(G13+$B$4+$B$3+S13+U13-X13))</f>
+        <f>B13*V13</f>
+        <v/>
+      </c>
+      <c r="X13" s="12">
+        <f>B13-G13-H13-I13-J13-K13-N13-P13-E13+W13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="14">
+        <f>X13-U13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="15">
+        <f>Y13/B13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="16">
+        <f>Y13/E13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="12">
+        <f>(H13+I13+N13+P13+E13)/(1-(F13+$B$4+$B$3+Q13+S13-V13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>FBO</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
         <v>2500</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>463.19</v>
+      <c r="C14" s="9" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="D14" s="10">
+        <f>$B$5</f>
+        <v/>
       </c>
       <c r="E14" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>D14+E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="11" t="n">
+        <f>C14+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>0.41</v>
       </c>
-      <c r="H14" s="12">
-        <f>C14*G14</f>
-        <v/>
+      <c r="G14" s="12">
+        <f>B14*F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>67</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="J14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="J14" s="12">
+        <f>B14*$B$4</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>B14*$B$3</f>
+        <v/>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>0.9219000000000001</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="N14" s="12">
+        <f>M14*(1-L14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P14" s="12">
+        <f>$B$6*$B$7*O14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R14" s="12">
+        <f>B14*Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="12">
-        <f>C14*$B$4</f>
-        <v/>
-      </c>
-      <c r="M14" s="12">
-        <f>C14*$B$3</f>
-        <v/>
-      </c>
-      <c r="N14" s="11" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="P14" s="12">
-        <f>O14*(1-N14)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R14" s="12">
-        <f>$B$6*$B$7*Q14</f>
-        <v/>
-      </c>
-      <c r="S14" s="11" t="n">
-        <v>0.1</v>
-      </c>
       <c r="T14" s="12">
-        <f>C14*S14</f>
-        <v/>
-      </c>
-      <c r="U14" s="11" t="n">
+        <f>B14*S14</f>
+        <v/>
+      </c>
+      <c r="U14" s="12">
+        <f>R14+T14</f>
+        <v/>
+      </c>
+      <c r="V14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="12">
-        <f>C14*U14</f>
-        <v/>
-      </c>
       <c r="W14" s="12">
-        <f>T14+V14</f>
-        <v/>
-      </c>
-      <c r="X14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="12">
-        <f>C14*X14</f>
-        <v/>
-      </c>
-      <c r="Z14" s="12">
-        <f>C14-H14-I14-J14-K14-L14-M14-P14-R14-F14+Y14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="14">
-        <f>Z14-W14</f>
-        <v/>
-      </c>
-      <c r="AB14" s="15">
-        <f>AA14/C14</f>
-        <v/>
-      </c>
-      <c r="AC14" s="16">
-        <f>AA14/F14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="12">
-        <f>(I14+J14+K14+P14+R14+F14)/(1-(G14+$B$4+$B$3+S14+U14-X14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>463.19</v>
-      </c>
-      <c r="E15" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>D15+E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H15" s="12">
-        <f>C15*G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="12">
-        <f>C15*$B$4</f>
-        <v/>
-      </c>
-      <c r="M15" s="12">
-        <f>C15*$B$3</f>
-        <v/>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>218</v>
-      </c>
-      <c r="P15" s="12">
-        <f>O15*(1-N15)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R15" s="12">
-        <f>$B$6*$B$7*Q15</f>
-        <v/>
-      </c>
-      <c r="S15" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T15" s="12">
-        <f>C15*S15</f>
-        <v/>
-      </c>
-      <c r="U15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="12">
-        <f>C15*U15</f>
-        <v/>
-      </c>
-      <c r="W15" s="12">
-        <f>T15+V15</f>
-        <v/>
-      </c>
-      <c r="X15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="12">
-        <f>C15*X15</f>
-        <v/>
-      </c>
-      <c r="Z15" s="12">
-        <f>C15-H15-I15-J15-K15-L15-M15-P15-R15-F15+Y15</f>
-        <v/>
-      </c>
-      <c r="AA15" s="14">
-        <f>Z15-W15</f>
-        <v/>
-      </c>
-      <c r="AB15" s="15">
-        <f>AA15/C15</f>
-        <v/>
-      </c>
-      <c r="AC15" s="16">
-        <f>AA15/F15</f>
-        <v/>
-      </c>
-      <c r="AD15" s="12">
-        <f>(I15+J15+K15+P15+R15+F15)/(1-(G15+$B$4+$B$3+S15+U15-X15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>FBO</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>347.76</v>
-      </c>
-      <c r="E16" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>D16+E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H16" s="12">
-        <f>C16*G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="12">
-        <f>C16*$B$4</f>
-        <v/>
-      </c>
-      <c r="M16" s="12">
-        <f>C16*$B$3</f>
-        <v/>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="P16" s="12">
-        <f>O16*(1-N16)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R16" s="12">
-        <f>$B$6*$B$7*Q16</f>
-        <v/>
-      </c>
-      <c r="S16" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T16" s="12">
-        <f>C16*S16</f>
-        <v/>
-      </c>
-      <c r="U16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="12">
-        <f>C16*U16</f>
-        <v/>
-      </c>
-      <c r="W16" s="12">
-        <f>T16+V16</f>
-        <v/>
-      </c>
-      <c r="X16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="12">
-        <f>C16*X16</f>
-        <v/>
-      </c>
-      <c r="Z16" s="12">
-        <f>C16-H16-I16-J16-K16-L16-M16-P16-R16-F16+Y16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="14">
-        <f>Z16-W16</f>
-        <v/>
-      </c>
-      <c r="AB16" s="15">
-        <f>AA16/C16</f>
-        <v/>
-      </c>
-      <c r="AC16" s="16">
-        <f>AA16/F16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="12">
-        <f>(I16+J16+K16+P16+R16+F16)/(1-(G16+$B$4+$B$3+S16+U16-X16))</f>
+        <f>B14*V14</f>
+        <v/>
+      </c>
+      <c r="X14" s="12">
+        <f>B14-G14-H14-I14-J14-K14-N14-P14-E14+W14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="14">
+        <f>X14-U14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="15">
+        <f>Y14/B14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="16">
+        <f>Y14/E14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="12">
+        <f>(H14+I14+N14+P14+E14)/(1-(F14+$B$4+$B$3+Q14+S14-V14))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>347.76</v>
-      </c>
-      <c r="E17" s="10">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>D17+E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H17" s="12">
-        <f>C17*G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
-        <f>C17*$B$4</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>C17*$B$3</f>
-        <v/>
-      </c>
-      <c r="N17" s="11" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="P17" s="12">
-        <f>O17*(1-N17)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R17" s="12">
-        <f>$B$6*$B$7*Q17</f>
-        <v/>
-      </c>
-      <c r="S17" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T17" s="12">
-        <f>C17*S17</f>
-        <v/>
-      </c>
-      <c r="U17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="12">
-        <f>C17*U17</f>
-        <v/>
-      </c>
-      <c r="W17" s="12">
-        <f>T17+V17</f>
-        <v/>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="12">
-        <f>C17*X17</f>
-        <v/>
-      </c>
-      <c r="Z17" s="12">
-        <f>C17-H17-I17-J17-K17-L17-M17-P17-R17-F17+Y17</f>
-        <v/>
-      </c>
-      <c r="AA17" s="14">
-        <f>Z17-W17</f>
-        <v/>
-      </c>
-      <c r="AB17" s="15">
-        <f>AA17/C17</f>
-        <v/>
-      </c>
-      <c r="AC17" s="16">
-        <f>AA17/F17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="12">
-        <f>(I17+J17+K17+P17+R17+F17)/(1-(G17+$B$4+$B$3+S17+U17-X17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Жёлтые ячейки — вход (цена, себест., комиссия, логистика, обработка отправления, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Реклама разбита по тарифам: Трафареты % (доля от цены) и Продвижение в поиске % (ставка от продажи). Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки и прибавляются к марже. Меняешь цену в колонке C → маржа и ROI пересчитываются.</t>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Только FBO. Жёлтые ячейки — вход (цена, себест., комиссия, логистика, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Реклама по актуальным форматам Ozon: Оплата за клик % (CPC, продвижение товаров — ДРР) и Вывод в топ % (CPO — ставка от цены заказа). Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки и прибавляются к марже. Меняешь цену в колонке B → маржа и ROI пересчитываются.</t>
         </is>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -109,8 +109,8 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -502,13 +502,14 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,7 +612,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Посл.миля</t>
+          <t>Доставка до ПВЗ</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -676,35 +677,40 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
+          <t>ДРР %</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
           <t>Соинвест, %</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>Соинвест ₽</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="Y11" s="6" t="inlineStr">
         <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="Z11" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="Z11" s="6" t="inlineStr">
+      <c r="AA11" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AB11" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr">
+      <c r="AC11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -786,31 +792,35 @@
         <f>R12+T12</f>
         <v/>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" s="14">
+        <f>U12/B12</f>
+        <v/>
+      </c>
+      <c r="W12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="12">
-        <f>B12*V12</f>
-        <v/>
-      </c>
       <c r="X12" s="12">
-        <f>B12-G12-H12-I12-J12-K12-N12-P12-E12+W12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="14">
-        <f>X12-U12</f>
+        <f>B12*W12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="12">
+        <f>B12-G12-H12-I12-J12-K12-N12-P12-E12+X12</f>
         <v/>
       </c>
       <c r="Z12" s="15">
-        <f>Y12/B12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="16">
-        <f>Y12/E12</f>
-        <v/>
-      </c>
-      <c r="AB12" s="12">
-        <f>(H12+I12+N12+P12+E12)/(1-(F12+$B$4+$B$3+Q12+S12-V12))</f>
+        <f>Y12-U12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="14">
+        <f>Z12/B12</f>
+        <v/>
+      </c>
+      <c r="AB12" s="16">
+        <f>Z12/E12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="12">
+        <f>(H12+I12+N12+P12+E12)/(1-(F12+$B$4+$B$3+Q12+S12-W12))</f>
         <v/>
       </c>
     </row>
@@ -890,31 +900,35 @@
         <f>R13+T13</f>
         <v/>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="V13" s="14">
+        <f>U13/B13</f>
+        <v/>
+      </c>
+      <c r="W13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="12">
-        <f>B13*V13</f>
-        <v/>
-      </c>
       <c r="X13" s="12">
-        <f>B13-G13-H13-I13-J13-K13-N13-P13-E13+W13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="14">
-        <f>X13-U13</f>
+        <f>B13*W13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="12">
+        <f>B13-G13-H13-I13-J13-K13-N13-P13-E13+X13</f>
         <v/>
       </c>
       <c r="Z13" s="15">
-        <f>Y13/B13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="16">
-        <f>Y13/E13</f>
-        <v/>
-      </c>
-      <c r="AB13" s="12">
-        <f>(H13+I13+N13+P13+E13)/(1-(F13+$B$4+$B$3+Q13+S13-V13))</f>
+        <f>Y13-U13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="14">
+        <f>Z13/B13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="16">
+        <f>Z13/E13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="12">
+        <f>(H13+I13+N13+P13+E13)/(1-(F13+$B$4+$B$3+Q13+S13-W13))</f>
         <v/>
       </c>
     </row>
@@ -994,31 +1008,35 @@
         <f>R14+T14</f>
         <v/>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" s="14">
+        <f>U14/B14</f>
+        <v/>
+      </c>
+      <c r="W14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="12">
-        <f>B14*V14</f>
-        <v/>
-      </c>
       <c r="X14" s="12">
-        <f>B14-G14-H14-I14-J14-K14-N14-P14-E14+W14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="14">
-        <f>X14-U14</f>
+        <f>B14*W14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="12">
+        <f>B14-G14-H14-I14-J14-K14-N14-P14-E14+X14</f>
         <v/>
       </c>
       <c r="Z14" s="15">
-        <f>Y14/B14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="16">
-        <f>Y14/E14</f>
-        <v/>
-      </c>
-      <c r="AB14" s="12">
-        <f>(H14+I14+N14+P14+E14)/(1-(F14+$B$4+$B$3+Q14+S14-V14))</f>
+        <f>Y14-U14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="14">
+        <f>Z14/B14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="16">
+        <f>Z14/E14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="12">
+        <f>(H14+I14+N14+P14+E14)/(1-(F14+$B$4+$B$3+Q14+S14-W14))</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -104,10 +104,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,38 +478,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AF17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,135 +585,150 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
+          <t>СПП, %</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Цена с СПП</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
           <t>Себест.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Фулфилмент</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>База затрат</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Комиссия %</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Комиссия ₽</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Наценка нелок., ₽</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>Доставка до ПВЗ</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Эквайринг</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Налог</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Выкуп %</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог база</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Объём, л</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Хранение</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик, %</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик ₽</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ, %</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ ₽</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>Реклама всего ₽</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="Y11" s="6" t="inlineStr">
         <is>
           <t>ДРР %</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="Z11" s="6" t="inlineStr">
         <is>
           <t>Соинвест, %</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="AA11" s="6" t="inlineStr">
         <is>
           <t>Соинвест ₽</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="AB11" s="6" t="inlineStr">
         <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="Z11" s="6" t="inlineStr">
+      <c r="AC11" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr">
+      <c r="AE11" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AF11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -726,101 +744,111 @@
         <v>2500</v>
       </c>
       <c r="C12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <f>B12*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="n">
         <v>663.86</v>
       </c>
-      <c r="D12" s="10">
+      <c r="F12" s="12">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E12" s="10">
-        <f>C12+D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="12">
+        <f>E12+F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="G12" s="12">
-        <f>B12*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="I12" s="10">
+        <f>B12*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="K12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="J12" s="12">
+      <c r="M12" s="10">
         <f>B12*$B$4</f>
         <v/>
       </c>
-      <c r="K12" s="12">
-        <f>B12*$B$3</f>
-        <v/>
-      </c>
-      <c r="L12" s="11" t="n">
+      <c r="N12" s="10">
+        <f>D12*$B$3</f>
+        <v/>
+      </c>
+      <c r="O12" s="9" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="P12" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="N12" s="12">
-        <f>M12*(1-L12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="13" t="n">
+      <c r="Q12" s="10">
+        <f>P12*(1-O12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="P12" s="12">
-        <f>$B$6*$B$7*O12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="11" t="n">
+      <c r="S12" s="10">
+        <f>$B$6*$B$7*R12</f>
+        <v/>
+      </c>
+      <c r="T12" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="R12" s="12">
-        <f>B12*Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="11" t="n">
+      <c r="U12" s="10">
+        <f>B12*T12</f>
+        <v/>
+      </c>
+      <c r="V12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="12">
-        <f>B12*S12</f>
-        <v/>
-      </c>
-      <c r="U12" s="12">
-        <f>R12+T12</f>
-        <v/>
-      </c>
-      <c r="V12" s="14">
-        <f>U12/B12</f>
-        <v/>
-      </c>
-      <c r="W12" s="11" t="n">
+      <c r="W12" s="10">
+        <f>B12*V12</f>
+        <v/>
+      </c>
+      <c r="X12" s="10">
+        <f>U12+W12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="14">
+        <f>X12/B12</f>
+        <v/>
+      </c>
+      <c r="Z12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X12" s="12">
-        <f>B12*W12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="12">
-        <f>B12-G12-H12-I12-J12-K12-N12-P12-E12+X12</f>
-        <v/>
-      </c>
-      <c r="Z12" s="15">
-        <f>Y12-U12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="14">
-        <f>Z12/B12</f>
-        <v/>
-      </c>
-      <c r="AB12" s="16">
-        <f>Z12/E12</f>
-        <v/>
-      </c>
-      <c r="AC12" s="12">
-        <f>(H12+I12+N12+P12+E12)/(1-(F12+$B$4+$B$3+Q12+S12-W12))</f>
+      <c r="AA12" s="10">
+        <f>B12*Z12</f>
+        <v/>
+      </c>
+      <c r="AB12" s="10">
+        <f>B12-I12-J12-K12-L12-M12-N12-Q12-S12-G12+AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="15">
+        <f>AB12-X12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="14">
+        <f>AC12/B12</f>
+        <v/>
+      </c>
+      <c r="AE12" s="16">
+        <f>AC12/G12</f>
+        <v/>
+      </c>
+      <c r="AF12" s="10">
+        <f>(J12+K12+L12+Q12+S12+G12)/(1-(H12+$B$4+(1-C12)*$B$3+T12+V12-Z12))</f>
         <v/>
       </c>
     </row>
@@ -834,101 +862,111 @@
         <v>2500</v>
       </c>
       <c r="C13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <f>B13*(1-C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>463.19</v>
       </c>
-      <c r="D13" s="10">
+      <c r="F13" s="12">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E13" s="10">
-        <f>C13+D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="G13" s="12">
+        <f>E13+F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="G13" s="12">
-        <f>B13*F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="I13" s="10">
+        <f>B13*H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="K13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="J13" s="12">
+      <c r="M13" s="10">
         <f>B13*$B$4</f>
         <v/>
       </c>
-      <c r="K13" s="12">
-        <f>B13*$B$3</f>
-        <v/>
-      </c>
-      <c r="L13" s="11" t="n">
+      <c r="N13" s="10">
+        <f>D13*$B$3</f>
+        <v/>
+      </c>
+      <c r="O13" s="9" t="n">
         <v>0.96</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="P13" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="N13" s="12">
-        <f>M13*(1-L13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="13" t="n">
+      <c r="Q13" s="10">
+        <f>P13*(1-O13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="P13" s="12">
-        <f>$B$6*$B$7*O13</f>
-        <v/>
-      </c>
-      <c r="Q13" s="11" t="n">
+      <c r="S13" s="10">
+        <f>$B$6*$B$7*R13</f>
+        <v/>
+      </c>
+      <c r="T13" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="R13" s="12">
-        <f>B13*Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="11" t="n">
+      <c r="U13" s="10">
+        <f>B13*T13</f>
+        <v/>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="12">
-        <f>B13*S13</f>
-        <v/>
-      </c>
-      <c r="U13" s="12">
-        <f>R13+T13</f>
-        <v/>
-      </c>
-      <c r="V13" s="14">
-        <f>U13/B13</f>
-        <v/>
-      </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" s="10">
+        <f>B13*V13</f>
+        <v/>
+      </c>
+      <c r="X13" s="10">
+        <f>U13+W13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="14">
+        <f>X13/B13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X13" s="12">
-        <f>B13*W13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="12">
-        <f>B13-G13-H13-I13-J13-K13-N13-P13-E13+X13</f>
-        <v/>
-      </c>
-      <c r="Z13" s="15">
-        <f>Y13-U13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="14">
-        <f>Z13/B13</f>
-        <v/>
-      </c>
-      <c r="AB13" s="16">
-        <f>Z13/E13</f>
-        <v/>
-      </c>
-      <c r="AC13" s="12">
-        <f>(H13+I13+N13+P13+E13)/(1-(F13+$B$4+$B$3+Q13+S13-W13))</f>
+      <c r="AA13" s="10">
+        <f>B13*Z13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="10">
+        <f>B13-I13-J13-K13-L13-M13-N13-Q13-S13-G13+AA13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="15">
+        <f>AB13-X13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="14">
+        <f>AC13/B13</f>
+        <v/>
+      </c>
+      <c r="AE13" s="16">
+        <f>AC13/G13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="10">
+        <f>(J13+K13+L13+Q13+S13+G13)/(1-(H13+$B$4+(1-C13)*$B$3+T13+V13-Z13))</f>
         <v/>
       </c>
     </row>
@@ -942,108 +980,118 @@
         <v>2500</v>
       </c>
       <c r="C14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10">
+        <f>B14*(1-C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>347.76</v>
       </c>
-      <c r="D14" s="10">
+      <c r="F14" s="12">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E14" s="10">
-        <f>C14+D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="11" t="n">
+      <c r="G14" s="12">
+        <f>E14+F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="G14" s="12">
-        <f>B14*F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="I14" s="10">
+        <f>B14*H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="K14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="J14" s="12">
+      <c r="M14" s="10">
         <f>B14*$B$4</f>
         <v/>
       </c>
-      <c r="K14" s="12">
-        <f>B14*$B$3</f>
-        <v/>
-      </c>
-      <c r="L14" s="11" t="n">
+      <c r="N14" s="10">
+        <f>D14*$B$3</f>
+        <v/>
+      </c>
+      <c r="O14" s="9" t="n">
         <v>0.9219000000000001</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="P14" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="N14" s="12">
-        <f>M14*(1-L14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="13" t="n">
+      <c r="Q14" s="10">
+        <f>P14*(1-O14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="P14" s="12">
-        <f>$B$6*$B$7*O14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="11" t="n">
+      <c r="S14" s="10">
+        <f>$B$6*$B$7*R14</f>
+        <v/>
+      </c>
+      <c r="T14" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="R14" s="12">
-        <f>B14*Q14</f>
-        <v/>
-      </c>
-      <c r="S14" s="11" t="n">
+      <c r="U14" s="10">
+        <f>B14*T14</f>
+        <v/>
+      </c>
+      <c r="V14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="12">
-        <f>B14*S14</f>
-        <v/>
-      </c>
-      <c r="U14" s="12">
-        <f>R14+T14</f>
-        <v/>
-      </c>
-      <c r="V14" s="14">
-        <f>U14/B14</f>
-        <v/>
-      </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" s="10">
+        <f>B14*V14</f>
+        <v/>
+      </c>
+      <c r="X14" s="10">
+        <f>U14+W14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="14">
+        <f>X14/B14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="12">
-        <f>B14*W14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="12">
-        <f>B14-G14-H14-I14-J14-K14-N14-P14-E14+X14</f>
-        <v/>
-      </c>
-      <c r="Z14" s="15">
-        <f>Y14-U14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="14">
-        <f>Z14/B14</f>
-        <v/>
-      </c>
-      <c r="AB14" s="16">
-        <f>Z14/E14</f>
-        <v/>
-      </c>
-      <c r="AC14" s="12">
-        <f>(H14+I14+N14+P14+E14)/(1-(F14+$B$4+$B$3+Q14+S14-W14))</f>
+      <c r="AA14" s="10">
+        <f>B14*Z14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="10">
+        <f>B14-I14-J14-K14-L14-M14-N14-Q14-S14-G14+AA14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="15">
+        <f>AB14-X14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="14">
+        <f>AC14/B14</f>
+        <v/>
+      </c>
+      <c r="AE14" s="16">
+        <f>AC14/G14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="10">
+        <f>(J14+K14+L14+Q14+S14+G14)/(1-(H14+$B$4+(1-C14)*$B$3+T14+V14-Z14))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Только FBO. Жёлтые ячейки — вход (цена, себест., комиссия, логистика, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Реклама по актуальным форматам Ozon: Оплата за клик % (CPC, продвижение товаров — ДРР) и Вывод в топ % (CPO — ставка от цены заказа). Соинвест % возьми в кабинете (Цены → Баллы за скидки): баллы компенсируют издержки и прибавляются к марже. Меняешь цену в колонке B → маржа и ROI пересчитываются.</t>
+          <t>Только FBO. Жёлтые ячейки — вход (цена, СПП %, себест., комиссия, логистика, наценка за нелокальность, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Цена с СПП = Цена×(1−СПП%); налог считается от цены с СПП. Объём — в литрах из габаритов карточки (если выгружены, иначе объёмный вес). Реклама по актуальным форматам Ozon: Оплата за клик % (CPC) и Вывод в топ % (CPO). Соинвест % — из кабинета (Цены → Баллы за скидки), баллы прибавляются к марже. Меняешь цену в колонке B → маржа и ROI пересчитываются.</t>
         </is>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -796,7 +796,7 @@
         <v/>
       </c>
       <c r="R12" s="13" t="n">
-        <v>0.2</v>
+        <v>0.735</v>
       </c>
       <c r="S12" s="10">
         <f>$B$6*$B$7*R12</f>
@@ -914,7 +914,7 @@
         <v/>
       </c>
       <c r="R13" s="13" t="n">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="S13" s="10">
         <f>$B$6*$B$7*R13</f>
@@ -1032,7 +1032,7 @@
         <v/>
       </c>
       <c r="R14" s="13" t="n">
-        <v>0.3</v>
+        <v>0.832</v>
       </c>
       <c r="S14" s="10">
         <f>$B$6*$B$7*R14</f>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,19 +27,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -52,17 +66,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,17 +90,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -115,7 +130,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -479,35 +494,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="13" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="17" max="19"/>
+    <col width="13" customWidth="1" min="20" max="21"/>
+    <col width="12" customWidth="1" min="22" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="11" customWidth="1" min="26" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
@@ -515,7 +520,7 @@
     <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ — меняй жёлтые ячейки, всё пересчитается</t>
@@ -529,7 +534,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +574,17 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Наценка за нелокальные продажи %</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -741,10 +756,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>2500</v>
+        <v>2722</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D12" s="10">
         <f>B12*(1-C12)</f>
@@ -771,8 +786,9 @@
       <c r="J12" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <v>0</v>
+      <c r="K12" s="12">
+        <f>J12*$B$8</f>
+        <v/>
       </c>
       <c r="L12" s="8" t="n">
         <v>25</v>
@@ -786,10 +802,11 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>81</v>
+        <v>0.9</v>
+      </c>
+      <c r="P12" s="8">
+        <f>J12</f>
+        <v/>
       </c>
       <c r="Q12" s="10">
         <f>P12*(1-O12)</f>
@@ -803,14 +820,14 @@
         <v/>
       </c>
       <c r="T12" s="9" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U12" s="10">
         <f>B12*T12</f>
         <v/>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W12" s="10">
         <f>B12*V12</f>
@@ -862,7 +879,7 @@
         <v>2500</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D13" s="10">
         <f>B13*(1-C13)</f>
@@ -889,8 +906,9 @@
       <c r="J13" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <v>0</v>
+      <c r="K13" s="12">
+        <f>J13*$B$8</f>
+        <v/>
       </c>
       <c r="L13" s="8" t="n">
         <v>25</v>
@@ -904,10 +922,10 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="10">
         <f>P13*(1-O13)</f>
@@ -980,7 +998,7 @@
         <v>2500</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D14" s="10">
         <f>B14*(1-C14)</f>
@@ -1007,8 +1025,9 @@
       <c r="J14" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>0</v>
+      <c r="K14" s="12">
+        <f>J14*$B$8</f>
+        <v/>
       </c>
       <c r="L14" s="8" t="n">
         <v>25</v>
@@ -1022,10 +1041,11 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0.9219000000000001</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>81</v>
+        <v>0.9</v>
+      </c>
+      <c r="P14" s="8">
+        <f>J14</f>
+        <v/>
       </c>
       <c r="Q14" s="10">
         <f>P14*(1-O14)</f>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -787,7 +787,7 @@
         <v>67</v>
       </c>
       <c r="K12" s="12">
-        <f>J12*$B$8</f>
+        <f>B12*$B$8</f>
         <v/>
       </c>
       <c r="L12" s="8" t="n">
@@ -865,7 +865,7 @@
         <v/>
       </c>
       <c r="AF12" s="10">
-        <f>(J12+K12+L12+Q12+S12+G12)/(1-(H12+$B$4+(1-C12)*$B$3+T12+V12-Z12))</f>
+        <f>(J12+L12+Q12+S12+G12)/(1-(H12+$B$4+(1-C12)*$B$3+$B$8+T12+V12-Z12))</f>
         <v/>
       </c>
     </row>
@@ -907,7 +907,7 @@
         <v>74</v>
       </c>
       <c r="K13" s="12">
-        <f>J13*$B$8</f>
+        <f>B13*$B$8</f>
         <v/>
       </c>
       <c r="L13" s="8" t="n">
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="AF13" s="10">
-        <f>(J13+K13+L13+Q13+S13+G13)/(1-(H13+$B$4+(1-C13)*$B$3+T13+V13-Z13))</f>
+        <f>(J13+L13+Q13+S13+G13)/(1-(H13+$B$4+(1-C13)*$B$3+$B$8+T13+V13-Z13))</f>
         <v/>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         <v>67</v>
       </c>
       <c r="K14" s="12">
-        <f>J14*$B$8</f>
+        <f>B14*$B$8</f>
         <v/>
       </c>
       <c r="L14" s="8" t="n">
@@ -1104,7 +1104,7 @@
         <v/>
       </c>
       <c r="AF14" s="10">
-        <f>(J14+K14+L14+Q14+S14+G14)/(1-(H14+$B$4+(1-C14)*$B$3+T14+V14-Z14))</f>
+        <f>(J14+L14+Q14+S14+G14)/(1-(H14+$B$4+(1-C14)*$B$3+$B$8+T14+V14-Z14))</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Юнитка Ozon (live)'!$A$11:$AG$24</definedName>
+  </definedNames>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +57,13 @@
       <i val="1"/>
       <color rgb="FF808080"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -107,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +137,9 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -493,31 +505,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF17"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="19"/>
-    <col width="13" customWidth="1" min="20" max="21"/>
-    <col width="12" customWidth="1" min="22" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="11" customWidth="1" min="26" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="42" customWidth="1" min="1" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="20"/>
+    <col width="13" customWidth="1" min="21" max="22"/>
+    <col width="12" customWidth="1" min="23" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="11" customWidth="1" min="27" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
@@ -526,6 +538,7 @@
           <t>ПАРАМЕТРЫ — меняй жёлтые ячейки, всё пересчитается</t>
         </is>
       </c>
+      <c r="B1" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,7 +546,7 @@
           <t>Налог с оборота</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -543,7 +556,7 @@
           <t>Эквайринг</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -553,7 +566,7 @@
           <t>Фулфилмент, ₽/шт</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -563,7 +576,7 @@
           <t>Хранение, ₽/л/день</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="C6" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -573,7 +586,7 @@
           <t>Дней хранения</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -583,7 +596,7 @@
           <t>Наценка за нелокальные продажи %</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -595,155 +608,160 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>Цена конкурентов с СПП</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>СПП, %</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Цена с СПП</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Себест.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Фулфилмент</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>База затрат</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Комиссия %</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>Комиссия ₽</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>Наценка нелок., ₽</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Доставка до ПВЗ</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Эквайринг</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Налог</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Выкуп %</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог база</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Обр.лог</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Объём, л</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>Хранение</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик, %</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик ₽</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ, %</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="X11" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ ₽</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="Y11" s="6" t="inlineStr">
         <is>
           <t>Реклама всего ₽</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="Z11" s="6" t="inlineStr">
         <is>
           <t>ДРР %</t>
         </is>
       </c>
-      <c r="Z11" s="6" t="inlineStr">
+      <c r="AA11" s="6" t="inlineStr">
         <is>
           <t>Соинвест, %</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AB11" s="6" t="inlineStr">
         <is>
           <t>Соинвест ₽</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr">
+      <c r="AC11" s="6" t="inlineStr">
         <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="AD11" s="6" t="inlineStr">
+      <c r="AE11" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="AE11" s="6" t="inlineStr">
+      <c r="AF11" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="AF11" s="6" t="inlineStr">
+      <c r="AG11" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
@@ -755,117 +773,122 @@
           <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>2722</v>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1250-1300</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="D12" s="10">
-        <f>B12*(1-C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10">
+        <f>C12*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>663.86</v>
       </c>
-      <c r="F12" s="12">
-        <f>$B$5</f>
-        <v/>
-      </c>
       <c r="G12" s="12">
-        <f>E12+F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="9" t="n">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H12" s="12">
+        <f>F12+G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="I12" s="10">
-        <f>B12*H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="8" t="n">
+      <c r="J12" s="10">
+        <f>C12*I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K12" s="12">
-        <f>B12*$B$8</f>
-        <v/>
-      </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="12">
+        <f>C12*$C$8</f>
+        <v/>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M12" s="10">
-        <f>B12*$B$4</f>
-        <v/>
-      </c>
       <c r="N12" s="10">
-        <f>D12*$B$3</f>
-        <v/>
-      </c>
-      <c r="O12" s="9" t="n">
+        <f>C12*$C$4</f>
+        <v/>
+      </c>
+      <c r="O12" s="10">
+        <f>E12*$C$3</f>
+        <v/>
+      </c>
+      <c r="P12" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="P12" s="8">
-        <f>J12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="10">
-        <f>P12*(1-O12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="13" t="n">
+      <c r="Q12" s="8">
+        <f>K12</f>
+        <v/>
+      </c>
+      <c r="R12" s="10">
+        <f>Q12*(1-P12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="13" t="n">
         <v>0.735</v>
       </c>
-      <c r="S12" s="10">
-        <f>$B$6*$B$7*R12</f>
-        <v/>
-      </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" s="10">
+        <f>$C$6*$C$7*S12</f>
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="U12" s="10">
-        <f>B12*T12</f>
-        <v/>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="10">
+        <f>C12*U12</f>
+        <v/>
+      </c>
+      <c r="W12" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="W12" s="10">
-        <f>B12*V12</f>
-        <v/>
-      </c>
       <c r="X12" s="10">
-        <f>U12+W12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="14">
-        <f>X12/B12</f>
-        <v/>
-      </c>
-      <c r="Z12" s="9" t="n">
+        <f>C12*W12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f>V12+X12</f>
+        <v/>
+      </c>
+      <c r="Z12" s="14">
+        <f>Y12/C12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" s="10">
-        <f>B12*Z12</f>
-        <v/>
-      </c>
       <c r="AB12" s="10">
-        <f>B12-I12-J12-K12-L12-M12-N12-Q12-S12-G12+AA12</f>
-        <v/>
-      </c>
-      <c r="AC12" s="15">
-        <f>AB12-X12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="14">
-        <f>AC12/B12</f>
-        <v/>
-      </c>
-      <c r="AE12" s="16">
-        <f>AC12/G12</f>
-        <v/>
-      </c>
-      <c r="AF12" s="10">
-        <f>(J12+L12+Q12+S12+G12)/(1-(H12+$B$4+(1-C12)*$B$3+$B$8+T12+V12-Z12))</f>
+        <f>C12*AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="10">
+        <f>C12-J12-K12-L12-M12-N12-O12-R12-T12-H12+AB12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="15">
+        <f>AC12-Y12</f>
+        <v/>
+      </c>
+      <c r="AE12" s="14">
+        <f>AD12/C12</f>
+        <v/>
+      </c>
+      <c r="AF12" s="16">
+        <f>AD12/H12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="10">
+        <f>(K12+M12+R12+T12+H12)/(1-(I12+$C$4+(1-D12)*$C$3+$C$8+U12+W12-AA12))</f>
         <v/>
       </c>
     </row>
@@ -875,116 +898,122 @@
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1076-1244</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="D13" s="10">
-        <f>B13*(1-C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10">
+        <f>C13*(1-D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>463.19</v>
       </c>
-      <c r="F13" s="12">
-        <f>$B$5</f>
-        <v/>
-      </c>
       <c r="G13" s="12">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="9" t="n">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
+        <f>F13+G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="I13" s="10">
-        <f>B13*H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="10">
+        <f>C13*I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="K13" s="12">
-        <f>B13*$B$8</f>
-        <v/>
-      </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="12">
+        <f>C13*$C$8</f>
+        <v/>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M13" s="10">
-        <f>B13*$B$4</f>
-        <v/>
-      </c>
       <c r="N13" s="10">
-        <f>D13*$B$3</f>
-        <v/>
-      </c>
-      <c r="O13" s="9" t="n">
+        <f>C13*$C$4</f>
+        <v/>
+      </c>
+      <c r="O13" s="10">
+        <f>E13*$C$3</f>
+        <v/>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q13" s="10">
-        <f>P13*(1-O13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="13" t="n">
+      <c r="Q13" s="8">
+        <f>K13</f>
+        <v/>
+      </c>
+      <c r="R13" s="10">
+        <f>Q13*(1-P13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="13" t="n">
         <v>1.28</v>
       </c>
-      <c r="S13" s="10">
-        <f>$B$6*$B$7*R13</f>
-        <v/>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U13" s="10">
-        <f>B13*T13</f>
-        <v/>
-      </c>
-      <c r="V13" s="9" t="n">
+      <c r="T13" s="10">
+        <f>$C$6*$C$7*S13</f>
+        <v/>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V13" s="10">
+        <f>C13*U13</f>
+        <v/>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X13" s="10">
+        <f>C13*W13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f>V13+X13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="14">
+        <f>Y13/C13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="10">
-        <f>B13*V13</f>
-        <v/>
-      </c>
-      <c r="X13" s="10">
-        <f>U13+W13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="14">
-        <f>X13/B13</f>
-        <v/>
-      </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="10">
-        <f>B13*Z13</f>
-        <v/>
-      </c>
       <c r="AB13" s="10">
-        <f>B13-I13-J13-K13-L13-M13-N13-Q13-S13-G13+AA13</f>
-        <v/>
-      </c>
-      <c r="AC13" s="15">
-        <f>AB13-X13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="14">
-        <f>AC13/B13</f>
-        <v/>
-      </c>
-      <c r="AE13" s="16">
-        <f>AC13/G13</f>
-        <v/>
-      </c>
-      <c r="AF13" s="10">
-        <f>(J13+L13+Q13+S13+G13)/(1-(H13+$B$4+(1-C13)*$B$3+$B$8+T13+V13-Z13))</f>
+        <f>C13*AA13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="10">
+        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-H13+AB13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="15">
+        <f>AC13-Y13</f>
+        <v/>
+      </c>
+      <c r="AE13" s="14">
+        <f>AD13/C13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="16">
+        <f>AD13/H13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="10">
+        <f>(K13+M13+R13+T13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+U13+W13-AA13))</f>
         <v/>
       </c>
     </row>
@@ -994,128 +1023,1341 @@
           <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>483 (много подделок)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1660</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="10">
+        <f>C14*(1-D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="G14" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
+        <f>F14+G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J14" s="10">
+        <f>C14*I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L14" s="12">
+        <f>C14*$C$8</f>
+        <v/>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" s="10">
+        <f>C14*$C$4</f>
+        <v/>
+      </c>
+      <c r="O14" s="10">
+        <f>E14*$C$3</f>
+        <v/>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="8">
+        <f>K14</f>
+        <v/>
+      </c>
+      <c r="R14" s="10">
+        <f>Q14*(1-P14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="13" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="T14" s="10">
+        <f>$C$6*$C$7*S14</f>
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V14" s="10">
+        <f>C14*U14</f>
+        <v/>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X14" s="10">
+        <f>C14*W14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f>V14+X14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="14">
+        <f>Y14/C14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="10">
+        <f>C14*AA14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="10">
+        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-H14+AB14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="15">
+        <f>AC14-Y14</f>
+        <v/>
+      </c>
+      <c r="AE14" s="14">
+        <f>AD14/C14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="16">
+        <f>AD14/H14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="10">
+        <f>(K14+M14+R14+T14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+U14+W14-AA14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="D15" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="D14" s="10">
-        <f>B14*(1-C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>347.76</v>
-      </c>
-      <c r="F14" s="12">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="G14" s="12">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="9" t="n">
+      <c r="E15" s="10">
+        <f>C15*(1-D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="G15" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H15" s="12">
+        <f>F15+G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="I14" s="10">
-        <f>B14*H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="8" t="n">
+      <c r="J15" s="10">
+        <f>C15*I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K14" s="12">
-        <f>B14*$B$8</f>
-        <v/>
-      </c>
-      <c r="L14" s="8" t="n">
+      <c r="L15" s="12">
+        <f>C15*$C$8</f>
+        <v/>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M14" s="10">
-        <f>B14*$B$4</f>
-        <v/>
-      </c>
-      <c r="N14" s="10">
-        <f>D14*$B$3</f>
-        <v/>
-      </c>
-      <c r="O14" s="9" t="n">
+      <c r="N15" s="10">
+        <f>C15*$C$4</f>
+        <v/>
+      </c>
+      <c r="O15" s="10">
+        <f>E15*$C$3</f>
+        <v/>
+      </c>
+      <c r="P15" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="P14" s="8">
-        <f>J14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="10">
-        <f>P14*(1-O14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="13" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="S14" s="10">
-        <f>$B$6*$B$7*R14</f>
-        <v/>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U14" s="10">
-        <f>B14*T14</f>
-        <v/>
-      </c>
-      <c r="V14" s="9" t="n">
+      <c r="Q15" s="8">
+        <f>K15</f>
+        <v/>
+      </c>
+      <c r="R15" s="10">
+        <f>Q15*(1-P15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="20" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T15" s="10">
+        <f>$C$6*$C$7*S15</f>
+        <v/>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V15" s="10">
+        <f>C15*U15</f>
+        <v/>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X15" s="10">
+        <f>C15*W15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f>V15+X15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="14">
+        <f>Y15/C15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="10">
-        <f>B14*V14</f>
-        <v/>
-      </c>
-      <c r="X14" s="10">
-        <f>U14+W14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="14">
-        <f>X14/B14</f>
-        <v/>
-      </c>
-      <c r="Z14" s="9" t="n">
+      <c r="AB15" s="10">
+        <f>C15*AA15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="10">
+        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-H15+AB15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="15">
+        <f>AC15-Y15</f>
+        <v/>
+      </c>
+      <c r="AE15" s="14">
+        <f>AD15/C15</f>
+        <v/>
+      </c>
+      <c r="AF15" s="16">
+        <f>AD15/H15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="10">
+        <f>(K15+M15+R15+T15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+U15+W15-AA15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E16" s="10">
+        <f>C16*(1-D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="G16" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H16" s="12">
+        <f>F16+G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J16" s="10">
+        <f>C16*I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L16" s="12">
+        <f>C16*$C$8</f>
+        <v/>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N16" s="10">
+        <f>C16*$C$4</f>
+        <v/>
+      </c>
+      <c r="O16" s="10">
+        <f>E16*$C$3</f>
+        <v/>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q16" s="8">
+        <f>K16</f>
+        <v/>
+      </c>
+      <c r="R16" s="10">
+        <f>Q16*(1-P16)</f>
+        <v/>
+      </c>
+      <c r="S16" s="20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T16" s="10">
+        <f>$C$6*$C$7*S16</f>
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V16" s="10">
+        <f>C16*U16</f>
+        <v/>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X16" s="10">
+        <f>C16*W16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f>V16+X16</f>
+        <v/>
+      </c>
+      <c r="Z16" s="14">
+        <f>Y16/C16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA14" s="10">
-        <f>B14*Z14</f>
-        <v/>
-      </c>
-      <c r="AB14" s="10">
-        <f>B14-I14-J14-K14-L14-M14-N14-Q14-S14-G14+AA14</f>
-        <v/>
-      </c>
-      <c r="AC14" s="15">
-        <f>AB14-X14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="14">
-        <f>AC14/B14</f>
-        <v/>
-      </c>
-      <c r="AE14" s="16">
-        <f>AC14/G14</f>
-        <v/>
-      </c>
-      <c r="AF14" s="10">
-        <f>(J14+L14+Q14+S14+G14)/(1-(H14+$B$4+(1-C14)*$B$3+$B$8+T14+V14-Z14))</f>
+      <c r="AB16" s="10">
+        <f>C16*AA16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="10">
+        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-H16+AB16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="15">
+        <f>AC16-Y16</f>
+        <v/>
+      </c>
+      <c r="AE16" s="14">
+        <f>AD16/C16</f>
+        <v/>
+      </c>
+      <c r="AF16" s="16">
+        <f>AD16/H16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="10">
+        <f>(K16+M16+R16+T16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+U16+W16-AA16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E17" s="10">
+        <f>C17*(1-D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="G17" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H17" s="12">
+        <f>F17+G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J17" s="10">
+        <f>C17*I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="L17" s="12">
+        <f>C17*$C$8</f>
+        <v/>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N17" s="10">
+        <f>C17*$C$4</f>
+        <v/>
+      </c>
+      <c r="O17" s="10">
+        <f>E17*$C$3</f>
+        <v/>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="8">
+        <f>K17</f>
+        <v/>
+      </c>
+      <c r="R17" s="10">
+        <f>Q17*(1-P17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T17" s="10">
+        <f>$C$6*$C$7*S17</f>
+        <v/>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V17" s="10">
+        <f>C17*U17</f>
+        <v/>
+      </c>
+      <c r="W17" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X17" s="10">
+        <f>C17*W17</f>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f>V17+X17</f>
+        <v/>
+      </c>
+      <c r="Z17" s="14">
+        <f>Y17/C17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="10">
+        <f>C17*AA17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="10">
+        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-H17+AB17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="15">
+        <f>AC17-Y17</f>
+        <v/>
+      </c>
+      <c r="AE17" s="14">
+        <f>AD17/C17</f>
+        <v/>
+      </c>
+      <c r="AF17" s="16">
+        <f>AD17/H17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="10">
+        <f>(K17+M17+R17+T17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+U17+W17-AA17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E18" s="10">
+        <f>C18*(1-D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>431.05</v>
+      </c>
+      <c r="G18" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>F18+G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J18" s="10">
+        <f>C18*I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L18" s="12">
+        <f>C18*$C$8</f>
+        <v/>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" s="10">
+        <f>C18*$C$4</f>
+        <v/>
+      </c>
+      <c r="O18" s="10">
+        <f>E18*$C$3</f>
+        <v/>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q18" s="8">
+        <f>K18</f>
+        <v/>
+      </c>
+      <c r="R18" s="10">
+        <f>Q18*(1-P18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="T18" s="10">
+        <f>$C$6*$C$7*S18</f>
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V18" s="10">
+        <f>C18*U18</f>
+        <v/>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X18" s="10">
+        <f>C18*W18</f>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f>V18+X18</f>
+        <v/>
+      </c>
+      <c r="Z18" s="14">
+        <f>Y18/C18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="10">
+        <f>C18*AA18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="10">
+        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-H18+AB18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="15">
+        <f>AC18-Y18</f>
+        <v/>
+      </c>
+      <c r="AE18" s="14">
+        <f>AD18/C18</f>
+        <v/>
+      </c>
+      <c r="AF18" s="16">
+        <f>AD18/H18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="10">
+        <f>(K18+M18+R18+T18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+U18+W18-AA18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="10">
+        <f>C19*(1-D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="G19" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H19" s="12">
+        <f>F19+G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J19" s="10">
+        <f>C19*I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L19" s="12">
+        <f>C19*$C$8</f>
+        <v/>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" s="10">
+        <f>C19*$C$4</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>E19*$C$3</f>
+        <v/>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q19" s="8">
+        <f>K19</f>
+        <v/>
+      </c>
+      <c r="R19" s="10">
+        <f>Q19*(1-P19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T19" s="10">
+        <f>$C$6*$C$7*S19</f>
+        <v/>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V19" s="10">
+        <f>C19*U19</f>
+        <v/>
+      </c>
+      <c r="W19" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X19" s="10">
+        <f>C19*W19</f>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f>V19+X19</f>
+        <v/>
+      </c>
+      <c r="Z19" s="14">
+        <f>Y19/C19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="10">
+        <f>C19*AA19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="10">
+        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-H19+AB19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="15">
+        <f>AC19-Y19</f>
+        <v/>
+      </c>
+      <c r="AE19" s="14">
+        <f>AD19/C19</f>
+        <v/>
+      </c>
+      <c r="AF19" s="16">
+        <f>AD19/H19</f>
+        <v/>
+      </c>
+      <c r="AG19" s="10">
+        <f>(K19+M19+R19+T19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+U19+W19-AA19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E20" s="10">
+        <f>C20*(1-D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>899.78</v>
+      </c>
+      <c r="G20" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H20" s="12">
+        <f>F20+G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J20" s="10">
+        <f>C20*I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="L20" s="12">
+        <f>C20*$C$8</f>
+        <v/>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N20" s="10">
+        <f>C20*$C$4</f>
+        <v/>
+      </c>
+      <c r="O20" s="10">
+        <f>E20*$C$3</f>
+        <v/>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q20" s="8">
+        <f>K20</f>
+        <v/>
+      </c>
+      <c r="R20" s="10">
+        <f>Q20*(1-P20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T20" s="10">
+        <f>$C$6*$C$7*S20</f>
+        <v/>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V20" s="10">
+        <f>C20*U20</f>
+        <v/>
+      </c>
+      <c r="W20" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X20" s="10">
+        <f>C20*W20</f>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f>V20+X20</f>
+        <v/>
+      </c>
+      <c r="Z20" s="14">
+        <f>Y20/C20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="10">
+        <f>C20*AA20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="10">
+        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-H20+AB20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="15">
+        <f>AC20-Y20</f>
+        <v/>
+      </c>
+      <c r="AE20" s="14">
+        <f>AD20/C20</f>
+        <v/>
+      </c>
+      <c r="AF20" s="16">
+        <f>AD20/H20</f>
+        <v/>
+      </c>
+      <c r="AG20" s="10">
+        <f>(K20+M20+R20+T20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+U20+W20-AA20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E21" s="10">
+        <f>C21*(1-D21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>646.83</v>
+      </c>
+      <c r="G21" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H21" s="12">
+        <f>F21+G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J21" s="10">
+        <f>C21*I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="L21" s="12">
+        <f>C21*$C$8</f>
+        <v/>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N21" s="10">
+        <f>C21*$C$4</f>
+        <v/>
+      </c>
+      <c r="O21" s="10">
+        <f>E21*$C$3</f>
+        <v/>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q21" s="8">
+        <f>K21</f>
+        <v/>
+      </c>
+      <c r="R21" s="10">
+        <f>Q21*(1-P21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="20" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T21" s="10">
+        <f>$C$6*$C$7*S21</f>
+        <v/>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V21" s="10">
+        <f>C21*U21</f>
+        <v/>
+      </c>
+      <c r="W21" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X21" s="10">
+        <f>C21*W21</f>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f>V21+X21</f>
+        <v/>
+      </c>
+      <c r="Z21" s="14">
+        <f>Y21/C21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="10">
+        <f>C21*AA21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="10">
+        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-H21+AB21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="15">
+        <f>AC21-Y21</f>
+        <v/>
+      </c>
+      <c r="AE21" s="14">
+        <f>AD21/C21</f>
+        <v/>
+      </c>
+      <c r="AF21" s="16">
+        <f>AD21/H21</f>
+        <v/>
+      </c>
+      <c r="AG21" s="10">
+        <f>(K21+M21+R21+T21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+U21+W21-AA21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E22" s="10">
+        <f>C22*(1-D22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>735.34</v>
+      </c>
+      <c r="G22" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>F22+G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J22" s="10">
+        <f>C22*I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L22" s="12">
+        <f>C22*$C$8</f>
+        <v/>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N22" s="10">
+        <f>C22*$C$4</f>
+        <v/>
+      </c>
+      <c r="O22" s="10">
+        <f>E22*$C$3</f>
+        <v/>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q22" s="8">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="R22" s="10">
+        <f>Q22*(1-P22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="20" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="T22" s="10">
+        <f>$C$6*$C$7*S22</f>
+        <v/>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V22" s="10">
+        <f>C22*U22</f>
+        <v/>
+      </c>
+      <c r="W22" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X22" s="10">
+        <f>C22*W22</f>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f>V22+X22</f>
+        <v/>
+      </c>
+      <c r="Z22" s="14">
+        <f>Y22/C22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="10">
+        <f>C22*AA22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="10">
+        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-H22+AB22</f>
+        <v/>
+      </c>
+      <c r="AD22" s="15">
+        <f>AC22-Y22</f>
+        <v/>
+      </c>
+      <c r="AE22" s="14">
+        <f>AD22/C22</f>
+        <v/>
+      </c>
+      <c r="AF22" s="16">
+        <f>AD22/H22</f>
+        <v/>
+      </c>
+      <c r="AG22" s="10">
+        <f>(K22+M22+R22+T22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+U22+W22-AA22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="10">
+        <f>C23*(1-D23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>853</v>
+      </c>
+      <c r="G23" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H23" s="12">
+        <f>F23+G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J23" s="10">
+        <f>C23*I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="L23" s="12">
+        <f>C23*$C$8</f>
+        <v/>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N23" s="10">
+        <f>C23*$C$4</f>
+        <v/>
+      </c>
+      <c r="O23" s="10">
+        <f>E23*$C$3</f>
+        <v/>
+      </c>
+      <c r="P23" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q23" s="8">
+        <f>K23</f>
+        <v/>
+      </c>
+      <c r="R23" s="10">
+        <f>Q23*(1-P23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T23" s="10">
+        <f>$C$6*$C$7*S23</f>
+        <v/>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V23" s="10">
+        <f>C23*U23</f>
+        <v/>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X23" s="10">
+        <f>C23*W23</f>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f>V23+X23</f>
+        <v/>
+      </c>
+      <c r="Z23" s="14">
+        <f>Y23/C23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="10">
+        <f>C23*AA23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="10">
+        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-H23+AB23</f>
+        <v/>
+      </c>
+      <c r="AD23" s="15">
+        <f>AC23-Y23</f>
+        <v/>
+      </c>
+      <c r="AE23" s="14">
+        <f>AD23/C23</f>
+        <v/>
+      </c>
+      <c r="AF23" s="16">
+        <f>AD23/H23</f>
+        <v/>
+      </c>
+      <c r="AG23" s="10">
+        <f>(K23+M23+R23+T23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+U23+W23-AA23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E24" s="10">
+        <f>C24*(1-D24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="G24" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H24" s="12">
+        <f>F24+G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J24" s="10">
+        <f>C24*I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="L24" s="12">
+        <f>C24*$C$8</f>
+        <v/>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="N24" s="10">
+        <f>C24*$C$4</f>
+        <v/>
+      </c>
+      <c r="O24" s="10">
+        <f>E24*$C$3</f>
+        <v/>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q24" s="8">
+        <f>K24</f>
+        <v/>
+      </c>
+      <c r="R24" s="10">
+        <f>Q24*(1-P24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T24" s="10">
+        <f>$C$6*$C$7*S24</f>
+        <v/>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V24" s="10">
+        <f>C24*U24</f>
+        <v/>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X24" s="10">
+        <f>C24*W24</f>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f>V24+X24</f>
+        <v/>
+      </c>
+      <c r="Z24" s="14">
+        <f>Y24/C24</f>
+        <v/>
+      </c>
+      <c r="AA24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="10">
+        <f>C24*AA24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="10">
+        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-H24+AB24</f>
+        <v/>
+      </c>
+      <c r="AD24" s="15">
+        <f>AC24-Y24</f>
+        <v/>
+      </c>
+      <c r="AE24" s="14">
+        <f>AD24/C24</f>
+        <v/>
+      </c>
+      <c r="AF24" s="16">
+        <f>AD24/H24</f>
+        <v/>
+      </c>
+      <c r="AG24" s="10">
+        <f>(K24+M24+R24+T24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+U24+W24-AA24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Только FBO. Жёлтые ячейки — вход (цена, СПП %, себест., комиссия, логистика, наценка за нелокальность, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Цена с СПП = Цена×(1−СПП%); налог считается от цены с СПП. Объём — в литрах из габаритов карточки (если выгружены, иначе объёмный вес). Реклама по актуальным форматам Ozon: Оплата за клик % (CPC) и Вывод в топ % (CPO). Соинвест % — из кабинета (Цены → Баллы за скидки), баллы прибавляются к марже. Меняешь цену в колонке B → маржа и ROI пересчитываются.</t>
         </is>
       </c>
+      <c r="B28" s="17" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A11:AG24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -66,7 +66,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +145,7 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -505,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="2"/>
@@ -530,6 +536,7 @@
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
@@ -600,6 +607,26 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Кроссдок: отгрузка ₽/л</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Кроссдок: перевозка ₽/л (средн. 26 скл.)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>4.423</v>
+      </c>
+    </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -766,6 +793,11 @@
           <t>Цена безубыт.</t>
         </is>
       </c>
+      <c r="AH11" s="6" t="inlineStr">
+        <is>
+          <t>Кроссдок ср., ₽/ед</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -872,7 +904,7 @@
         <v/>
       </c>
       <c r="AC12" s="10">
-        <f>C12-J12-K12-L12-M12-N12-O12-R12-T12-H12+AB12</f>
+        <f>C12-J12-K12-L12-M12-N12-O12-R12-T12-H12+AB12-AH12</f>
         <v/>
       </c>
       <c r="AD12" s="15">
@@ -888,7 +920,11 @@
         <v/>
       </c>
       <c r="AG12" s="10">
-        <f>(K12+M12+R12+T12+H12)/(1-(I12+$C$4+(1-D12)*$C$3+$C$8+U12+W12-AA12))</f>
+        <f>(K12+M12+R12+T12+H12+AH12)/(1-(I12+$C$4+(1-D12)*$C$3+$C$8+U12+W12-AA12))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="12">
+        <f>S12*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -997,7 +1033,7 @@
         <v/>
       </c>
       <c r="AC13" s="10">
-        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-H13+AB13</f>
+        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-H13+AB13-AH13</f>
         <v/>
       </c>
       <c r="AD13" s="15">
@@ -1013,7 +1049,11 @@
         <v/>
       </c>
       <c r="AG13" s="10">
-        <f>(K13+M13+R13+T13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+U13+W13-AA13))</f>
+        <f>(K13+M13+R13+T13+H13+AH13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+U13+W13-AA13))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="12">
+        <f>S13*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1122,7 +1162,7 @@
         <v/>
       </c>
       <c r="AC14" s="10">
-        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-H14+AB14</f>
+        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-H14+AB14-AH14</f>
         <v/>
       </c>
       <c r="AD14" s="15">
@@ -1138,7 +1178,11 @@
         <v/>
       </c>
       <c r="AG14" s="10">
-        <f>(K14+M14+R14+T14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+U14+W14-AA14))</f>
+        <f>(K14+M14+R14+T14+H14+AH14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+U14+W14-AA14))</f>
+        <v/>
+      </c>
+      <c r="AH14" s="12">
+        <f>S14*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1149,7 +1193,7 @@
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>2500</v>
+        <v>1025</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0.45</v>
@@ -1242,7 +1286,7 @@
         <v/>
       </c>
       <c r="AC15" s="10">
-        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-H15+AB15</f>
+        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-H15+AB15-AH15</f>
         <v/>
       </c>
       <c r="AD15" s="15">
@@ -1258,7 +1302,11 @@
         <v/>
       </c>
       <c r="AG15" s="10">
-        <f>(K15+M15+R15+T15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+U15+W15-AA15))</f>
+        <f>(K15+M15+R15+T15+H15+AH15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+U15+W15-AA15))</f>
+        <v/>
+      </c>
+      <c r="AH15" s="12">
+        <f>S15*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1269,7 +1317,7 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>2500</v>
+        <v>1710</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0.45</v>
@@ -1362,7 +1410,7 @@
         <v/>
       </c>
       <c r="AC16" s="10">
-        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-H16+AB16</f>
+        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-H16+AB16-AH16</f>
         <v/>
       </c>
       <c r="AD16" s="15">
@@ -1378,7 +1426,11 @@
         <v/>
       </c>
       <c r="AG16" s="10">
-        <f>(K16+M16+R16+T16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+U16+W16-AA16))</f>
+        <f>(K16+M16+R16+T16+H16+AH16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+U16+W16-AA16))</f>
+        <v/>
+      </c>
+      <c r="AH16" s="12">
+        <f>S16*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1389,7 +1441,7 @@
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2500</v>
+        <v>1850</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0.45</v>
@@ -1482,7 +1534,7 @@
         <v/>
       </c>
       <c r="AC17" s="10">
-        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-H17+AB17</f>
+        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-H17+AB17-AH17</f>
         <v/>
       </c>
       <c r="AD17" s="15">
@@ -1498,7 +1550,11 @@
         <v/>
       </c>
       <c r="AG17" s="10">
-        <f>(K17+M17+R17+T17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+U17+W17-AA17))</f>
+        <f>(K17+M17+R17+T17+H17+AH17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+U17+W17-AA17))</f>
+        <v/>
+      </c>
+      <c r="AH17" s="12">
+        <f>S17*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1509,7 +1565,7 @@
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>2500</v>
+        <v>1950</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0.45</v>
@@ -1602,7 +1658,7 @@
         <v/>
       </c>
       <c r="AC18" s="10">
-        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-H18+AB18</f>
+        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-H18+AB18-AH18</f>
         <v/>
       </c>
       <c r="AD18" s="15">
@@ -1618,7 +1674,11 @@
         <v/>
       </c>
       <c r="AG18" s="10">
-        <f>(K18+M18+R18+T18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+U18+W18-AA18))</f>
+        <f>(K18+M18+R18+T18+H18+AH18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+U18+W18-AA18))</f>
+        <v/>
+      </c>
+      <c r="AH18" s="12">
+        <f>S18*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1629,7 +1689,7 @@
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2500</v>
+        <v>1550</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0.45</v>
@@ -1722,7 +1782,7 @@
         <v/>
       </c>
       <c r="AC19" s="10">
-        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-H19+AB19</f>
+        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-H19+AB19-AH19</f>
         <v/>
       </c>
       <c r="AD19" s="15">
@@ -1738,7 +1798,11 @@
         <v/>
       </c>
       <c r="AG19" s="10">
-        <f>(K19+M19+R19+T19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+U19+W19-AA19))</f>
+        <f>(K19+M19+R19+T19+H19+AH19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+U19+W19-AA19))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="12">
+        <f>S19*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1749,7 +1813,7 @@
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2500</v>
+        <v>3550</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0.45</v>
@@ -1842,7 +1906,7 @@
         <v/>
       </c>
       <c r="AC20" s="10">
-        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-H20+AB20</f>
+        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-H20+AB20-AH20</f>
         <v/>
       </c>
       <c r="AD20" s="15">
@@ -1858,7 +1922,11 @@
         <v/>
       </c>
       <c r="AG20" s="10">
-        <f>(K20+M20+R20+T20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+U20+W20-AA20))</f>
+        <f>(K20+M20+R20+T20+H20+AH20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+U20+W20-AA20))</f>
+        <v/>
+      </c>
+      <c r="AH20" s="12">
+        <f>S20*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1869,7 +1937,7 @@
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2500</v>
+        <v>2650</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0.45</v>
@@ -1962,7 +2030,7 @@
         <v/>
       </c>
       <c r="AC21" s="10">
-        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-H21+AB21</f>
+        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-H21+AB21-AH21</f>
         <v/>
       </c>
       <c r="AD21" s="15">
@@ -1978,7 +2046,11 @@
         <v/>
       </c>
       <c r="AG21" s="10">
-        <f>(K21+M21+R21+T21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+U21+W21-AA21))</f>
+        <f>(K21+M21+R21+T21+H21+AH21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+U21+W21-AA21))</f>
+        <v/>
+      </c>
+      <c r="AH21" s="12">
+        <f>S21*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -1989,7 +2061,7 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0.45</v>
@@ -2082,7 +2154,7 @@
         <v/>
       </c>
       <c r="AC22" s="10">
-        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-H22+AB22</f>
+        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-H22+AB22-AH22</f>
         <v/>
       </c>
       <c r="AD22" s="15">
@@ -2098,7 +2170,11 @@
         <v/>
       </c>
       <c r="AG22" s="10">
-        <f>(K22+M22+R22+T22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+U22+W22-AA22))</f>
+        <f>(K22+M22+R22+T22+H22+AH22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+U22+W22-AA22))</f>
+        <v/>
+      </c>
+      <c r="AH22" s="12">
+        <f>S22*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -2109,7 +2185,7 @@
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0.45</v>
@@ -2202,7 +2278,7 @@
         <v/>
       </c>
       <c r="AC23" s="10">
-        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-H23+AB23</f>
+        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-H23+AB23-AH23</f>
         <v/>
       </c>
       <c r="AD23" s="15">
@@ -2218,7 +2294,11 @@
         <v/>
       </c>
       <c r="AG23" s="10">
-        <f>(K23+M23+R23+T23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+U23+W23-AA23))</f>
+        <f>(K23+M23+R23+T23+H23+AH23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+U23+W23-AA23))</f>
+        <v/>
+      </c>
+      <c r="AH23" s="12">
+        <f>S23*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>
@@ -2229,7 +2309,7 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>2500</v>
+        <v>2280</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0.45</v>
@@ -2322,7 +2402,7 @@
         <v/>
       </c>
       <c r="AC24" s="10">
-        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-H24+AB24</f>
+        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-H24+AB24-AH24</f>
         <v/>
       </c>
       <c r="AD24" s="15">
@@ -2338,7 +2418,11 @@
         <v/>
       </c>
       <c r="AG24" s="10">
-        <f>(K24+M24+R24+T24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+U24+W24-AA24))</f>
+        <f>(K24+M24+R24+T24+H24+AH24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+U24+W24-AA24))</f>
+        <v/>
+      </c>
+      <c r="AH24" s="12">
+        <f>S24*($C$9+$C$10)</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -610,11 +610,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Кроссдок: отгрузка ₽/л</t>
+          <t>Кроссдок: обработка (склады/СЦ) ₽/л</t>
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>2.45</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Юнитка Ozon (live)'!$A$11:$AG$24</definedName>
-  </definedNames>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,41 +28,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="204"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="6">
@@ -75,22 +52,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF305496"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,24 +81,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,23 +108,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -511,41 +485,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:AH27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="20"/>
-    <col width="13" customWidth="1" min="21" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col hidden="1" width="11" customWidth="1" min="27" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ — меняй жёлтые ячейки, всё пересчитается</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,7 +597,7 @@
           <t>Кроссдок: обработка (склады/СЦ) ₽/л</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="5" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -623,1825 +607,1840 @@
           <t>Кроссдок: перевозка ₽/л (средн. 26 скл.)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="5" t="n">
         <v>4.423</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Цена конкурентов с СПП</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>СПП, %</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Цена с СПП</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Себест.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Фулфилмент</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>База затрат</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Комиссия %</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Комиссия ₽</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>Наценка нелок., ₽</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>Доставка до ПВЗ</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>Эквайринг</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>Налог</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>Выкуп %</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Обр.лог база</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>Обр.лог</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>Объём, л</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>Хранение</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Кроссдок ср., ₽/ед</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик, %</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="W12" s="6" t="inlineStr">
         <is>
           <t>Оплата за клик ₽</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="X12" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ, %</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>Вывод в топ ₽</t>
         </is>
       </c>
-      <c r="Y11" s="6" t="inlineStr">
+      <c r="Z12" s="6" t="inlineStr">
         <is>
           <t>Реклама всего ₽</t>
         </is>
       </c>
-      <c r="Z11" s="6" t="inlineStr">
+      <c r="AA12" s="6" t="inlineStr">
         <is>
           <t>ДРР %</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="inlineStr">
+      <c r="AB12" s="6" t="inlineStr">
         <is>
           <t>Соинвест, %</t>
         </is>
       </c>
-      <c r="AB11" s="6" t="inlineStr">
+      <c r="AC12" s="6" t="inlineStr">
         <is>
           <t>Соинвест ₽</t>
         </is>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AD12" s="6" t="inlineStr">
         <is>
           <t>Маржа до рекл.</t>
         </is>
       </c>
-      <c r="AD11" s="6" t="inlineStr">
+      <c r="AE12" s="6" t="inlineStr">
         <is>
           <t>Маржа/шт</t>
         </is>
       </c>
-      <c r="AE11" s="6" t="inlineStr">
+      <c r="AF12" s="6" t="inlineStr">
         <is>
           <t>Маржа % цены</t>
         </is>
       </c>
-      <c r="AF11" s="6" t="inlineStr">
+      <c r="AG12" s="6" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
-      </c>
-      <c r="AH11" s="6" t="inlineStr">
-        <is>
-          <t>Кроссдок ср., ₽/ед</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1250-1300</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>2750</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E12" s="10">
-        <f>C12*(1-D12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>663.86</v>
-      </c>
-      <c r="G12" s="12">
-        <f>$C$5</f>
-        <v/>
-      </c>
-      <c r="H12" s="12">
-        <f>F12+G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J12" s="10">
-        <f>C12*I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="L12" s="12">
-        <f>C12*$C$8</f>
-        <v/>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="N12" s="10">
-        <f>C12*$C$4</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>E12*$C$3</f>
-        <v/>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q12" s="8">
-        <f>K12</f>
-        <v/>
-      </c>
-      <c r="R12" s="10">
-        <f>Q12*(1-P12)</f>
-        <v/>
-      </c>
-      <c r="S12" s="13" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="T12" s="10">
-        <f>$C$6*$C$7*S12</f>
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V12" s="10">
-        <f>C12*U12</f>
-        <v/>
-      </c>
-      <c r="W12" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X12" s="10">
-        <f>C12*W12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="10">
-        <f>V12+X12</f>
-        <v/>
-      </c>
-      <c r="Z12" s="14">
-        <f>Y12/C12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="10">
-        <f>C12*AA12</f>
-        <v/>
-      </c>
-      <c r="AC12" s="10">
-        <f>C12-J12-K12-L12-M12-N12-O12-R12-T12-H12+AB12-AH12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="15">
-        <f>AC12-Y12</f>
-        <v/>
-      </c>
-      <c r="AE12" s="14">
-        <f>AD12/C12</f>
-        <v/>
-      </c>
-      <c r="AF12" s="16">
-        <f>AD12/H12</f>
-        <v/>
-      </c>
-      <c r="AG12" s="10">
-        <f>(K12+M12+R12+T12+H12+AH12)/(1-(I12+$C$4+(1-D12)*$C$3+$C$8+U12+W12-AA12))</f>
-        <v/>
-      </c>
-      <c r="AH12" s="12">
-        <f>S12*($C$9+$C$10)</f>
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>1076-1244</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>2080</v>
-      </c>
-      <c r="D13" s="9" t="n">
+          <t>Celimax Dual Barrier Creamy Toner</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>1250-1300</t>
+        </is>
+      </c>
+      <c r="C13" s="9">
+        <f>(1.25*H13+K13+M13+R13+T13+U13)/(1-I13-$C$8-$C$4-(1-D13)*$C$3+AB13-V13-X13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <f>C13*(1-D13)</f>
         <v/>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>463.19</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="12" t="n">
+        <v>663.86</v>
+      </c>
+      <c r="G13" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>F13+G13</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="11">
         <f>C13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="L13" s="12">
+      <c r="K13" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L13" s="11">
         <f>C13*$C$8</f>
         <v/>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="11">
         <f>C13*$C$4</f>
         <v/>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="11">
         <f>E13*$C$3</f>
         <v/>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13" s="14">
         <f>K13</f>
         <v/>
       </c>
-      <c r="R13" s="10">
+      <c r="R13" s="11">
         <f>Q13*(1-P13)</f>
         <v/>
       </c>
-      <c r="S13" s="13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T13" s="10">
+      <c r="S13" s="15" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="T13" s="11">
         <f>$C$6*$C$7*S13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="13">
+        <f>S13*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V13" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V13" s="10">
-        <f>C13*U13</f>
-        <v/>
-      </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="11">
+        <f>C13*V13</f>
+        <v/>
+      </c>
+      <c r="X13" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X13" s="10">
-        <f>C13*W13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="10">
-        <f>V13+X13</f>
-        <v/>
-      </c>
-      <c r="Z13" s="14">
-        <f>Y13/C13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="9" t="n">
+      <c r="Y13" s="11">
+        <f>C13*X13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="11">
+        <f>W13+Y13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="16">
+        <f>Z13/C13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB13" s="10">
-        <f>C13*AA13</f>
-        <v/>
-      </c>
-      <c r="AC13" s="10">
-        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-H13+AB13-AH13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="15">
-        <f>AC13-Y13</f>
-        <v/>
-      </c>
-      <c r="AE13" s="14">
-        <f>AD13/C13</f>
+      <c r="AC13" s="11">
+        <f>C13*AB13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="11">
+        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-U13-H13+AC13</f>
+        <v/>
+      </c>
+      <c r="AE13" s="17">
+        <f>AD13-Z13</f>
         <v/>
       </c>
       <c r="AF13" s="16">
-        <f>AD13/H13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="10">
-        <f>(K13+M13+R13+T13+H13+AH13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+U13+W13-AA13))</f>
-        <v/>
-      </c>
-      <c r="AH13" s="12">
-        <f>S13*($C$9+$C$10)</f>
+        <f>AE13/C13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="18">
+        <f>AE13/H13</f>
+        <v/>
+      </c>
+      <c r="AH13" s="11">
+        <f>(K13+M13+R13+T13+U13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+V13+X13-AB13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>483 (много подделок)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>1660</v>
-      </c>
-      <c r="D14" s="9" t="n">
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>1076-1244</t>
+        </is>
+      </c>
+      <c r="C14" s="9">
+        <f>(1.25*H14+K14+M14+R14+T14+U14)/(1-I14-$C$8-$C$4-(1-D14)*$C$3+AB14-V14-X14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="11">
         <f>C14*(1-D14)</f>
         <v/>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>347.76</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="F14" s="12" t="n">
+        <v>463.19</v>
+      </c>
+      <c r="G14" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>F14+G14</f>
         <v/>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="11">
         <f>C14*I14</f>
         <v/>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="L14" s="12">
+      <c r="K14" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="L14" s="11">
         <f>C14*$C$8</f>
         <v/>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="11">
         <f>C14*$C$4</f>
         <v/>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="11">
         <f>E14*$C$3</f>
         <v/>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="14">
         <f>K14</f>
         <v/>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="11">
         <f>Q14*(1-P14)</f>
         <v/>
       </c>
-      <c r="S14" s="13" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="T14" s="10">
+      <c r="S14" s="15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" s="11">
         <f>$C$6*$C$7*S14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="13">
+        <f>S14*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V14" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V14" s="10">
-        <f>C14*U14</f>
-        <v/>
-      </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="11">
+        <f>C14*V14</f>
+        <v/>
+      </c>
+      <c r="X14" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X14" s="10">
-        <f>C14*W14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="10">
-        <f>V14+X14</f>
-        <v/>
-      </c>
-      <c r="Z14" s="14">
-        <f>Y14/C14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="9" t="n">
+      <c r="Y14" s="11">
+        <f>C14*X14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="11">
+        <f>W14+Y14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="16">
+        <f>Z14/C14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" s="10">
-        <f>C14*AA14</f>
-        <v/>
-      </c>
-      <c r="AC14" s="10">
-        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-H14+AB14-AH14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="15">
-        <f>AC14-Y14</f>
-        <v/>
-      </c>
-      <c r="AE14" s="14">
-        <f>AD14/C14</f>
+      <c r="AC14" s="11">
+        <f>C14*AB14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="11">
+        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-U14-H14+AC14</f>
+        <v/>
+      </c>
+      <c r="AE14" s="17">
+        <f>AD14-Z14</f>
         <v/>
       </c>
       <c r="AF14" s="16">
-        <f>AD14/H14</f>
-        <v/>
-      </c>
-      <c r="AG14" s="10">
-        <f>(K14+M14+R14+T14+H14+AH14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+U14+W14-AA14))</f>
-        <v/>
-      </c>
-      <c r="AH14" s="12">
-        <f>S14*($C$9+$C$10)</f>
+        <f>AE14/C14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="18">
+        <f>AE14/H14</f>
+        <v/>
+      </c>
+      <c r="AH14" s="11">
+        <f>(K14+M14+R14+T14+U14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+V14+X14-AB14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>1025</v>
-      </c>
-      <c r="D15" s="9" t="n">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>483 (много подделок)</t>
+        </is>
+      </c>
+      <c r="C15" s="9">
+        <f>(1.25*H15+K15+M15+R15+T15+U15)/(1-I15-$C$8-$C$4-(1-D15)*$C$3+AB15-V15-X15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="11">
         <f>C15*(1-D15)</f>
         <v/>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="G15" s="12">
+      <c r="F15" s="12" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="G15" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>F15+G15</f>
         <v/>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="11">
         <f>C15*I15</f>
         <v/>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="K15" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="11">
         <f>C15*$C$8</f>
         <v/>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="11">
         <f>C15*$C$4</f>
         <v/>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="11">
         <f>E15*$C$3</f>
         <v/>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="14">
         <f>K15</f>
         <v/>
       </c>
-      <c r="R15" s="10">
+      <c r="R15" s="11">
         <f>Q15*(1-P15)</f>
         <v/>
       </c>
-      <c r="S15" s="20" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="T15" s="10">
+      <c r="S15" s="15" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="T15" s="11">
         <f>$C$6*$C$7*S15</f>
         <v/>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="13">
+        <f>S15*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V15" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V15" s="10">
-        <f>C15*U15</f>
-        <v/>
-      </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="11">
+        <f>C15*V15</f>
+        <v/>
+      </c>
+      <c r="X15" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X15" s="10">
-        <f>C15*W15</f>
-        <v/>
-      </c>
-      <c r="Y15" s="10">
-        <f>V15+X15</f>
-        <v/>
-      </c>
-      <c r="Z15" s="14">
-        <f>Y15/C15</f>
-        <v/>
-      </c>
-      <c r="AA15" s="9" t="n">
+      <c r="Y15" s="11">
+        <f>C15*X15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="11">
+        <f>W15+Y15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="16">
+        <f>Z15/C15</f>
+        <v/>
+      </c>
+      <c r="AB15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB15" s="10">
-        <f>C15*AA15</f>
-        <v/>
-      </c>
-      <c r="AC15" s="10">
-        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-H15+AB15-AH15</f>
-        <v/>
-      </c>
-      <c r="AD15" s="15">
-        <f>AC15-Y15</f>
-        <v/>
-      </c>
-      <c r="AE15" s="14">
-        <f>AD15/C15</f>
+      <c r="AC15" s="11">
+        <f>C15*AB15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="11">
+        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-U15-H15+AC15</f>
+        <v/>
+      </c>
+      <c r="AE15" s="17">
+        <f>AD15-Z15</f>
         <v/>
       </c>
       <c r="AF15" s="16">
-        <f>AD15/H15</f>
-        <v/>
-      </c>
-      <c r="AG15" s="10">
-        <f>(K15+M15+R15+T15+H15+AH15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+U15+W15-AA15))</f>
-        <v/>
-      </c>
-      <c r="AH15" s="12">
-        <f>S15*($C$9+$C$10)</f>
+        <f>AE15/C15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="18">
+        <f>AE15/H15</f>
+        <v/>
+      </c>
+      <c r="AH15" s="11">
+        <f>(K15+M15+R15+T15+U15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+V15+X15-AB15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>1710</v>
-      </c>
-      <c r="D16" s="9" t="n">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9">
+        <f>(1.25*H16+K16+M16+R16+T16+U16)/(1-I16-$C$8-$C$4-(1-D16)*$C$3+AB16-V16-X16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="11">
         <f>C16*(1-D16)</f>
         <v/>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>361.03</v>
-      </c>
-      <c r="G16" s="12">
+      <c r="F16" s="12" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="G16" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>F16+G16</f>
         <v/>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="11">
         <f>C16*I16</f>
         <v/>
       </c>
-      <c r="K16" s="8" t="n">
+      <c r="K16" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <f>C16*$C$8</f>
         <v/>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="11">
         <f>C16*$C$4</f>
         <v/>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="11">
         <f>E16*$C$3</f>
         <v/>
       </c>
-      <c r="P16" s="9" t="n">
+      <c r="P16" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q16" s="14">
         <f>K16</f>
         <v/>
       </c>
-      <c r="R16" s="10">
+      <c r="R16" s="11">
         <f>Q16*(1-P16)</f>
         <v/>
       </c>
-      <c r="S16" s="20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="T16" s="10">
+      <c r="S16" s="15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T16" s="11">
         <f>$C$6*$C$7*S16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n">
+      <c r="U16" s="13">
+        <f>S16*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V16" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V16" s="10">
-        <f>C16*U16</f>
-        <v/>
-      </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="11">
+        <f>C16*V16</f>
+        <v/>
+      </c>
+      <c r="X16" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X16" s="10">
-        <f>C16*W16</f>
-        <v/>
-      </c>
-      <c r="Y16" s="10">
-        <f>V16+X16</f>
-        <v/>
-      </c>
-      <c r="Z16" s="14">
-        <f>Y16/C16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n">
+      <c r="Y16" s="11">
+        <f>C16*X16</f>
+        <v/>
+      </c>
+      <c r="Z16" s="11">
+        <f>W16+Y16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="16">
+        <f>Z16/C16</f>
+        <v/>
+      </c>
+      <c r="AB16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="10">
-        <f>C16*AA16</f>
-        <v/>
-      </c>
-      <c r="AC16" s="10">
-        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-H16+AB16-AH16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="15">
-        <f>AC16-Y16</f>
-        <v/>
-      </c>
-      <c r="AE16" s="14">
-        <f>AD16/C16</f>
+      <c r="AC16" s="11">
+        <f>C16*AB16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="11">
+        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-U16-H16+AC16</f>
+        <v/>
+      </c>
+      <c r="AE16" s="17">
+        <f>AD16-Z16</f>
         <v/>
       </c>
       <c r="AF16" s="16">
-        <f>AD16/H16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="10">
-        <f>(K16+M16+R16+T16+H16+AH16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+U16+W16-AA16))</f>
-        <v/>
-      </c>
-      <c r="AH16" s="12">
-        <f>S16*($C$9+$C$10)</f>
+        <f>AE16/C16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="18">
+        <f>AE16/H16</f>
+        <v/>
+      </c>
+      <c r="AH16" s="11">
+        <f>(K16+M16+R16+T16+U16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+V16+X16-AB16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D17" s="9" t="n">
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="9">
+        <f>(1.25*H17+K17+M17+R17+T17+U17)/(1-I17-$C$8-$C$4-(1-D17)*$C$3+AB17-V17-X17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="11">
         <f>C17*(1-D17)</f>
         <v/>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>396.72</v>
-      </c>
-      <c r="G17" s="12">
+      <c r="F17" s="12" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="G17" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <f>F17+G17</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="11">
         <f>C17*I17</f>
         <v/>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="L17" s="12">
+      <c r="K17" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" s="11">
         <f>C17*$C$8</f>
         <v/>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="11">
         <f>C17*$C$4</f>
         <v/>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="11">
         <f>E17*$C$3</f>
         <v/>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="P17" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17" s="14">
         <f>K17</f>
         <v/>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="11">
         <f>Q17*(1-P17)</f>
         <v/>
       </c>
-      <c r="S17" s="20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T17" s="10">
+      <c r="S17" s="15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T17" s="11">
         <f>$C$6*$C$7*S17</f>
         <v/>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="13">
+        <f>S17*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V17" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V17" s="10">
-        <f>C17*U17</f>
-        <v/>
-      </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="11">
+        <f>C17*V17</f>
+        <v/>
+      </c>
+      <c r="X17" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X17" s="10">
-        <f>C17*W17</f>
-        <v/>
-      </c>
-      <c r="Y17" s="10">
-        <f>V17+X17</f>
-        <v/>
-      </c>
-      <c r="Z17" s="14">
-        <f>Y17/C17</f>
-        <v/>
-      </c>
-      <c r="AA17" s="9" t="n">
+      <c r="Y17" s="11">
+        <f>C17*X17</f>
+        <v/>
+      </c>
+      <c r="Z17" s="11">
+        <f>W17+Y17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="16">
+        <f>Z17/C17</f>
+        <v/>
+      </c>
+      <c r="AB17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="10">
-        <f>C17*AA17</f>
-        <v/>
-      </c>
-      <c r="AC17" s="10">
-        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-H17+AB17-AH17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="15">
-        <f>AC17-Y17</f>
-        <v/>
-      </c>
-      <c r="AE17" s="14">
-        <f>AD17/C17</f>
+      <c r="AC17" s="11">
+        <f>C17*AB17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="11">
+        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-U17-H17+AC17</f>
+        <v/>
+      </c>
+      <c r="AE17" s="17">
+        <f>AD17-Z17</f>
         <v/>
       </c>
       <c r="AF17" s="16">
-        <f>AD17/H17</f>
-        <v/>
-      </c>
-      <c r="AG17" s="10">
-        <f>(K17+M17+R17+T17+H17+AH17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+U17+W17-AA17))</f>
-        <v/>
-      </c>
-      <c r="AH17" s="12">
-        <f>S17*($C$9+$C$10)</f>
+        <f>AE17/C17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="18">
+        <f>AE17/H17</f>
+        <v/>
+      </c>
+      <c r="AH17" s="11">
+        <f>(K17+M17+R17+T17+U17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+V17+X17-AB17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D18" s="9" t="n">
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="9">
+        <f>(1.25*H18+K18+M18+R18+T18+U18)/(1-I18-$C$8-$C$4-(1-D18)*$C$3+AB18-V18-X18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="11">
         <f>C18*(1-D18)</f>
         <v/>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>431.05</v>
-      </c>
-      <c r="G18" s="12">
+      <c r="F18" s="12" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="G18" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>F18+G18</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="11">
         <f>C18*I18</f>
         <v/>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="L18" s="12">
+      <c r="K18" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="L18" s="11">
         <f>C18*$C$8</f>
         <v/>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="11">
         <f>C18*$C$4</f>
         <v/>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="11">
         <f>E18*$C$3</f>
         <v/>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="14">
         <f>K18</f>
         <v/>
       </c>
-      <c r="R18" s="10">
+      <c r="R18" s="11">
         <f>Q18*(1-P18)</f>
         <v/>
       </c>
-      <c r="S18" s="20" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="T18" s="10">
+      <c r="S18" s="15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T18" s="11">
         <f>$C$6*$C$7*S18</f>
         <v/>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="13">
+        <f>S18*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V18" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V18" s="10">
-        <f>C18*U18</f>
-        <v/>
-      </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="11">
+        <f>C18*V18</f>
+        <v/>
+      </c>
+      <c r="X18" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X18" s="10">
-        <f>C18*W18</f>
-        <v/>
-      </c>
-      <c r="Y18" s="10">
-        <f>V18+X18</f>
-        <v/>
-      </c>
-      <c r="Z18" s="14">
-        <f>Y18/C18</f>
-        <v/>
-      </c>
-      <c r="AA18" s="9" t="n">
+      <c r="Y18" s="11">
+        <f>C18*X18</f>
+        <v/>
+      </c>
+      <c r="Z18" s="11">
+        <f>W18+Y18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="16">
+        <f>Z18/C18</f>
+        <v/>
+      </c>
+      <c r="AB18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" s="10">
-        <f>C18*AA18</f>
-        <v/>
-      </c>
-      <c r="AC18" s="10">
-        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-H18+AB18-AH18</f>
-        <v/>
-      </c>
-      <c r="AD18" s="15">
-        <f>AC18-Y18</f>
-        <v/>
-      </c>
-      <c r="AE18" s="14">
-        <f>AD18/C18</f>
+      <c r="AC18" s="11">
+        <f>C18*AB18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="11">
+        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-U18-H18+AC18</f>
+        <v/>
+      </c>
+      <c r="AE18" s="17">
+        <f>AD18-Z18</f>
         <v/>
       </c>
       <c r="AF18" s="16">
-        <f>AD18/H18</f>
-        <v/>
-      </c>
-      <c r="AG18" s="10">
-        <f>(K18+M18+R18+T18+H18+AH18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+U18+W18-AA18))</f>
-        <v/>
-      </c>
-      <c r="AH18" s="12">
-        <f>S18*($C$9+$C$10)</f>
+        <f>AE18/C18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="18">
+        <f>AE18/H18</f>
+        <v/>
+      </c>
+      <c r="AH18" s="11">
+        <f>(K18+M18+R18+T18+U18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+V18+X18-AB18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>1550</v>
-      </c>
-      <c r="D19" s="9" t="n">
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="9">
+        <f>(1.25*H19+K19+M19+R19+T19+U19)/(1-I19-$C$8-$C$4-(1-D19)*$C$3+AB19-V19-X19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="11">
         <f>C19*(1-D19)</f>
         <v/>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>313.84</v>
-      </c>
-      <c r="G19" s="12">
+      <c r="F19" s="12" t="n">
+        <v>431.05</v>
+      </c>
+      <c r="G19" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <f>F19+G19</f>
         <v/>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="11">
         <f>C19*I19</f>
         <v/>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="K19" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="11">
         <f>C19*$C$8</f>
         <v/>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="11">
         <f>C19*$C$4</f>
         <v/>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="11">
         <f>E19*$C$3</f>
         <v/>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="P19" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="14">
         <f>K19</f>
         <v/>
       </c>
-      <c r="R19" s="10">
+      <c r="R19" s="11">
         <f>Q19*(1-P19)</f>
         <v/>
       </c>
-      <c r="S19" s="20" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="T19" s="10">
+      <c r="S19" s="15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="T19" s="11">
         <f>$C$6*$C$7*S19</f>
         <v/>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="13">
+        <f>S19*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V19" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V19" s="10">
-        <f>C19*U19</f>
-        <v/>
-      </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="11">
+        <f>C19*V19</f>
+        <v/>
+      </c>
+      <c r="X19" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X19" s="10">
-        <f>C19*W19</f>
-        <v/>
-      </c>
-      <c r="Y19" s="10">
-        <f>V19+X19</f>
-        <v/>
-      </c>
-      <c r="Z19" s="14">
-        <f>Y19/C19</f>
-        <v/>
-      </c>
-      <c r="AA19" s="9" t="n">
+      <c r="Y19" s="11">
+        <f>C19*X19</f>
+        <v/>
+      </c>
+      <c r="Z19" s="11">
+        <f>W19+Y19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="16">
+        <f>Z19/C19</f>
+        <v/>
+      </c>
+      <c r="AB19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" s="10">
-        <f>C19*AA19</f>
-        <v/>
-      </c>
-      <c r="AC19" s="10">
-        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-H19+AB19-AH19</f>
-        <v/>
-      </c>
-      <c r="AD19" s="15">
-        <f>AC19-Y19</f>
-        <v/>
-      </c>
-      <c r="AE19" s="14">
-        <f>AD19/C19</f>
+      <c r="AC19" s="11">
+        <f>C19*AB19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="11">
+        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-U19-H19+AC19</f>
+        <v/>
+      </c>
+      <c r="AE19" s="17">
+        <f>AD19-Z19</f>
         <v/>
       </c>
       <c r="AF19" s="16">
-        <f>AD19/H19</f>
-        <v/>
-      </c>
-      <c r="AG19" s="10">
-        <f>(K19+M19+R19+T19+H19+AH19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+U19+W19-AA19))</f>
-        <v/>
-      </c>
-      <c r="AH19" s="12">
-        <f>S19*($C$9+$C$10)</f>
+        <f>AE19/C19</f>
+        <v/>
+      </c>
+      <c r="AG19" s="18">
+        <f>AE19/H19</f>
+        <v/>
+      </c>
+      <c r="AH19" s="11">
+        <f>(K19+M19+R19+T19+U19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+V19+X19-AB19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D20" s="9" t="n">
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="9">
+        <f>(1.25*H20+K20+M20+R20+T20+U20)/(1-I20-$C$8-$C$4-(1-D20)*$C$3+AB20-V20-X20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="11">
         <f>C20*(1-D20)</f>
         <v/>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>899.78</v>
-      </c>
-      <c r="G20" s="12">
+      <c r="F20" s="12" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="G20" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>F20+G20</f>
         <v/>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="11">
         <f>C20*I20</f>
         <v/>
       </c>
-      <c r="K20" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="L20" s="12">
+      <c r="K20" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L20" s="11">
         <f>C20*$C$8</f>
         <v/>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="11">
         <f>C20*$C$4</f>
         <v/>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="11">
         <f>E20*$C$3</f>
         <v/>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="P20" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="Q20" s="14">
         <f>K20</f>
         <v/>
       </c>
-      <c r="R20" s="10">
+      <c r="R20" s="11">
         <f>Q20*(1-P20)</f>
         <v/>
       </c>
-      <c r="S20" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T20" s="10">
+      <c r="S20" s="15" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T20" s="11">
         <f>$C$6*$C$7*S20</f>
         <v/>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="13">
+        <f>S20*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V20" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V20" s="10">
-        <f>C20*U20</f>
-        <v/>
-      </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="11">
+        <f>C20*V20</f>
+        <v/>
+      </c>
+      <c r="X20" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X20" s="10">
-        <f>C20*W20</f>
-        <v/>
-      </c>
-      <c r="Y20" s="10">
-        <f>V20+X20</f>
-        <v/>
-      </c>
-      <c r="Z20" s="14">
-        <f>Y20/C20</f>
-        <v/>
-      </c>
-      <c r="AA20" s="9" t="n">
+      <c r="Y20" s="11">
+        <f>C20*X20</f>
+        <v/>
+      </c>
+      <c r="Z20" s="11">
+        <f>W20+Y20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="16">
+        <f>Z20/C20</f>
+        <v/>
+      </c>
+      <c r="AB20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" s="10">
-        <f>C20*AA20</f>
-        <v/>
-      </c>
-      <c r="AC20" s="10">
-        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-H20+AB20-AH20</f>
-        <v/>
-      </c>
-      <c r="AD20" s="15">
-        <f>AC20-Y20</f>
-        <v/>
-      </c>
-      <c r="AE20" s="14">
-        <f>AD20/C20</f>
+      <c r="AC20" s="11">
+        <f>C20*AB20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="11">
+        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-U20-H20+AC20</f>
+        <v/>
+      </c>
+      <c r="AE20" s="17">
+        <f>AD20-Z20</f>
         <v/>
       </c>
       <c r="AF20" s="16">
-        <f>AD20/H20</f>
-        <v/>
-      </c>
-      <c r="AG20" s="10">
-        <f>(K20+M20+R20+T20+H20+AH20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+U20+W20-AA20))</f>
-        <v/>
-      </c>
-      <c r="AH20" s="12">
-        <f>S20*($C$9+$C$10)</f>
+        <f>AE20/C20</f>
+        <v/>
+      </c>
+      <c r="AG20" s="18">
+        <f>AE20/H20</f>
+        <v/>
+      </c>
+      <c r="AH20" s="11">
+        <f>(K20+M20+R20+T20+U20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+V20+X20-AB20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>2650</v>
-      </c>
-      <c r="D21" s="9" t="n">
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="9">
+        <f>(1.25*H21+K21+M21+R21+T21+U21)/(1-I21-$C$8-$C$4-(1-D21)*$C$3+AB21-V21-X21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="11">
         <f>C21*(1-D21)</f>
         <v/>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>646.83</v>
-      </c>
-      <c r="G21" s="12">
+      <c r="F21" s="12" t="n">
+        <v>899.78</v>
+      </c>
+      <c r="G21" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="13">
         <f>F21+G21</f>
         <v/>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="11">
         <f>C21*I21</f>
         <v/>
       </c>
-      <c r="K21" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="L21" s="12">
+      <c r="K21" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="L21" s="11">
         <f>C21*$C$8</f>
         <v/>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="11">
         <f>C21*$C$4</f>
         <v/>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="11">
         <f>E21*$C$3</f>
         <v/>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="14">
         <f>K21</f>
         <v/>
       </c>
-      <c r="R21" s="10">
+      <c r="R21" s="11">
         <f>Q21*(1-P21)</f>
         <v/>
       </c>
-      <c r="S21" s="20" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T21" s="10">
+      <c r="S21" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T21" s="11">
         <f>$C$6*$C$7*S21</f>
         <v/>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="13">
+        <f>S21*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V21" s="10">
-        <f>C21*U21</f>
-        <v/>
-      </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="11">
+        <f>C21*V21</f>
+        <v/>
+      </c>
+      <c r="X21" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X21" s="10">
-        <f>C21*W21</f>
-        <v/>
-      </c>
-      <c r="Y21" s="10">
-        <f>V21+X21</f>
-        <v/>
-      </c>
-      <c r="Z21" s="14">
-        <f>Y21/C21</f>
-        <v/>
-      </c>
-      <c r="AA21" s="9" t="n">
+      <c r="Y21" s="11">
+        <f>C21*X21</f>
+        <v/>
+      </c>
+      <c r="Z21" s="11">
+        <f>W21+Y21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="16">
+        <f>Z21/C21</f>
+        <v/>
+      </c>
+      <c r="AB21" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" s="10">
-        <f>C21*AA21</f>
-        <v/>
-      </c>
-      <c r="AC21" s="10">
-        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-H21+AB21-AH21</f>
-        <v/>
-      </c>
-      <c r="AD21" s="15">
-        <f>AC21-Y21</f>
-        <v/>
-      </c>
-      <c r="AE21" s="14">
-        <f>AD21/C21</f>
+      <c r="AC21" s="11">
+        <f>C21*AB21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="11">
+        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-U21-H21+AC21</f>
+        <v/>
+      </c>
+      <c r="AE21" s="17">
+        <f>AD21-Z21</f>
         <v/>
       </c>
       <c r="AF21" s="16">
-        <f>AD21/H21</f>
-        <v/>
-      </c>
-      <c r="AG21" s="10">
-        <f>(K21+M21+R21+T21+H21+AH21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+U21+W21-AA21))</f>
-        <v/>
-      </c>
-      <c r="AH21" s="12">
-        <f>S21*($C$9+$C$10)</f>
+        <f>AE21/C21</f>
+        <v/>
+      </c>
+      <c r="AG21" s="18">
+        <f>AE21/H21</f>
+        <v/>
+      </c>
+      <c r="AH21" s="11">
+        <f>(K21+M21+R21+T21+U21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+V21+X21-AB21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D22" s="9" t="n">
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="9">
+        <f>(1.25*H22+K22+M22+R22+T22+U22)/(1-I22-$C$8-$C$4-(1-D22)*$C$3+AB22-V22-X22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="11">
         <f>C22*(1-D22)</f>
         <v/>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>735.34</v>
-      </c>
-      <c r="G22" s="12">
+      <c r="F22" s="12" t="n">
+        <v>646.83</v>
+      </c>
+      <c r="G22" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="13">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="11">
         <f>C22*I22</f>
         <v/>
       </c>
-      <c r="K22" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="L22" s="12">
+      <c r="K22" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="L22" s="11">
         <f>C22*$C$8</f>
         <v/>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="11">
         <f>C22*$C$4</f>
         <v/>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="11">
         <f>E22*$C$3</f>
         <v/>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="Q22" s="14">
         <f>K22</f>
         <v/>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="11">
         <f>Q22*(1-P22)</f>
         <v/>
       </c>
-      <c r="S22" s="20" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="T22" s="10">
+      <c r="S22" s="15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T22" s="11">
         <f>$C$6*$C$7*S22</f>
         <v/>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" s="13">
+        <f>S22*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V22" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V22" s="10">
-        <f>C22*U22</f>
-        <v/>
-      </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="11">
+        <f>C22*V22</f>
+        <v/>
+      </c>
+      <c r="X22" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X22" s="10">
-        <f>C22*W22</f>
-        <v/>
-      </c>
-      <c r="Y22" s="10">
-        <f>V22+X22</f>
-        <v/>
-      </c>
-      <c r="Z22" s="14">
-        <f>Y22/C22</f>
-        <v/>
-      </c>
-      <c r="AA22" s="9" t="n">
+      <c r="Y22" s="11">
+        <f>C22*X22</f>
+        <v/>
+      </c>
+      <c r="Z22" s="11">
+        <f>W22+Y22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="16">
+        <f>Z22/C22</f>
+        <v/>
+      </c>
+      <c r="AB22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB22" s="10">
-        <f>C22*AA22</f>
-        <v/>
-      </c>
-      <c r="AC22" s="10">
-        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-H22+AB22-AH22</f>
-        <v/>
-      </c>
-      <c r="AD22" s="15">
-        <f>AC22-Y22</f>
-        <v/>
-      </c>
-      <c r="AE22" s="14">
-        <f>AD22/C22</f>
+      <c r="AC22" s="11">
+        <f>C22*AB22</f>
+        <v/>
+      </c>
+      <c r="AD22" s="11">
+        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-U22-H22+AC22</f>
+        <v/>
+      </c>
+      <c r="AE22" s="17">
+        <f>AD22-Z22</f>
         <v/>
       </c>
       <c r="AF22" s="16">
-        <f>AD22/H22</f>
-        <v/>
-      </c>
-      <c r="AG22" s="10">
-        <f>(K22+M22+R22+T22+H22+AH22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+U22+W22-AA22))</f>
-        <v/>
-      </c>
-      <c r="AH22" s="12">
-        <f>S22*($C$9+$C$10)</f>
+        <f>AE22/C22</f>
+        <v/>
+      </c>
+      <c r="AG22" s="18">
+        <f>AE22/H22</f>
+        <v/>
+      </c>
+      <c r="AH22" s="11">
+        <f>(K22+M22+R22+T22+U22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+V22+X22-AB22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D23" s="9" t="n">
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="9">
+        <f>(1.25*H23+K23+M23+R23+T23+U23)/(1-I23-$C$8-$C$4-(1-D23)*$C$3+AB23-V23-X23)</f>
+        <v/>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="11">
         <f>C23*(1-D23)</f>
         <v/>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>853</v>
-      </c>
-      <c r="G23" s="12">
+      <c r="F23" s="12" t="n">
+        <v>735.34</v>
+      </c>
+      <c r="G23" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="11">
         <f>C23*I23</f>
         <v/>
       </c>
-      <c r="K23" s="8" t="n">
+      <c r="K23" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="11">
         <f>C23*$C$8</f>
         <v/>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="11">
         <f>C23*$C$4</f>
         <v/>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="11">
         <f>E23*$C$3</f>
         <v/>
       </c>
-      <c r="P23" s="9" t="n">
+      <c r="P23" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="14">
         <f>K23</f>
         <v/>
       </c>
-      <c r="R23" s="10">
+      <c r="R23" s="11">
         <f>Q23*(1-P23)</f>
         <v/>
       </c>
-      <c r="S23" s="20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T23" s="10">
+      <c r="S23" s="15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="T23" s="11">
         <f>$C$6*$C$7*S23</f>
         <v/>
       </c>
-      <c r="U23" s="9" t="n">
+      <c r="U23" s="13">
+        <f>S23*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V23" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V23" s="10">
-        <f>C23*U23</f>
-        <v/>
-      </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="11">
+        <f>C23*V23</f>
+        <v/>
+      </c>
+      <c r="X23" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X23" s="10">
-        <f>C23*W23</f>
-        <v/>
-      </c>
-      <c r="Y23" s="10">
-        <f>V23+X23</f>
-        <v/>
-      </c>
-      <c r="Z23" s="14">
-        <f>Y23/C23</f>
-        <v/>
-      </c>
-      <c r="AA23" s="9" t="n">
+      <c r="Y23" s="11">
+        <f>C23*X23</f>
+        <v/>
+      </c>
+      <c r="Z23" s="11">
+        <f>W23+Y23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="16">
+        <f>Z23/C23</f>
+        <v/>
+      </c>
+      <c r="AB23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" s="10">
-        <f>C23*AA23</f>
-        <v/>
-      </c>
-      <c r="AC23" s="10">
-        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-H23+AB23-AH23</f>
-        <v/>
-      </c>
-      <c r="AD23" s="15">
-        <f>AC23-Y23</f>
-        <v/>
-      </c>
-      <c r="AE23" s="14">
-        <f>AD23/C23</f>
+      <c r="AC23" s="11">
+        <f>C23*AB23</f>
+        <v/>
+      </c>
+      <c r="AD23" s="11">
+        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-U23-H23+AC23</f>
+        <v/>
+      </c>
+      <c r="AE23" s="17">
+        <f>AD23-Z23</f>
         <v/>
       </c>
       <c r="AF23" s="16">
-        <f>AD23/H23</f>
-        <v/>
-      </c>
-      <c r="AG23" s="10">
-        <f>(K23+M23+R23+T23+H23+AH23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+U23+W23-AA23))</f>
-        <v/>
-      </c>
-      <c r="AH23" s="12">
-        <f>S23*($C$9+$C$10)</f>
+        <f>AE23/C23</f>
+        <v/>
+      </c>
+      <c r="AG23" s="18">
+        <f>AE23/H23</f>
+        <v/>
+      </c>
+      <c r="AH23" s="11">
+        <f>(K23+M23+R23+T23+U23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+V23+X23-AB23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>2280</v>
-      </c>
-      <c r="D24" s="9" t="n">
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9">
+        <f>(1.25*H24+K24+M24+R24+T24+U24)/(1-I24-$C$8-$C$4-(1-D24)*$C$3+AB24-V24-X24)</f>
+        <v/>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="11">
         <f>C24*(1-D24)</f>
         <v/>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>532.1</v>
-      </c>
-      <c r="G24" s="12">
+      <c r="F24" s="12" t="n">
+        <v>853</v>
+      </c>
+      <c r="G24" s="13">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="13">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="11">
         <f>C24*I24</f>
         <v/>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="L24" s="12">
+      <c r="K24" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="L24" s="11">
         <f>C24*$C$8</f>
         <v/>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="11">
         <f>C24*$C$4</f>
         <v/>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="11">
         <f>E24*$C$3</f>
         <v/>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="Q24" s="14">
         <f>K24</f>
         <v/>
       </c>
-      <c r="R24" s="10">
+      <c r="R24" s="11">
         <f>Q24*(1-P24)</f>
         <v/>
       </c>
-      <c r="S24" s="20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="T24" s="10">
+      <c r="S24" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T24" s="11">
         <f>$C$6*$C$7*S24</f>
         <v/>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="13">
+        <f>S24*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V24" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V24" s="10">
-        <f>C24*U24</f>
-        <v/>
-      </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="11">
+        <f>C24*V24</f>
+        <v/>
+      </c>
+      <c r="X24" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="X24" s="10">
-        <f>C24*W24</f>
-        <v/>
-      </c>
-      <c r="Y24" s="10">
-        <f>V24+X24</f>
-        <v/>
-      </c>
-      <c r="Z24" s="14">
-        <f>Y24/C24</f>
-        <v/>
-      </c>
-      <c r="AA24" s="9" t="n">
+      <c r="Y24" s="11">
+        <f>C24*X24</f>
+        <v/>
+      </c>
+      <c r="Z24" s="11">
+        <f>W24+Y24</f>
+        <v/>
+      </c>
+      <c r="AA24" s="16">
+        <f>Z24/C24</f>
+        <v/>
+      </c>
+      <c r="AB24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AB24" s="10">
-        <f>C24*AA24</f>
-        <v/>
-      </c>
-      <c r="AC24" s="10">
-        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-H24+AB24-AH24</f>
-        <v/>
-      </c>
-      <c r="AD24" s="15">
-        <f>AC24-Y24</f>
-        <v/>
-      </c>
-      <c r="AE24" s="14">
-        <f>AD24/C24</f>
+      <c r="AC24" s="11">
+        <f>C24*AB24</f>
+        <v/>
+      </c>
+      <c r="AD24" s="11">
+        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-U24-H24+AC24</f>
+        <v/>
+      </c>
+      <c r="AE24" s="17">
+        <f>AD24-Z24</f>
         <v/>
       </c>
       <c r="AF24" s="16">
-        <f>AD24/H24</f>
-        <v/>
-      </c>
-      <c r="AG24" s="10">
-        <f>(K24+M24+R24+T24+H24+AH24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+U24+W24-AA24))</f>
-        <v/>
-      </c>
-      <c r="AH24" s="12">
-        <f>S24*($C$9+$C$10)</f>
+        <f>AE24/C24</f>
+        <v/>
+      </c>
+      <c r="AG24" s="18">
+        <f>AE24/H24</f>
+        <v/>
+      </c>
+      <c r="AH24" s="11">
+        <f>(K24+M24+R24+T24+U24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+V24+X24-AB24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n"/>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="9">
+        <f>(1.25*H25+K25+M25+R25+T25+U25)/(1-I25-$C$8-$C$4-(1-D25)*$C$3+AB25-V25-X25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" s="11">
+        <f>C25*(1-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="G25" s="13">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H25" s="13">
+        <f>F25+G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J25" s="11">
+        <f>C25*I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="L25" s="11">
+        <f>C25*$C$8</f>
+        <v/>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" s="11">
+        <f>C25*$C$4</f>
+        <v/>
+      </c>
+      <c r="O25" s="11">
+        <f>E25*$C$3</f>
+        <v/>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q25" s="14">
+        <f>K25</f>
+        <v/>
+      </c>
+      <c r="R25" s="11">
+        <f>Q25*(1-P25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T25" s="11">
+        <f>$C$6*$C$7*S25</f>
+        <v/>
+      </c>
+      <c r="U25" s="13">
+        <f>S25*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V25" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W25" s="11">
+        <f>C25*V25</f>
+        <v/>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y25" s="11">
+        <f>C25*X25</f>
+        <v/>
+      </c>
+      <c r="Z25" s="11">
+        <f>W25+Y25</f>
+        <v/>
+      </c>
+      <c r="AA25" s="16">
+        <f>Z25/C25</f>
+        <v/>
+      </c>
+      <c r="AB25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="11">
+        <f>C25*AB25</f>
+        <v/>
+      </c>
+      <c r="AD25" s="11">
+        <f>C25-J25-K25-L25-M25-N25-O25-R25-T25-U25-H25+AC25</f>
+        <v/>
+      </c>
+      <c r="AE25" s="17">
+        <f>AD25-Z25</f>
+        <v/>
+      </c>
+      <c r="AF25" s="16">
+        <f>AE25/C25</f>
+        <v/>
+      </c>
+      <c r="AG25" s="18">
+        <f>AE25/H25</f>
+        <v/>
+      </c>
+      <c r="AH25" s="11">
+        <f>(K25+M25+R25+T25+U25+H25)/(1-(I25+$C$4+(1-D25)*$C$3+$C$8+V25+X25-AB25))</f>
+        <v/>
+      </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Только FBO. Жёлтые ячейки — вход (цена, СПП %, себест., комиссия, логистика, наценка за нелокальность, выкуп, объём, реклама %, соинвест %) и параметры B3:B7. Остальное — формулы. Цена с СПП = Цена×(1−СПП%); налог считается от цены с СПП. Объём — в литрах из габаритов карточки (если выгружены, иначе объёмный вес). Реклама по актуальным форматам Ozon: Оплата за клик % (CPC) и Вывод в топ % (CPO). Соинвест % — из кабинета (Цены → Баллы за скидки), баллы прибавляются к марже. Меняешь цену в колонке B → маржа и ROI пересчитываются.</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n"/>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Цена (столбец C, оранжевый) — формула: подбирает цену под ROI 25%. Кроссдок = Объём×(обработка C9 + перевозка C10), стоит после Хранения. Жёлтые ячейки — вход.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:AG24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,19 +27,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -52,22 +82,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,23 +111,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,8 +138,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,9 +149,12 @@
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -485,38 +517,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AH28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42.08984375" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="9" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="14" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="18" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="22" max="23"/>
+    <col width="11" customWidth="1" min="24" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="10" customWidth="1" min="28" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
@@ -524,7 +543,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ — меняй жёлтые ячейки, всё пересчитается</t>
@@ -784,1661 +803,1806 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>1250-1300</t>
         </is>
       </c>
-      <c r="C13" s="9">
-        <f>(1.25*H13+K13+M13+R13+T13+U13)/(1-I13-$C$8-$C$4-(1-D13)*$C$3+AB13-V13-X13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="10" t="n">
+      <c r="C13" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>C13*(1-D13)</f>
         <v/>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="10" t="n">
         <v>663.86</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="11">
         <f>F13+G13</f>
         <v/>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="9">
         <f>C13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="9">
         <f>C13*$C$8</f>
         <v/>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="9">
         <f>C13*$C$4</f>
         <v/>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="9">
         <f>E13*$C$3</f>
         <v/>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="P13" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="Q13" s="12">
         <f>K13</f>
         <v/>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="9">
         <f>Q13*(1-P13)</f>
         <v/>
       </c>
-      <c r="S13" s="15" t="n">
+      <c r="S13" s="13" t="n">
         <v>0.735</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13" s="9">
         <f>$C$6*$C$7*S13</f>
         <v/>
       </c>
-      <c r="U13" s="13">
+      <c r="U13" s="11">
         <f>S13*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W13" s="11">
+      <c r="W13" s="9">
         <f>C13*V13</f>
         <v/>
       </c>
-      <c r="X13" s="10" t="n">
+      <c r="X13" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y13" s="11">
+      <c r="Y13" s="9">
         <f>C13*X13</f>
         <v/>
       </c>
-      <c r="Z13" s="11">
+      <c r="Z13" s="9">
         <f>W13+Y13</f>
         <v/>
       </c>
-      <c r="AA13" s="16">
+      <c r="AA13" s="14">
         <f>Z13/C13</f>
         <v/>
       </c>
-      <c r="AB13" s="10" t="n">
+      <c r="AB13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" s="11">
+      <c r="AC13" s="9">
         <f>C13*AB13</f>
         <v/>
       </c>
-      <c r="AD13" s="11">
+      <c r="AD13" s="9">
         <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-U13-H13+AC13</f>
         <v/>
       </c>
-      <c r="AE13" s="17">
+      <c r="AE13" s="15">
         <f>AD13-Z13</f>
         <v/>
       </c>
-      <c r="AF13" s="16">
+      <c r="AF13" s="14">
         <f>AE13/C13</f>
         <v/>
       </c>
-      <c r="AG13" s="18">
+      <c r="AG13" s="16">
         <f>AE13/H13</f>
         <v/>
       </c>
-      <c r="AH13" s="11">
+      <c r="AH13" s="9">
         <f>(K13+M13+R13+T13+U13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+V13+X13-AB13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>1076-1244</t>
         </is>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <f>(1.25*H14+K14+M14+R14+T14+U14)/(1-I14-$C$8-$C$4-(1-D14)*$C$3+AB14-V14-X14)</f>
         <v/>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <f>C14*(1-D14)</f>
         <v/>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="10" t="n">
         <v>463.19</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="11">
         <f>F14+G14</f>
         <v/>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="9">
         <f>C14*I14</f>
         <v/>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="9">
         <f>C14*$C$8</f>
         <v/>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="9">
         <f>C14*$C$4</f>
         <v/>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="9">
         <f>E14*$C$3</f>
         <v/>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="P14" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="14">
+      <c r="Q14" s="12">
         <f>K14</f>
         <v/>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="9">
         <f>Q14*(1-P14)</f>
         <v/>
       </c>
-      <c r="S14" s="15" t="n">
+      <c r="S14" s="13" t="n">
         <v>1.28</v>
       </c>
-      <c r="T14" s="11">
+      <c r="T14" s="9">
         <f>$C$6*$C$7*S14</f>
         <v/>
       </c>
-      <c r="U14" s="13">
+      <c r="U14" s="11">
         <f>S14*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="V14" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W14" s="11">
+      <c r="W14" s="9">
         <f>C14*V14</f>
         <v/>
       </c>
-      <c r="X14" s="10" t="n">
+      <c r="X14" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y14" s="11">
+      <c r="Y14" s="9">
         <f>C14*X14</f>
         <v/>
       </c>
-      <c r="Z14" s="11">
+      <c r="Z14" s="9">
         <f>W14+Y14</f>
         <v/>
       </c>
-      <c r="AA14" s="16">
+      <c r="AA14" s="14">
         <f>Z14/C14</f>
         <v/>
       </c>
-      <c r="AB14" s="10" t="n">
+      <c r="AB14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="11">
+      <c r="AC14" s="9">
         <f>C14*AB14</f>
         <v/>
       </c>
-      <c r="AD14" s="11">
+      <c r="AD14" s="9">
         <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-U14-H14+AC14</f>
         <v/>
       </c>
-      <c r="AE14" s="17">
+      <c r="AE14" s="15">
         <f>AD14-Z14</f>
         <v/>
       </c>
-      <c r="AF14" s="16">
+      <c r="AF14" s="14">
         <f>AE14/C14</f>
         <v/>
       </c>
-      <c r="AG14" s="18">
+      <c r="AG14" s="16">
         <f>AE14/H14</f>
         <v/>
       </c>
-      <c r="AH14" s="11">
+      <c r="AH14" s="9">
         <f>(K14+M14+R14+T14+U14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+V14+X14-AB14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>483 (много подделок)</t>
         </is>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <f>(1.25*H15+K15+M15+R15+T15+U15)/(1-I15-$C$8-$C$4-(1-D15)*$C$3+AB15-V15-X15)</f>
         <v/>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <f>C15*(1-D15)</f>
         <v/>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="10" t="n">
         <v>347.76</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="11">
         <f>F15+G15</f>
         <v/>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="9">
         <f>C15*I15</f>
         <v/>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="9">
         <f>C15*$C$8</f>
         <v/>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="9">
         <f>C15*$C$4</f>
         <v/>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="9">
         <f>E15*$C$3</f>
         <v/>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="P15" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q15" s="14">
+      <c r="Q15" s="12">
         <f>K15</f>
         <v/>
       </c>
-      <c r="R15" s="11">
+      <c r="R15" s="9">
         <f>Q15*(1-P15)</f>
         <v/>
       </c>
-      <c r="S15" s="15" t="n">
+      <c r="S15" s="13" t="n">
         <v>0.832</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15" s="9">
         <f>$C$6*$C$7*S15</f>
         <v/>
       </c>
-      <c r="U15" s="13">
+      <c r="U15" s="11">
         <f>S15*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W15" s="11">
+      <c r="W15" s="9">
         <f>C15*V15</f>
         <v/>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="X15" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y15" s="11">
+      <c r="Y15" s="9">
         <f>C15*X15</f>
         <v/>
       </c>
-      <c r="Z15" s="11">
+      <c r="Z15" s="9">
         <f>W15+Y15</f>
         <v/>
       </c>
-      <c r="AA15" s="16">
+      <c r="AA15" s="14">
         <f>Z15/C15</f>
         <v/>
       </c>
-      <c r="AB15" s="10" t="n">
+      <c r="AB15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" s="11">
+      <c r="AC15" s="9">
         <f>C15*AB15</f>
         <v/>
       </c>
-      <c r="AD15" s="11">
+      <c r="AD15" s="9">
         <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-U15-H15+AC15</f>
         <v/>
       </c>
-      <c r="AE15" s="17">
+      <c r="AE15" s="15">
         <f>AD15-Z15</f>
         <v/>
       </c>
-      <c r="AF15" s="16">
+      <c r="AF15" s="14">
         <f>AE15/C15</f>
         <v/>
       </c>
-      <c r="AG15" s="18">
+      <c r="AG15" s="16">
         <f>AE15/H15</f>
         <v/>
       </c>
-      <c r="AH15" s="11">
+      <c r="AH15" s="9">
         <f>(K15+M15+R15+T15+U15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+V15+X15-AB15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>260-382 (много подделок)</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
         <f>(1.25*H16+K16+M16+R16+T16+U16)/(1-I16-$C$8-$C$4-(1-D16)*$C$3+AB16-V16-X16)</f>
         <v/>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f>C16*(1-D16)</f>
         <v/>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="10" t="n">
         <v>161.3</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="11">
         <f>F16+G16</f>
         <v/>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="9">
         <f>C16*I16</f>
         <v/>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="9">
         <f>C16*$C$8</f>
         <v/>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="9">
         <f>C16*$C$4</f>
         <v/>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="9">
         <f>E16*$C$3</f>
         <v/>
       </c>
-      <c r="P16" s="10" t="n">
+      <c r="P16" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="Q16" s="12">
         <f>K16</f>
         <v/>
       </c>
-      <c r="R16" s="11">
+      <c r="R16" s="9">
         <f>Q16*(1-P16)</f>
         <v/>
       </c>
-      <c r="S16" s="15" t="n">
+      <c r="S16" s="13" t="n">
         <v>0.72</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16" s="9">
         <f>$C$6*$C$7*S16</f>
         <v/>
       </c>
-      <c r="U16" s="13">
+      <c r="U16" s="11">
         <f>S16*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W16" s="11">
+      <c r="W16" s="9">
         <f>C16*V16</f>
         <v/>
       </c>
-      <c r="X16" s="10" t="n">
+      <c r="X16" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y16" s="11">
+      <c r="Y16" s="9">
         <f>C16*X16</f>
         <v/>
       </c>
-      <c r="Z16" s="11">
+      <c r="Z16" s="9">
         <f>W16+Y16</f>
         <v/>
       </c>
-      <c r="AA16" s="16">
+      <c r="AA16" s="14">
         <f>Z16/C16</f>
         <v/>
       </c>
-      <c r="AB16" s="10" t="n">
+      <c r="AB16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="11">
+      <c r="AC16" s="9">
         <f>C16*AB16</f>
         <v/>
       </c>
-      <c r="AD16" s="11">
+      <c r="AD16" s="9">
         <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-U16-H16+AC16</f>
         <v/>
       </c>
-      <c r="AE16" s="17">
+      <c r="AE16" s="15">
         <f>AD16-Z16</f>
         <v/>
       </c>
-      <c r="AF16" s="16">
+      <c r="AF16" s="14">
         <f>AE16/C16</f>
         <v/>
       </c>
-      <c r="AG16" s="18">
+      <c r="AG16" s="16">
         <f>AE16/H16</f>
         <v/>
       </c>
-      <c r="AH16" s="11">
+      <c r="AH16" s="9">
         <f>(K16+M16+R16+T16+U16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+V16+X16-AB16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>896 (заказов 2137шт за 30 дней, но за один день заказали 1200шт, в другой день 387шт в остальные дни заказов нет почти ), остальные 850-1000, продаж 250-380 шт</t>
+        </is>
+      </c>
+      <c r="C17" s="7">
         <f>(1.25*H17+K17+M17+R17+T17+U17)/(1-I17-$C$8-$C$4-(1-D17)*$C$3+AB17-V17-X17)</f>
         <v/>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>C17*(1-D17)</f>
         <v/>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="10" t="n">
         <v>361.03</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="11">
         <f>F17+G17</f>
         <v/>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="9">
         <f>C17*I17</f>
         <v/>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="9">
         <f>C17*$C$8</f>
         <v/>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="9">
         <f>C17*$C$4</f>
         <v/>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="9">
         <f>E17*$C$3</f>
         <v/>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="P17" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q17" s="14">
+      <c r="Q17" s="12">
         <f>K17</f>
         <v/>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="9">
         <f>Q17*(1-P17)</f>
         <v/>
       </c>
-      <c r="S17" s="15" t="n">
+      <c r="S17" s="13" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17" s="9">
         <f>$C$6*$C$7*S17</f>
         <v/>
       </c>
-      <c r="U17" s="13">
+      <c r="U17" s="11">
         <f>S17*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="V17" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W17" s="11">
+      <c r="W17" s="9">
         <f>C17*V17</f>
         <v/>
       </c>
-      <c r="X17" s="10" t="n">
+      <c r="X17" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y17" s="11">
+      <c r="Y17" s="9">
         <f>C17*X17</f>
         <v/>
       </c>
-      <c r="Z17" s="11">
+      <c r="Z17" s="9">
         <f>W17+Y17</f>
         <v/>
       </c>
-      <c r="AA17" s="16">
+      <c r="AA17" s="14">
         <f>Z17/C17</f>
         <v/>
       </c>
-      <c r="AB17" s="10" t="n">
+      <c r="AB17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" s="11">
+      <c r="AC17" s="9">
         <f>C17*AB17</f>
         <v/>
       </c>
-      <c r="AD17" s="11">
+      <c r="AD17" s="9">
         <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-U17-H17+AC17</f>
         <v/>
       </c>
-      <c r="AE17" s="17">
+      <c r="AE17" s="15">
         <f>AD17-Z17</f>
         <v/>
       </c>
-      <c r="AF17" s="16">
+      <c r="AF17" s="14">
         <f>AE17/C17</f>
         <v/>
       </c>
-      <c r="AG17" s="18">
+      <c r="AG17" s="16">
         <f>AE17/H17</f>
         <v/>
       </c>
-      <c r="AH17" s="11">
+      <c r="AH17" s="9">
         <f>(K17+M17+R17+T17+U17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+V17+X17-AB17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>вообще нет, один только за 1670р, продаж нет почти</t>
+        </is>
+      </c>
+      <c r="C18" s="7">
         <f>(1.25*H18+K18+M18+R18+T18+U18)/(1-I18-$C$8-$C$4-(1-D18)*$C$3+AB18-V18-X18)</f>
         <v/>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>C18*(1-D18)</f>
         <v/>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="10" t="n">
         <v>396.72</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="11">
         <f>F18+G18</f>
         <v/>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="9">
         <f>C18*I18</f>
         <v/>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="9">
         <f>C18*$C$8</f>
         <v/>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="M18" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="9">
         <f>C18*$C$4</f>
         <v/>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="9">
         <f>E18*$C$3</f>
         <v/>
       </c>
-      <c r="P18" s="10" t="n">
+      <c r="P18" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q18" s="14">
+      <c r="Q18" s="12">
         <f>K18</f>
         <v/>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="9">
         <f>Q18*(1-P18)</f>
         <v/>
       </c>
-      <c r="S18" s="15" t="n">
+      <c r="S18" s="13" t="n">
         <v>1.89</v>
       </c>
-      <c r="T18" s="11">
+      <c r="T18" s="9">
         <f>$C$6*$C$7*S18</f>
         <v/>
       </c>
-      <c r="U18" s="13">
+      <c r="U18" s="11">
         <f>S18*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W18" s="11">
+      <c r="W18" s="9">
         <f>C18*V18</f>
         <v/>
       </c>
-      <c r="X18" s="10" t="n">
+      <c r="X18" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y18" s="11">
+      <c r="Y18" s="9">
         <f>C18*X18</f>
         <v/>
       </c>
-      <c r="Z18" s="11">
+      <c r="Z18" s="9">
         <f>W18+Y18</f>
         <v/>
       </c>
-      <c r="AA18" s="16">
+      <c r="AA18" s="14">
         <f>Z18/C18</f>
         <v/>
       </c>
-      <c r="AB18" s="10" t="n">
+      <c r="AB18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="11">
+      <c r="AC18" s="9">
         <f>C18*AB18</f>
         <v/>
       </c>
-      <c r="AD18" s="11">
+      <c r="AD18" s="9">
         <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-U18-H18+AC18</f>
         <v/>
       </c>
-      <c r="AE18" s="17">
+      <c r="AE18" s="15">
         <f>AD18-Z18</f>
         <v/>
       </c>
-      <c r="AF18" s="16">
+      <c r="AF18" s="14">
         <f>AE18/C18</f>
         <v/>
       </c>
-      <c r="AG18" s="18">
+      <c r="AG18" s="16">
         <f>AE18/H18</f>
         <v/>
       </c>
-      <c r="AH18" s="11">
+      <c r="AH18" s="9">
         <f>(K18+M18+R18+T18+U18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+V18+X18-AB18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>есть много, цены от 950 до 3700, продаж почти нет</t>
+        </is>
+      </c>
+      <c r="C19" s="7">
         <f>(1.25*H19+K19+M19+R19+T19+U19)/(1-I19-$C$8-$C$4-(1-D19)*$C$3+AB19-V19-X19)</f>
         <v/>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <f>C19*(1-D19)</f>
         <v/>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="10" t="n">
         <v>431.05</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="11">
         <f>F19+G19</f>
         <v/>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I19" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="9">
         <f>C19*I19</f>
         <v/>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="9">
         <f>C19*$C$8</f>
         <v/>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="9">
         <f>C19*$C$4</f>
         <v/>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="9">
         <f>E19*$C$3</f>
         <v/>
       </c>
-      <c r="P19" s="10" t="n">
+      <c r="P19" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q19" s="14">
+      <c r="Q19" s="12">
         <f>K19</f>
         <v/>
       </c>
-      <c r="R19" s="11">
+      <c r="R19" s="9">
         <f>Q19*(1-P19)</f>
         <v/>
       </c>
-      <c r="S19" s="15" t="n">
+      <c r="S19" s="13" t="n">
         <v>0.73</v>
       </c>
-      <c r="T19" s="11">
+      <c r="T19" s="9">
         <f>$C$6*$C$7*S19</f>
         <v/>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="11">
         <f>S19*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W19" s="11">
+      <c r="W19" s="9">
         <f>C19*V19</f>
         <v/>
       </c>
-      <c r="X19" s="10" t="n">
+      <c r="X19" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y19" s="11">
+      <c r="Y19" s="9">
         <f>C19*X19</f>
         <v/>
       </c>
-      <c r="Z19" s="11">
+      <c r="Z19" s="9">
         <f>W19+Y19</f>
         <v/>
       </c>
-      <c r="AA19" s="16">
+      <c r="AA19" s="14">
         <f>Z19/C19</f>
         <v/>
       </c>
-      <c r="AB19" s="10" t="n">
+      <c r="AB19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="AC19" s="9">
         <f>C19*AB19</f>
         <v/>
       </c>
-      <c r="AD19" s="11">
+      <c r="AD19" s="9">
         <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-U19-H19+AC19</f>
         <v/>
       </c>
-      <c r="AE19" s="17">
+      <c r="AE19" s="15">
         <f>AD19-Z19</f>
         <v/>
       </c>
-      <c r="AF19" s="16">
+      <c r="AF19" s="14">
         <f>AE19/C19</f>
         <v/>
       </c>
-      <c r="AG19" s="18">
+      <c r="AG19" s="16">
         <f>AE19/H19</f>
         <v/>
       </c>
-      <c r="AH19" s="11">
+      <c r="AH19" s="9">
         <f>(K19+M19+R19+T19+U19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+V19+X19-AB19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>1533р - 40шт, 1104р-18шт</t>
+        </is>
+      </c>
+      <c r="C20" s="7">
         <f>(1.25*H20+K20+M20+R20+T20+U20)/(1-I20-$C$8-$C$4-(1-D20)*$C$3+AB20-V20-X20)</f>
         <v/>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="9">
         <f>C20*(1-D20)</f>
         <v/>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="10" t="n">
         <v>313.84</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="11">
         <f>F20+G20</f>
         <v/>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="9">
         <f>C20*I20</f>
         <v/>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="9">
         <f>C20*$C$8</f>
         <v/>
       </c>
-      <c r="M20" s="14" t="n">
+      <c r="M20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="9">
         <f>C20*$C$4</f>
         <v/>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="9">
         <f>E20*$C$3</f>
         <v/>
       </c>
-      <c r="P20" s="10" t="n">
+      <c r="P20" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="12">
         <f>K20</f>
         <v/>
       </c>
-      <c r="R20" s="11">
+      <c r="R20" s="9">
         <f>Q20*(1-P20)</f>
         <v/>
       </c>
-      <c r="S20" s="15" t="n">
+      <c r="S20" s="13" t="n">
         <v>0.86</v>
       </c>
-      <c r="T20" s="11">
+      <c r="T20" s="9">
         <f>$C$6*$C$7*S20</f>
         <v/>
       </c>
-      <c r="U20" s="13">
+      <c r="U20" s="11">
         <f>S20*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V20" s="10" t="n">
+      <c r="V20" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W20" s="11">
+      <c r="W20" s="9">
         <f>C20*V20</f>
         <v/>
       </c>
-      <c r="X20" s="10" t="n">
+      <c r="X20" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y20" s="11">
+      <c r="Y20" s="9">
         <f>C20*X20</f>
         <v/>
       </c>
-      <c r="Z20" s="11">
+      <c r="Z20" s="9">
         <f>W20+Y20</f>
         <v/>
       </c>
-      <c r="AA20" s="16">
+      <c r="AA20" s="14">
         <f>Z20/C20</f>
         <v/>
       </c>
-      <c r="AB20" s="10" t="n">
+      <c r="AB20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="11">
+      <c r="AC20" s="9">
         <f>C20*AB20</f>
         <v/>
       </c>
-      <c r="AD20" s="11">
+      <c r="AD20" s="9">
         <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-U20-H20+AC20</f>
         <v/>
       </c>
-      <c r="AE20" s="17">
+      <c r="AE20" s="15">
         <f>AD20-Z20</f>
         <v/>
       </c>
-      <c r="AF20" s="16">
+      <c r="AF20" s="14">
         <f>AE20/C20</f>
         <v/>
       </c>
-      <c r="AG20" s="18">
+      <c r="AG20" s="16">
         <f>AE20/H20</f>
         <v/>
       </c>
-      <c r="AH20" s="11">
+      <c r="AH20" s="9">
         <f>(K20+M20+R20+T20+U20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+V20+X20-AB20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="9">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>1900-2900р, 160-200шт</t>
+        </is>
+      </c>
+      <c r="C21" s="7">
         <f>(1.25*H21+K21+M21+R21+T21+U21)/(1-I21-$C$8-$C$4-(1-D21)*$C$3+AB21-V21-X21)</f>
         <v/>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="9">
         <f>C21*(1-D21)</f>
         <v/>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="10" t="n">
         <v>899.78</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="11">
         <f>F21+G21</f>
         <v/>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I21" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="9">
         <f>C21*I21</f>
         <v/>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="9">
         <f>C21*$C$8</f>
         <v/>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="9">
         <f>C21*$C$4</f>
         <v/>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="9">
         <f>E21*$C$3</f>
         <v/>
       </c>
-      <c r="P21" s="10" t="n">
+      <c r="P21" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q21" s="14">
+      <c r="Q21" s="12">
         <f>K21</f>
         <v/>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="9">
         <f>Q21*(1-P21)</f>
         <v/>
       </c>
-      <c r="S21" s="15" t="n">
+      <c r="S21" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="9">
         <f>$C$6*$C$7*S21</f>
         <v/>
       </c>
-      <c r="U21" s="13">
+      <c r="U21" s="11">
         <f>S21*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W21" s="11">
+      <c r="W21" s="9">
         <f>C21*V21</f>
         <v/>
       </c>
-      <c r="X21" s="10" t="n">
+      <c r="X21" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y21" s="11">
+      <c r="Y21" s="9">
         <f>C21*X21</f>
         <v/>
       </c>
-      <c r="Z21" s="11">
+      <c r="Z21" s="9">
         <f>W21+Y21</f>
         <v/>
       </c>
-      <c r="AA21" s="16">
+      <c r="AA21" s="14">
         <f>Z21/C21</f>
         <v/>
       </c>
-      <c r="AB21" s="10" t="n">
+      <c r="AB21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="11">
+      <c r="AC21" s="9">
         <f>C21*AB21</f>
         <v/>
       </c>
-      <c r="AD21" s="11">
+      <c r="AD21" s="9">
         <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-U21-H21+AC21</f>
         <v/>
       </c>
-      <c r="AE21" s="17">
+      <c r="AE21" s="15">
         <f>AD21-Z21</f>
         <v/>
       </c>
-      <c r="AF21" s="16">
+      <c r="AF21" s="14">
         <f>AE21/C21</f>
         <v/>
       </c>
-      <c r="AG21" s="18">
+      <c r="AG21" s="16">
         <f>AE21/H21</f>
         <v/>
       </c>
-      <c r="AH21" s="11">
+      <c r="AH21" s="9">
         <f>(K21+M21+R21+T21+U21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+V21+X21-AB21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="7">
         <f>(1.25*H22+K22+M22+R22+T22+U22)/(1-I22-$C$8-$C$4-(1-D22)*$C$3+AB22-V22-X22)</f>
         <v/>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="9">
         <f>C22*(1-D22)</f>
         <v/>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="10" t="n">
         <v>646.83</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="11">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="9">
         <f>C22*I22</f>
         <v/>
       </c>
-      <c r="K22" s="14" t="n">
+      <c r="K22" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="9">
         <f>C22*$C$8</f>
         <v/>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="9">
         <f>C22*$C$4</f>
         <v/>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="9">
         <f>E22*$C$3</f>
         <v/>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="P22" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q22" s="14">
+      <c r="Q22" s="12">
         <f>K22</f>
         <v/>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="9">
         <f>Q22*(1-P22)</f>
         <v/>
       </c>
-      <c r="S22" s="15" t="n">
+      <c r="S22" s="13" t="n">
         <v>0.19</v>
       </c>
-      <c r="T22" s="11">
+      <c r="T22" s="9">
         <f>$C$6*$C$7*S22</f>
         <v/>
       </c>
-      <c r="U22" s="13">
+      <c r="U22" s="11">
         <f>S22*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W22" s="11">
+      <c r="W22" s="9">
         <f>C22*V22</f>
         <v/>
       </c>
-      <c r="X22" s="10" t="n">
+      <c r="X22" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y22" s="11">
+      <c r="Y22" s="9">
         <f>C22*X22</f>
         <v/>
       </c>
-      <c r="Z22" s="11">
+      <c r="Z22" s="9">
         <f>W22+Y22</f>
         <v/>
       </c>
-      <c r="AA22" s="16">
+      <c r="AA22" s="14">
         <f>Z22/C22</f>
         <v/>
       </c>
-      <c r="AB22" s="10" t="n">
+      <c r="AB22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" s="11">
+      <c r="AC22" s="9">
         <f>C22*AB22</f>
         <v/>
       </c>
-      <c r="AD22" s="11">
+      <c r="AD22" s="9">
         <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-U22-H22+AC22</f>
         <v/>
       </c>
-      <c r="AE22" s="17">
+      <c r="AE22" s="15">
         <f>AD22-Z22</f>
         <v/>
       </c>
-      <c r="AF22" s="16">
+      <c r="AF22" s="14">
         <f>AE22/C22</f>
         <v/>
       </c>
-      <c r="AG22" s="18">
+      <c r="AG22" s="16">
         <f>AE22/H22</f>
         <v/>
       </c>
-      <c r="AH22" s="11">
+      <c r="AH22" s="9">
         <f>(K22+M22+R22+T22+U22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+V22+X22-AB22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="9">
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="7">
         <f>(1.25*H23+K23+M23+R23+T23+U23)/(1-I23-$C$8-$C$4-(1-D23)*$C$3+AB23-V23-X23)</f>
         <v/>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="9">
         <f>C23*(1-D23)</f>
         <v/>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="10" t="n">
         <v>735.34</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="11">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="9">
         <f>C23*I23</f>
         <v/>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="9">
         <f>C23*$C$8</f>
         <v/>
       </c>
-      <c r="M23" s="14" t="n">
+      <c r="M23" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="9">
         <f>C23*$C$4</f>
         <v/>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="9">
         <f>E23*$C$3</f>
         <v/>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="P23" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="Q23" s="12">
         <f>K23</f>
         <v/>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="9">
         <f>Q23*(1-P23)</f>
         <v/>
       </c>
-      <c r="S23" s="15" t="n">
+      <c r="S23" s="13" t="n">
         <v>0.61</v>
       </c>
-      <c r="T23" s="11">
+      <c r="T23" s="9">
         <f>$C$6*$C$7*S23</f>
         <v/>
       </c>
-      <c r="U23" s="13">
+      <c r="U23" s="11">
         <f>S23*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W23" s="11">
+      <c r="W23" s="9">
         <f>C23*V23</f>
         <v/>
       </c>
-      <c r="X23" s="10" t="n">
+      <c r="X23" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y23" s="11">
+      <c r="Y23" s="9">
         <f>C23*X23</f>
         <v/>
       </c>
-      <c r="Z23" s="11">
+      <c r="Z23" s="9">
         <f>W23+Y23</f>
         <v/>
       </c>
-      <c r="AA23" s="16">
+      <c r="AA23" s="14">
         <f>Z23/C23</f>
         <v/>
       </c>
-      <c r="AB23" s="10" t="n">
+      <c r="AB23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" s="11">
+      <c r="AC23" s="9">
         <f>C23*AB23</f>
         <v/>
       </c>
-      <c r="AD23" s="11">
+      <c r="AD23" s="9">
         <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-U23-H23+AC23</f>
         <v/>
       </c>
-      <c r="AE23" s="17">
+      <c r="AE23" s="15">
         <f>AD23-Z23</f>
         <v/>
       </c>
-      <c r="AF23" s="16">
+      <c r="AF23" s="14">
         <f>AE23/C23</f>
         <v/>
       </c>
-      <c r="AG23" s="18">
+      <c r="AG23" s="16">
         <f>AE23/H23</f>
         <v/>
       </c>
-      <c r="AH23" s="11">
+      <c r="AH23" s="9">
         <f>(K23+M23+R23+T23+U23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+V23+X23-AB23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="9">
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="7">
         <f>(1.25*H24+K24+M24+R24+T24+U24)/(1-I24-$C$8-$C$4-(1-D24)*$C$3+AB24-V24-X24)</f>
         <v/>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <f>C24*(1-D24)</f>
         <v/>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="10" t="n">
         <v>853</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="11">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="9">
         <f>C24*I24</f>
         <v/>
       </c>
-      <c r="K24" s="14" t="n">
+      <c r="K24" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="9">
         <f>C24*$C$8</f>
         <v/>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="9">
         <f>C24*$C$4</f>
         <v/>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="9">
         <f>E24*$C$3</f>
         <v/>
       </c>
-      <c r="P24" s="10" t="n">
+      <c r="P24" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="Q24" s="12">
         <f>K24</f>
         <v/>
       </c>
-      <c r="R24" s="11">
+      <c r="R24" s="9">
         <f>Q24*(1-P24)</f>
         <v/>
       </c>
-      <c r="S24" s="15" t="n">
+      <c r="S24" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="T24" s="11">
+      <c r="T24" s="9">
         <f>$C$6*$C$7*S24</f>
         <v/>
       </c>
-      <c r="U24" s="13">
+      <c r="U24" s="11">
         <f>S24*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W24" s="11">
+      <c r="W24" s="9">
         <f>C24*V24</f>
         <v/>
       </c>
-      <c r="X24" s="10" t="n">
+      <c r="X24" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="Y24" s="9">
         <f>C24*X24</f>
         <v/>
       </c>
-      <c r="Z24" s="11">
+      <c r="Z24" s="9">
         <f>W24+Y24</f>
         <v/>
       </c>
-      <c r="AA24" s="16">
+      <c r="AA24" s="14">
         <f>Z24/C24</f>
         <v/>
       </c>
-      <c r="AB24" s="10" t="n">
+      <c r="AB24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="AC24" s="9">
         <f>C24*AB24</f>
         <v/>
       </c>
-      <c r="AD24" s="11">
+      <c r="AD24" s="9">
         <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-U24-H24+AC24</f>
         <v/>
       </c>
-      <c r="AE24" s="17">
+      <c r="AE24" s="15">
         <f>AD24-Z24</f>
         <v/>
       </c>
-      <c r="AF24" s="16">
+      <c r="AF24" s="14">
         <f>AE24/C24</f>
         <v/>
       </c>
-      <c r="AG24" s="18">
+      <c r="AG24" s="16">
         <f>AE24/H24</f>
         <v/>
       </c>
-      <c r="AH24" s="11">
+      <c r="AH24" s="9">
         <f>(K24+M24+R24+T24+U24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+V24+X24-AB24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный укрепляющий тонер с бифидобактериями</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="7">
+        <f>(1.25*H25+K25+M25+R25+T25+U25)/(1-I25-$C$8-$C$4-(1-D25)*$C$3+AB25-V25-X25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" s="9">
+        <f>C25*(1-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>650</v>
+      </c>
+      <c r="G25" s="11">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H25" s="11">
+        <f>F25+G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J25" s="9">
+        <f>C25*I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="L25" s="9">
+        <f>C25*$C$8</f>
+        <v/>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" s="9">
+        <f>C25*$C$4</f>
+        <v/>
+      </c>
+      <c r="O25" s="9">
+        <f>E25*$C$3</f>
+        <v/>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q25" s="12">
+        <f>K25</f>
+        <v/>
+      </c>
+      <c r="R25" s="9">
+        <f>Q25*(1-P25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="13" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="T25" s="9">
+        <f>$C$6*$C$7*S25</f>
+        <v/>
+      </c>
+      <c r="U25" s="11">
+        <f>S25*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W25" s="9">
+        <f>C25*V25</f>
+        <v/>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y25" s="9">
+        <f>C25*X25</f>
+        <v/>
+      </c>
+      <c r="Z25" s="9">
+        <f>W25+Y25</f>
+        <v/>
+      </c>
+      <c r="AA25" s="14">
+        <f>Z25/C25</f>
+        <v/>
+      </c>
+      <c r="AB25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="9">
+        <f>C25*AB25</f>
+        <v/>
+      </c>
+      <c r="AD25" s="9">
+        <f>C25-J25-K25-L25-M25-N25-O25-R25-T25-U25-H25+AC25</f>
+        <v/>
+      </c>
+      <c r="AE25" s="15">
+        <f>AD25-Z25</f>
+        <v/>
+      </c>
+      <c r="AF25" s="14">
+        <f>AE25/C25</f>
+        <v/>
+      </c>
+      <c r="AG25" s="16">
+        <f>AE25/H25</f>
+        <v/>
+      </c>
+      <c r="AH25" s="9">
+        <f>(K25+M25+R25+T25+U25+H25)/(1-(I25+$C$4+(1-D25)*$C$3+$C$8+V25+X25-AB25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="9">
-        <f>(1.25*H25+K25+M25+R25+T25+U25)/(1-I25-$C$8-$C$4-(1-D25)*$C$3+AB25-V25-X25)</f>
-        <v/>
-      </c>
-      <c r="D25" s="10" t="n">
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="7">
+        <f>(1.25*H26+K26+M26+R26+T26+U26)/(1-I26-$C$8-$C$4-(1-D26)*$C$3+AB26-V26-X26)</f>
+        <v/>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="E25" s="11">
-        <f>C25*(1-D25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="12" t="n">
+      <c r="E26" s="9">
+        <f>C26*(1-D26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>532.1</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G26" s="11">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H25" s="13">
-        <f>F25+G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="10" t="n">
+      <c r="H26" s="11">
+        <f>F26+G26</f>
+        <v/>
+      </c>
+      <c r="I26" s="8" t="n">
         <v>0.41</v>
       </c>
-      <c r="J25" s="11">
-        <f>C25*I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="14" t="n">
+      <c r="J26" s="9">
+        <f>C26*I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="L25" s="11">
-        <f>C25*$C$8</f>
-        <v/>
-      </c>
-      <c r="M25" s="14" t="n">
+      <c r="L26" s="9">
+        <f>C26*$C$8</f>
+        <v/>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N25" s="11">
-        <f>C25*$C$4</f>
-        <v/>
-      </c>
-      <c r="O25" s="11">
-        <f>E25*$C$3</f>
-        <v/>
-      </c>
-      <c r="P25" s="10" t="n">
+      <c r="N26" s="9">
+        <f>C26*$C$4</f>
+        <v/>
+      </c>
+      <c r="O26" s="9">
+        <f>E26*$C$3</f>
+        <v/>
+      </c>
+      <c r="P26" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="14">
-        <f>K25</f>
-        <v/>
-      </c>
-      <c r="R25" s="11">
-        <f>Q25*(1-P25)</f>
-        <v/>
-      </c>
-      <c r="S25" s="15" t="n">
+      <c r="Q26" s="12">
+        <f>K26</f>
+        <v/>
+      </c>
+      <c r="R26" s="9">
+        <f>Q26*(1-P26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="13" t="n">
         <v>0.38</v>
       </c>
-      <c r="T25" s="11">
-        <f>$C$6*$C$7*S25</f>
-        <v/>
-      </c>
-      <c r="U25" s="13">
-        <f>S25*($C$9+$C$10)</f>
-        <v/>
-      </c>
-      <c r="V25" s="10" t="n">
+      <c r="T26" s="9">
+        <f>$C$6*$C$7*S26</f>
+        <v/>
+      </c>
+      <c r="U26" s="11">
+        <f>S26*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W25" s="11">
-        <f>C25*V25</f>
-        <v/>
-      </c>
-      <c r="X25" s="10" t="n">
+      <c r="W26" s="9">
+        <f>C26*V26</f>
+        <v/>
+      </c>
+      <c r="X26" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y25" s="11">
-        <f>C25*X25</f>
-        <v/>
-      </c>
-      <c r="Z25" s="11">
-        <f>W25+Y25</f>
-        <v/>
-      </c>
-      <c r="AA25" s="16">
-        <f>Z25/C25</f>
-        <v/>
-      </c>
-      <c r="AB25" s="10" t="n">
+      <c r="Y26" s="9">
+        <f>C26*X26</f>
+        <v/>
+      </c>
+      <c r="Z26" s="9">
+        <f>W26+Y26</f>
+        <v/>
+      </c>
+      <c r="AA26" s="14">
+        <f>Z26/C26</f>
+        <v/>
+      </c>
+      <c r="AB26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="11">
-        <f>C25*AB25</f>
-        <v/>
-      </c>
-      <c r="AD25" s="11">
-        <f>C25-J25-K25-L25-M25-N25-O25-R25-T25-U25-H25+AC25</f>
-        <v/>
-      </c>
-      <c r="AE25" s="17">
-        <f>AD25-Z25</f>
-        <v/>
-      </c>
-      <c r="AF25" s="16">
-        <f>AE25/C25</f>
-        <v/>
-      </c>
-      <c r="AG25" s="18">
-        <f>AE25/H25</f>
-        <v/>
-      </c>
-      <c r="AH25" s="11">
-        <f>(K25+M25+R25+T25+U25+H25)/(1-(I25+$C$4+(1-D25)*$C$3+$C$8+V25+X25-AB25))</f>
+      <c r="AC26" s="9">
+        <f>C26*AB26</f>
+        <v/>
+      </c>
+      <c r="AD26" s="9">
+        <f>C26-J26-K26-L26-M26-N26-O26-R26-T26-U26-H26+AC26</f>
+        <v/>
+      </c>
+      <c r="AE26" s="15">
+        <f>AD26-Z26</f>
+        <v/>
+      </c>
+      <c r="AF26" s="14">
+        <f>AE26/C26</f>
+        <v/>
+      </c>
+      <c r="AG26" s="16">
+        <f>AE26/H26</f>
+        <v/>
+      </c>
+      <c r="AH26" s="9">
+        <f>(K26+M26+R26+T26+U26+H26)/(1-(I26+$C$4+(1-D26)*$C$3+$C$8+V26+X26-AB26))</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Цена (столбец C, оранжевый) — формула: подбирает цену под ROI 25%. Кроссдок = Объём×(обработка C9 + перевозка C10), стоит после Хранения. Жёлтые ячейки — вход.</t>
-        </is>
-      </c>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -2386,7 +2386,7 @@
         <v/>
       </c>
       <c r="K25" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L25" s="9">
         <f>C25*$C$8</f>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -18,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,50 +28,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
       <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="204"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="204"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="6">
@@ -82,22 +52,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF305496"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,24 +81,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00D0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,7 +107,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,15 +116,13 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -517,33 +485,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:AF27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42.08984375" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="7"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="11"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="16"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="20"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="23"/>
-    <col width="11" customWidth="1" min="24" max="25"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="10" customWidth="1" min="28" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ПАРАМЕТРЫ — меняй жёлтые ячейки, всё пересчитается</t>
@@ -768,1841 +747,1618 @@
       </c>
       <c r="AB12" s="6" t="inlineStr">
         <is>
-          <t>Соинвест, %</t>
+          <t>Маржа до рекл.</t>
         </is>
       </c>
       <c r="AC12" s="6" t="inlineStr">
         <is>
-          <t>Соинвест ₽</t>
+          <t>Маржа/шт</t>
         </is>
       </c>
       <c r="AD12" s="6" t="inlineStr">
         <is>
-          <t>Маржа до рекл.</t>
+          <t>Маржа % цены</t>
         </is>
       </c>
       <c r="AE12" s="6" t="inlineStr">
         <is>
-          <t>Маржа/шт</t>
+          <t>ROI %</t>
         </is>
       </c>
       <c r="AF12" s="6" t="inlineStr">
-        <is>
-          <t>Маржа % цены</t>
-        </is>
-      </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>ROI %</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>Цена безубыт.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>1250-1300</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="4" t="n">
         <v>2600</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <f>C13*(1-D13)</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="11" t="n">
         <v>663.86</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="12">
         <f>F13+G13</f>
         <v/>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="10">
         <f>C13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="10">
         <f>C13*$C$8</f>
         <v/>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="10">
         <f>C13*$C$4</f>
         <v/>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="10">
         <f>E13*$C$3</f>
         <v/>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="P13" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="13">
         <f>K13</f>
         <v/>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="10">
         <f>Q13*(1-P13)</f>
         <v/>
       </c>
-      <c r="S13" s="13" t="n">
+      <c r="S13" s="14" t="n">
         <v>0.735</v>
       </c>
-      <c r="T13" s="9">
+      <c r="T13" s="10">
         <f>$C$6*$C$7*S13</f>
         <v/>
       </c>
-      <c r="U13" s="11">
+      <c r="U13" s="12">
         <f>S13*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W13" s="9">
+      <c r="W13" s="10">
         <f>C13*V13</f>
         <v/>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Y13" s="10">
         <f>C13*X13</f>
         <v/>
       </c>
-      <c r="Z13" s="9">
+      <c r="Z13" s="10">
         <f>W13+Y13</f>
         <v/>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13" s="15">
         <f>Z13/C13</f>
         <v/>
       </c>
-      <c r="AB13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="9">
-        <f>C13*AB13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="9">
-        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-U13-H13+AC13</f>
-        <v/>
-      </c>
-      <c r="AE13" s="15">
-        <f>AD13-Z13</f>
-        <v/>
-      </c>
-      <c r="AF13" s="14">
-        <f>AE13/C13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="16">
-        <f>AE13/H13</f>
-        <v/>
-      </c>
-      <c r="AH13" s="9">
-        <f>(K13+M13+R13+T13+U13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+V13+X13-AB13))</f>
+      <c r="AB13" s="10">
+        <f>C13-J13-K13-L13-M13-N13-O13-R13-T13-U13-H13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="16">
+        <f>AB13-Z13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="15">
+        <f>AC13/C13</f>
+        <v/>
+      </c>
+      <c r="AE13" s="17">
+        <f>AC13/H13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="10">
+        <f>(K13+M13+R13+T13+U13+H13)/(1-(I13+$C$4+(1-D13)*$C$3+$C$8+V13+X13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>1076-1244</t>
         </is>
       </c>
-      <c r="C14" s="7">
-        <f>(1.25*H14+K14+M14+R14+T14+U14)/(1-I14-$C$8-$C$4-(1-D14)*$C$3+AB14-V14-X14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="8" t="n">
+      <c r="C14" s="18">
+        <f>(1.25*H14+K14+M14+R14+T14+U14)/(1-I14-$C$8-$C$4-(1-D14)*$C$3-V14-X14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <f>C14*(1-D14)</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <v>463.19</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <f>F14+G14</f>
         <v/>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="10">
         <f>C14*I14</f>
         <v/>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="10">
         <f>C14*$C$8</f>
         <v/>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="10">
         <f>C14*$C$4</f>
         <v/>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="10">
         <f>E14*$C$3</f>
         <v/>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="P14" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="13">
         <f>K14</f>
         <v/>
       </c>
-      <c r="R14" s="9">
+      <c r="R14" s="10">
         <f>Q14*(1-P14)</f>
         <v/>
       </c>
-      <c r="S14" s="13" t="n">
+      <c r="S14" s="14" t="n">
         <v>1.28</v>
       </c>
-      <c r="T14" s="9">
+      <c r="T14" s="10">
         <f>$C$6*$C$7*S14</f>
         <v/>
       </c>
-      <c r="U14" s="11">
+      <c r="U14" s="12">
         <f>S14*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W14" s="9">
+      <c r="W14" s="10">
         <f>C14*V14</f>
         <v/>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y14" s="9">
+      <c r="Y14" s="10">
         <f>C14*X14</f>
         <v/>
       </c>
-      <c r="Z14" s="9">
+      <c r="Z14" s="10">
         <f>W14+Y14</f>
         <v/>
       </c>
-      <c r="AA14" s="14">
+      <c r="AA14" s="15">
         <f>Z14/C14</f>
         <v/>
       </c>
-      <c r="AB14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="9">
-        <f>C14*AB14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="9">
-        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-U14-H14+AC14</f>
-        <v/>
-      </c>
-      <c r="AE14" s="15">
-        <f>AD14-Z14</f>
-        <v/>
-      </c>
-      <c r="AF14" s="14">
-        <f>AE14/C14</f>
-        <v/>
-      </c>
-      <c r="AG14" s="16">
-        <f>AE14/H14</f>
-        <v/>
-      </c>
-      <c r="AH14" s="9">
-        <f>(K14+M14+R14+T14+U14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+V14+X14-AB14))</f>
+      <c r="AB14" s="10">
+        <f>C14-J14-K14-L14-M14-N14-O14-R14-T14-U14-H14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="16">
+        <f>AB14-Z14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="15">
+        <f>AC14/C14</f>
+        <v/>
+      </c>
+      <c r="AE14" s="17">
+        <f>AC14/H14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="10">
+        <f>(K14+M14+R14+T14+U14+H14)/(1-(I14+$C$4+(1-D14)*$C$3+$C$8+V14+X14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>483 (много подделок)</t>
         </is>
       </c>
-      <c r="C15" s="7">
-        <f>(1.25*H15+K15+M15+R15+T15+U15)/(1-I15-$C$8-$C$4-(1-D15)*$C$3+AB15-V15-X15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="8" t="n">
+      <c r="C15" s="18">
+        <f>(1.25*H15+K15+M15+R15+T15+U15)/(1-I15-$C$8-$C$4-(1-D15)*$C$3-V15-X15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <f>C15*(1-D15)</f>
         <v/>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="11" t="n">
         <v>347.76</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="12">
         <f>F15+G15</f>
         <v/>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="10">
         <f>C15*I15</f>
         <v/>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="10">
         <f>C15*$C$8</f>
         <v/>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="10">
         <f>C15*$C$4</f>
         <v/>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <f>E15*$C$3</f>
         <v/>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="P15" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="13">
         <f>K15</f>
         <v/>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="10">
         <f>Q15*(1-P15)</f>
         <v/>
       </c>
-      <c r="S15" s="13" t="n">
+      <c r="S15" s="14" t="n">
         <v>0.832</v>
       </c>
-      <c r="T15" s="9">
+      <c r="T15" s="10">
         <f>$C$6*$C$7*S15</f>
         <v/>
       </c>
-      <c r="U15" s="11">
+      <c r="U15" s="12">
         <f>S15*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W15" s="9">
+      <c r="W15" s="10">
         <f>C15*V15</f>
         <v/>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y15" s="9">
+      <c r="Y15" s="10">
         <f>C15*X15</f>
         <v/>
       </c>
-      <c r="Z15" s="9">
+      <c r="Z15" s="10">
         <f>W15+Y15</f>
         <v/>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15" s="15">
         <f>Z15/C15</f>
         <v/>
       </c>
-      <c r="AB15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="9">
-        <f>C15*AB15</f>
-        <v/>
-      </c>
-      <c r="AD15" s="9">
-        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-U15-H15+AC15</f>
-        <v/>
-      </c>
-      <c r="AE15" s="15">
-        <f>AD15-Z15</f>
-        <v/>
-      </c>
-      <c r="AF15" s="14">
-        <f>AE15/C15</f>
-        <v/>
-      </c>
-      <c r="AG15" s="16">
-        <f>AE15/H15</f>
-        <v/>
-      </c>
-      <c r="AH15" s="9">
-        <f>(K15+M15+R15+T15+U15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+V15+X15-AB15))</f>
+      <c r="AB15" s="10">
+        <f>C15-J15-K15-L15-M15-N15-O15-R15-T15-U15-H15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="16">
+        <f>AB15-Z15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="15">
+        <f>AC15/C15</f>
+        <v/>
+      </c>
+      <c r="AE15" s="17">
+        <f>AC15/H15</f>
+        <v/>
+      </c>
+      <c r="AF15" s="10">
+        <f>(K15+M15+R15+T15+U15+H15)/(1-(I15+$C$4+(1-D15)*$C$3+$C$8+V15+X15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>260-382 (много подделок)</t>
         </is>
       </c>
-      <c r="C16" s="7">
-        <f>(1.25*H16+K16+M16+R16+T16+U16)/(1-I16-$C$8-$C$4-(1-D16)*$C$3+AB16-V16-X16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="8" t="n">
+      <c r="C16" s="18">
+        <f>(1.25*H16+K16+M16+R16+T16+U16)/(1-I16-$C$8-$C$4-(1-D16)*$C$3-V16-X16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f>C16*(1-D16)</f>
         <v/>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="11" t="n">
         <v>161.3</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="12">
         <f>F16+G16</f>
         <v/>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <f>C16*I16</f>
         <v/>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <f>C16*$C$8</f>
         <v/>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="10">
         <f>C16*$C$4</f>
         <v/>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <f>E16*$C$3</f>
         <v/>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="P16" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="Q16" s="13">
         <f>K16</f>
         <v/>
       </c>
-      <c r="R16" s="9">
+      <c r="R16" s="10">
         <f>Q16*(1-P16)</f>
         <v/>
       </c>
-      <c r="S16" s="13" t="n">
+      <c r="S16" s="14" t="n">
         <v>0.72</v>
       </c>
-      <c r="T16" s="9">
+      <c r="T16" s="10">
         <f>$C$6*$C$7*S16</f>
         <v/>
       </c>
-      <c r="U16" s="11">
+      <c r="U16" s="12">
         <f>S16*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V16" s="8" t="n">
+      <c r="V16" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W16" s="9">
+      <c r="W16" s="10">
         <f>C16*V16</f>
         <v/>
       </c>
-      <c r="X16" s="8" t="n">
+      <c r="X16" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y16" s="9">
+      <c r="Y16" s="10">
         <f>C16*X16</f>
         <v/>
       </c>
-      <c r="Z16" s="9">
+      <c r="Z16" s="10">
         <f>W16+Y16</f>
         <v/>
       </c>
-      <c r="AA16" s="14">
+      <c r="AA16" s="15">
         <f>Z16/C16</f>
         <v/>
       </c>
-      <c r="AB16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="9">
-        <f>C16*AB16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9">
-        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-U16-H16+AC16</f>
-        <v/>
-      </c>
-      <c r="AE16" s="15">
-        <f>AD16-Z16</f>
-        <v/>
-      </c>
-      <c r="AF16" s="14">
-        <f>AE16/C16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="16">
-        <f>AE16/H16</f>
-        <v/>
-      </c>
-      <c r="AH16" s="9">
-        <f>(K16+M16+R16+T16+U16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+V16+X16-AB16))</f>
+      <c r="AB16" s="10">
+        <f>C16-J16-K16-L16-M16-N16-O16-R16-T16-U16-H16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="16">
+        <f>AB16-Z16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="15">
+        <f>AC16/C16</f>
+        <v/>
+      </c>
+      <c r="AE16" s="17">
+        <f>AC16/H16</f>
+        <v/>
+      </c>
+      <c r="AF16" s="10">
+        <f>(K16+M16+R16+T16+U16+H16)/(1-(I16+$C$4+(1-D16)*$C$3+$C$8+V16+X16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>896 (заказов 2137шт за 30 дней, но за один день заказали 1200шт, в другой день 387шт в остальные дни заказов нет почти ), остальные 850-1000, продаж 250-380 шт</t>
         </is>
       </c>
-      <c r="C17" s="7">
-        <f>(1.25*H17+K17+M17+R17+T17+U17)/(1-I17-$C$8-$C$4-(1-D17)*$C$3+AB17-V17-X17)</f>
-        <v/>
-      </c>
-      <c r="D17" s="8" t="n">
+      <c r="C17" s="18">
+        <f>(1.25*H17+K17+M17+R17+T17+U17)/(1-I17-$C$8-$C$4-(1-D17)*$C$3-V17-X17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>C17*(1-D17)</f>
         <v/>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="11" t="n">
         <v>361.03</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="12">
         <f>F17+G17</f>
         <v/>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <f>C17*I17</f>
         <v/>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <f>C17*$C$8</f>
         <v/>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="10">
         <f>C17*$C$4</f>
         <v/>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <f>E17*$C$3</f>
         <v/>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="P17" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="13">
         <f>K17</f>
         <v/>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="10">
         <f>Q17*(1-P17)</f>
         <v/>
       </c>
-      <c r="S17" s="13" t="n">
+      <c r="S17" s="14" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="T17" s="9">
+      <c r="T17" s="10">
         <f>$C$6*$C$7*S17</f>
         <v/>
       </c>
-      <c r="U17" s="11">
+      <c r="U17" s="12">
         <f>S17*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="V17" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W17" s="9">
+      <c r="W17" s="10">
         <f>C17*V17</f>
         <v/>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y17" s="9">
+      <c r="Y17" s="10">
         <f>C17*X17</f>
         <v/>
       </c>
-      <c r="Z17" s="9">
+      <c r="Z17" s="10">
         <f>W17+Y17</f>
         <v/>
       </c>
-      <c r="AA17" s="14">
+      <c r="AA17" s="15">
         <f>Z17/C17</f>
         <v/>
       </c>
-      <c r="AB17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="9">
-        <f>C17*AB17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="9">
-        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-U17-H17+AC17</f>
-        <v/>
-      </c>
-      <c r="AE17" s="15">
-        <f>AD17-Z17</f>
-        <v/>
-      </c>
-      <c r="AF17" s="14">
-        <f>AE17/C17</f>
-        <v/>
-      </c>
-      <c r="AG17" s="16">
-        <f>AE17/H17</f>
-        <v/>
-      </c>
-      <c r="AH17" s="9">
-        <f>(K17+M17+R17+T17+U17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+V17+X17-AB17))</f>
+      <c r="AB17" s="10">
+        <f>C17-J17-K17-L17-M17-N17-O17-R17-T17-U17-H17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="16">
+        <f>AB17-Z17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="15">
+        <f>AC17/C17</f>
+        <v/>
+      </c>
+      <c r="AE17" s="17">
+        <f>AC17/H17</f>
+        <v/>
+      </c>
+      <c r="AF17" s="10">
+        <f>(K17+M17+R17+T17+U17+H17)/(1-(I17+$C$4+(1-D17)*$C$3+$C$8+V17+X17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>вообще нет, один только за 1670р, продаж нет почти</t>
         </is>
       </c>
-      <c r="C18" s="7">
-        <f>(1.25*H18+K18+M18+R18+T18+U18)/(1-I18-$C$8-$C$4-(1-D18)*$C$3+AB18-V18-X18)</f>
-        <v/>
-      </c>
-      <c r="D18" s="8" t="n">
+      <c r="C18" s="18">
+        <f>(1.25*H18+K18+M18+R18+T18+U18)/(1-I18-$C$8-$C$4-(1-D18)*$C$3-V18-X18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>C18*(1-D18)</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="11" t="n">
         <v>396.72</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="12">
         <f>F18+G18</f>
         <v/>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="10">
         <f>C18*I18</f>
         <v/>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="10">
         <f>C18*$C$8</f>
         <v/>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="M18" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="10">
         <f>C18*$C$4</f>
         <v/>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="10">
         <f>E18*$C$3</f>
         <v/>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="P18" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="13">
         <f>K18</f>
         <v/>
       </c>
-      <c r="R18" s="9">
+      <c r="R18" s="10">
         <f>Q18*(1-P18)</f>
         <v/>
       </c>
-      <c r="S18" s="13" t="n">
+      <c r="S18" s="14" t="n">
         <v>1.89</v>
       </c>
-      <c r="T18" s="9">
+      <c r="T18" s="10">
         <f>$C$6*$C$7*S18</f>
         <v/>
       </c>
-      <c r="U18" s="11">
+      <c r="U18" s="12">
         <f>S18*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W18" s="9">
+      <c r="W18" s="10">
         <f>C18*V18</f>
         <v/>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y18" s="9">
+      <c r="Y18" s="10">
         <f>C18*X18</f>
         <v/>
       </c>
-      <c r="Z18" s="9">
+      <c r="Z18" s="10">
         <f>W18+Y18</f>
         <v/>
       </c>
-      <c r="AA18" s="14">
+      <c r="AA18" s="15">
         <f>Z18/C18</f>
         <v/>
       </c>
-      <c r="AB18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="9">
-        <f>C18*AB18</f>
-        <v/>
-      </c>
-      <c r="AD18" s="9">
-        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-U18-H18+AC18</f>
-        <v/>
-      </c>
-      <c r="AE18" s="15">
-        <f>AD18-Z18</f>
-        <v/>
-      </c>
-      <c r="AF18" s="14">
-        <f>AE18/C18</f>
-        <v/>
-      </c>
-      <c r="AG18" s="16">
-        <f>AE18/H18</f>
-        <v/>
-      </c>
-      <c r="AH18" s="9">
-        <f>(K18+M18+R18+T18+U18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+V18+X18-AB18))</f>
+      <c r="AB18" s="10">
+        <f>C18-J18-K18-L18-M18-N18-O18-R18-T18-U18-H18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="16">
+        <f>AB18-Z18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="15">
+        <f>AC18/C18</f>
+        <v/>
+      </c>
+      <c r="AE18" s="17">
+        <f>AC18/H18</f>
+        <v/>
+      </c>
+      <c r="AF18" s="10">
+        <f>(K18+M18+R18+T18+U18+H18)/(1-(I18+$C$4+(1-D18)*$C$3+$C$8+V18+X18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>есть много, цены от 950 до 3700, продаж почти нет</t>
         </is>
       </c>
-      <c r="C19" s="7">
-        <f>(1.25*H19+K19+M19+R19+T19+U19)/(1-I19-$C$8-$C$4-(1-D19)*$C$3+AB19-V19-X19)</f>
-        <v/>
-      </c>
-      <c r="D19" s="8" t="n">
+      <c r="C19" s="18">
+        <f>(1.25*H19+K19+M19+R19+T19+U19)/(1-I19-$C$8-$C$4-(1-D19)*$C$3-V19-X19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>C19*(1-D19)</f>
         <v/>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>431.05</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="12">
         <f>F19+G19</f>
         <v/>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="10">
         <f>C19*I19</f>
         <v/>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="K19" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="10">
         <f>C19*$C$8</f>
         <v/>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="10">
         <f>C19*$C$4</f>
         <v/>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="10">
         <f>E19*$C$3</f>
         <v/>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="P19" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="13">
         <f>K19</f>
         <v/>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="10">
         <f>Q19*(1-P19)</f>
         <v/>
       </c>
-      <c r="S19" s="13" t="n">
+      <c r="S19" s="14" t="n">
         <v>0.73</v>
       </c>
-      <c r="T19" s="9">
+      <c r="T19" s="10">
         <f>$C$6*$C$7*S19</f>
         <v/>
       </c>
-      <c r="U19" s="11">
+      <c r="U19" s="12">
         <f>S19*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W19" s="9">
+      <c r="W19" s="10">
         <f>C19*V19</f>
         <v/>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y19" s="9">
+      <c r="Y19" s="10">
         <f>C19*X19</f>
         <v/>
       </c>
-      <c r="Z19" s="9">
+      <c r="Z19" s="10">
         <f>W19+Y19</f>
         <v/>
       </c>
-      <c r="AA19" s="14">
+      <c r="AA19" s="15">
         <f>Z19/C19</f>
         <v/>
       </c>
-      <c r="AB19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="9">
-        <f>C19*AB19</f>
-        <v/>
-      </c>
-      <c r="AD19" s="9">
-        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-U19-H19+AC19</f>
-        <v/>
-      </c>
-      <c r="AE19" s="15">
-        <f>AD19-Z19</f>
-        <v/>
-      </c>
-      <c r="AF19" s="14">
-        <f>AE19/C19</f>
-        <v/>
-      </c>
-      <c r="AG19" s="16">
-        <f>AE19/H19</f>
-        <v/>
-      </c>
-      <c r="AH19" s="9">
-        <f>(K19+M19+R19+T19+U19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+V19+X19-AB19))</f>
+      <c r="AB19" s="10">
+        <f>C19-J19-K19-L19-M19-N19-O19-R19-T19-U19-H19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="16">
+        <f>AB19-Z19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="15">
+        <f>AC19/C19</f>
+        <v/>
+      </c>
+      <c r="AE19" s="17">
+        <f>AC19/H19</f>
+        <v/>
+      </c>
+      <c r="AF19" s="10">
+        <f>(K19+M19+R19+T19+U19+H19)/(1-(I19+$C$4+(1-D19)*$C$3+$C$8+V19+X19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>1533р - 40шт, 1104р-18шт</t>
         </is>
       </c>
-      <c r="C20" s="7">
-        <f>(1.25*H20+K20+M20+R20+T20+U20)/(1-I20-$C$8-$C$4-(1-D20)*$C$3+AB20-V20-X20)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8" t="n">
+      <c r="C20" s="18">
+        <f>(1.25*H20+K20+M20+R20+T20+U20)/(1-I20-$C$8-$C$4-(1-D20)*$C$3-V20-X20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f>C20*(1-D20)</f>
         <v/>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="11" t="n">
         <v>313.84</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="12">
         <f>F20+G20</f>
         <v/>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="10">
         <f>C20*I20</f>
         <v/>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="10">
         <f>C20*$C$8</f>
         <v/>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="10">
         <f>C20*$C$4</f>
         <v/>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="10">
         <f>E20*$C$3</f>
         <v/>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="P20" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="13">
         <f>K20</f>
         <v/>
       </c>
-      <c r="R20" s="9">
+      <c r="R20" s="10">
         <f>Q20*(1-P20)</f>
         <v/>
       </c>
-      <c r="S20" s="13" t="n">
+      <c r="S20" s="14" t="n">
         <v>0.86</v>
       </c>
-      <c r="T20" s="9">
+      <c r="T20" s="10">
         <f>$C$6*$C$7*S20</f>
         <v/>
       </c>
-      <c r="U20" s="11">
+      <c r="U20" s="12">
         <f>S20*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W20" s="9">
+      <c r="W20" s="10">
         <f>C20*V20</f>
         <v/>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y20" s="9">
+      <c r="Y20" s="10">
         <f>C20*X20</f>
         <v/>
       </c>
-      <c r="Z20" s="9">
+      <c r="Z20" s="10">
         <f>W20+Y20</f>
         <v/>
       </c>
-      <c r="AA20" s="14">
+      <c r="AA20" s="15">
         <f>Z20/C20</f>
         <v/>
       </c>
-      <c r="AB20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="9">
-        <f>C20*AB20</f>
-        <v/>
-      </c>
-      <c r="AD20" s="9">
-        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-U20-H20+AC20</f>
-        <v/>
-      </c>
-      <c r="AE20" s="15">
-        <f>AD20-Z20</f>
-        <v/>
-      </c>
-      <c r="AF20" s="14">
-        <f>AE20/C20</f>
-        <v/>
-      </c>
-      <c r="AG20" s="16">
-        <f>AE20/H20</f>
-        <v/>
-      </c>
-      <c r="AH20" s="9">
-        <f>(K20+M20+R20+T20+U20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+V20+X20-AB20))</f>
+      <c r="AB20" s="10">
+        <f>C20-J20-K20-L20-M20-N20-O20-R20-T20-U20-H20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="16">
+        <f>AB20-Z20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="15">
+        <f>AC20/C20</f>
+        <v/>
+      </c>
+      <c r="AE20" s="17">
+        <f>AC20/H20</f>
+        <v/>
+      </c>
+      <c r="AF20" s="10">
+        <f>(K20+M20+R20+T20+U20+H20)/(1-(I20+$C$4+(1-D20)*$C$3+$C$8+V20+X20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>1900-2900р, 160-200шт</t>
         </is>
       </c>
-      <c r="C21" s="7">
-        <f>(1.25*H21+K21+M21+R21+T21+U21)/(1-I21-$C$8-$C$4-(1-D21)*$C$3+AB21-V21-X21)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8" t="n">
+      <c r="C21" s="18">
+        <f>(1.25*H21+K21+M21+R21+T21+U21)/(1-I21-$C$8-$C$4-(1-D21)*$C$3-V21-X21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <f>C21*(1-D21)</f>
         <v/>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="11" t="n">
         <v>899.78</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="12">
         <f>F21+G21</f>
         <v/>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="10">
         <f>C21*I21</f>
         <v/>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="10">
         <f>C21*$C$8</f>
         <v/>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="10">
         <f>C21*$C$4</f>
         <v/>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="10">
         <f>E21*$C$3</f>
         <v/>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="P21" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="13">
         <f>K21</f>
         <v/>
       </c>
-      <c r="R21" s="9">
+      <c r="R21" s="10">
         <f>Q21*(1-P21)</f>
         <v/>
       </c>
-      <c r="S21" s="13" t="n">
+      <c r="S21" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" s="9">
+      <c r="T21" s="10">
         <f>$C$6*$C$7*S21</f>
         <v/>
       </c>
-      <c r="U21" s="11">
+      <c r="U21" s="12">
         <f>S21*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W21" s="9">
+      <c r="W21" s="10">
         <f>C21*V21</f>
         <v/>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y21" s="9">
+      <c r="Y21" s="10">
         <f>C21*X21</f>
         <v/>
       </c>
-      <c r="Z21" s="9">
+      <c r="Z21" s="10">
         <f>W21+Y21</f>
         <v/>
       </c>
-      <c r="AA21" s="14">
+      <c r="AA21" s="15">
         <f>Z21/C21</f>
         <v/>
       </c>
-      <c r="AB21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="9">
-        <f>C21*AB21</f>
-        <v/>
-      </c>
-      <c r="AD21" s="9">
-        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-U21-H21+AC21</f>
-        <v/>
-      </c>
-      <c r="AE21" s="15">
-        <f>AD21-Z21</f>
-        <v/>
-      </c>
-      <c r="AF21" s="14">
-        <f>AE21/C21</f>
-        <v/>
-      </c>
-      <c r="AG21" s="16">
-        <f>AE21/H21</f>
-        <v/>
-      </c>
-      <c r="AH21" s="9">
-        <f>(K21+M21+R21+T21+U21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+V21+X21-AB21))</f>
+      <c r="AB21" s="10">
+        <f>C21-J21-K21-L21-M21-N21-O21-R21-T21-U21-H21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="16">
+        <f>AB21-Z21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="15">
+        <f>AC21/C21</f>
+        <v/>
+      </c>
+      <c r="AE21" s="17">
+        <f>AC21/H21</f>
+        <v/>
+      </c>
+      <c r="AF21" s="10">
+        <f>(K21+M21+R21+T21+U21+H21)/(1-(I21+$C$4+(1-D21)*$C$3+$C$8+V21+X21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="7">
-        <f>(1.25*H22+K22+M22+R22+T22+U22)/(1-I22-$C$8-$C$4-(1-D22)*$C$3+AB22-V22-X22)</f>
-        <v/>
-      </c>
-      <c r="D22" s="8" t="n">
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="18">
+        <f>(1.25*H22+K22+M22+R22+T22+U22)/(1-I22-$C$8-$C$4-(1-D22)*$C$3-V22-X22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <f>C22*(1-D22)</f>
         <v/>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="11" t="n">
         <v>646.83</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="10">
         <f>C22*I22</f>
         <v/>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="K22" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="10">
         <f>C22*$C$8</f>
         <v/>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="10">
         <f>C22*$C$4</f>
         <v/>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="10">
         <f>E22*$C$3</f>
         <v/>
       </c>
-      <c r="P22" s="8" t="n">
+      <c r="P22" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="13">
         <f>K22</f>
         <v/>
       </c>
-      <c r="R22" s="9">
+      <c r="R22" s="10">
         <f>Q22*(1-P22)</f>
         <v/>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="14" t="n">
         <v>0.19</v>
       </c>
-      <c r="T22" s="9">
+      <c r="T22" s="10">
         <f>$C$6*$C$7*S22</f>
         <v/>
       </c>
-      <c r="U22" s="11">
+      <c r="U22" s="12">
         <f>S22*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W22" s="9">
+      <c r="W22" s="10">
         <f>C22*V22</f>
         <v/>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="X22" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y22" s="9">
+      <c r="Y22" s="10">
         <f>C22*X22</f>
         <v/>
       </c>
-      <c r="Z22" s="9">
+      <c r="Z22" s="10">
         <f>W22+Y22</f>
         <v/>
       </c>
-      <c r="AA22" s="14">
+      <c r="AA22" s="15">
         <f>Z22/C22</f>
         <v/>
       </c>
-      <c r="AB22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="9">
-        <f>C22*AB22</f>
-        <v/>
-      </c>
-      <c r="AD22" s="9">
-        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-U22-H22+AC22</f>
-        <v/>
-      </c>
-      <c r="AE22" s="15">
-        <f>AD22-Z22</f>
-        <v/>
-      </c>
-      <c r="AF22" s="14">
-        <f>AE22/C22</f>
-        <v/>
-      </c>
-      <c r="AG22" s="16">
-        <f>AE22/H22</f>
-        <v/>
-      </c>
-      <c r="AH22" s="9">
-        <f>(K22+M22+R22+T22+U22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+V22+X22-AB22))</f>
+      <c r="AB22" s="10">
+        <f>C22-J22-K22-L22-M22-N22-O22-R22-T22-U22-H22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="16">
+        <f>AB22-Z22</f>
+        <v/>
+      </c>
+      <c r="AD22" s="15">
+        <f>AC22/C22</f>
+        <v/>
+      </c>
+      <c r="AE22" s="17">
+        <f>AC22/H22</f>
+        <v/>
+      </c>
+      <c r="AF22" s="10">
+        <f>(K22+M22+R22+T22+U22+H22)/(1-(I22+$C$4+(1-D22)*$C$3+$C$8+V22+X22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="7">
-        <f>(1.25*H23+K23+M23+R23+T23+U23)/(1-I23-$C$8-$C$4-(1-D23)*$C$3+AB23-V23-X23)</f>
-        <v/>
-      </c>
-      <c r="D23" s="8" t="n">
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="18">
+        <f>(1.25*H23+K23+M23+R23+T23+U23)/(1-I23-$C$8-$C$4-(1-D23)*$C$3-V23-X23)</f>
+        <v/>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <f>C23*(1-D23)</f>
         <v/>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="11" t="n">
         <v>735.34</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="12">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="10">
         <f>C23*I23</f>
         <v/>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="K23" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="10">
         <f>C23*$C$8</f>
         <v/>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="M23" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="10">
         <f>C23*$C$4</f>
         <v/>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="10">
         <f>E23*$C$3</f>
         <v/>
       </c>
-      <c r="P23" s="8" t="n">
+      <c r="P23" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="13">
         <f>K23</f>
         <v/>
       </c>
-      <c r="R23" s="9">
+      <c r="R23" s="10">
         <f>Q23*(1-P23)</f>
         <v/>
       </c>
-      <c r="S23" s="13" t="n">
+      <c r="S23" s="14" t="n">
         <v>0.61</v>
       </c>
-      <c r="T23" s="9">
+      <c r="T23" s="10">
         <f>$C$6*$C$7*S23</f>
         <v/>
       </c>
-      <c r="U23" s="11">
+      <c r="U23" s="12">
         <f>S23*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V23" s="8" t="n">
+      <c r="V23" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W23" s="9">
+      <c r="W23" s="10">
         <f>C23*V23</f>
         <v/>
       </c>
-      <c r="X23" s="8" t="n">
+      <c r="X23" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y23" s="9">
+      <c r="Y23" s="10">
         <f>C23*X23</f>
         <v/>
       </c>
-      <c r="Z23" s="9">
+      <c r="Z23" s="10">
         <f>W23+Y23</f>
         <v/>
       </c>
-      <c r="AA23" s="14">
+      <c r="AA23" s="15">
         <f>Z23/C23</f>
         <v/>
       </c>
-      <c r="AB23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="9">
-        <f>C23*AB23</f>
-        <v/>
-      </c>
-      <c r="AD23" s="9">
-        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-U23-H23+AC23</f>
-        <v/>
-      </c>
-      <c r="AE23" s="15">
-        <f>AD23-Z23</f>
-        <v/>
-      </c>
-      <c r="AF23" s="14">
-        <f>AE23/C23</f>
-        <v/>
-      </c>
-      <c r="AG23" s="16">
-        <f>AE23/H23</f>
-        <v/>
-      </c>
-      <c r="AH23" s="9">
-        <f>(K23+M23+R23+T23+U23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+V23+X23-AB23))</f>
+      <c r="AB23" s="10">
+        <f>C23-J23-K23-L23-M23-N23-O23-R23-T23-U23-H23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="16">
+        <f>AB23-Z23</f>
+        <v/>
+      </c>
+      <c r="AD23" s="15">
+        <f>AC23/C23</f>
+        <v/>
+      </c>
+      <c r="AE23" s="17">
+        <f>AC23/H23</f>
+        <v/>
+      </c>
+      <c r="AF23" s="10">
+        <f>(K23+M23+R23+T23+U23+H23)/(1-(I23+$C$4+(1-D23)*$C$3+$C$8+V23+X23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="7">
-        <f>(1.25*H24+K24+M24+R24+T24+U24)/(1-I24-$C$8-$C$4-(1-D24)*$C$3+AB24-V24-X24)</f>
-        <v/>
-      </c>
-      <c r="D24" s="8" t="n">
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="18">
+        <f>(1.25*H24+K24+M24+R24+T24+U24)/(1-I24-$C$8-$C$4-(1-D24)*$C$3-V24-X24)</f>
+        <v/>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <f>C24*(1-D24)</f>
         <v/>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="11" t="n">
         <v>853</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="12">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="10">
         <f>C24*I24</f>
         <v/>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="K24" s="13" t="n">
         <v>67</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="10">
         <f>C24*$C$8</f>
         <v/>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="M24" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="10">
         <f>C24*$C$4</f>
         <v/>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="10">
         <f>E24*$C$3</f>
         <v/>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="P24" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="13">
         <f>K24</f>
         <v/>
       </c>
-      <c r="R24" s="9">
+      <c r="R24" s="10">
         <f>Q24*(1-P24)</f>
         <v/>
       </c>
-      <c r="S24" s="13" t="n">
+      <c r="S24" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="T24" s="9">
+      <c r="T24" s="10">
         <f>$C$6*$C$7*S24</f>
         <v/>
       </c>
-      <c r="U24" s="11">
+      <c r="U24" s="12">
         <f>S24*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W24" s="9">
+      <c r="W24" s="10">
         <f>C24*V24</f>
         <v/>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y24" s="9">
+      <c r="Y24" s="10">
         <f>C24*X24</f>
         <v/>
       </c>
-      <c r="Z24" s="9">
+      <c r="Z24" s="10">
         <f>W24+Y24</f>
         <v/>
       </c>
-      <c r="AA24" s="14">
+      <c r="AA24" s="15">
         <f>Z24/C24</f>
         <v/>
       </c>
-      <c r="AB24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="9">
-        <f>C24*AB24</f>
-        <v/>
-      </c>
-      <c r="AD24" s="9">
-        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-U24-H24+AC24</f>
-        <v/>
-      </c>
-      <c r="AE24" s="15">
-        <f>AD24-Z24</f>
-        <v/>
-      </c>
-      <c r="AF24" s="14">
-        <f>AE24/C24</f>
-        <v/>
-      </c>
-      <c r="AG24" s="16">
-        <f>AE24/H24</f>
-        <v/>
-      </c>
-      <c r="AH24" s="9">
-        <f>(K24+M24+R24+T24+U24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+V24+X24-AB24))</f>
+      <c r="AB24" s="10">
+        <f>C24-J24-K24-L24-M24-N24-O24-R24-T24-U24-H24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="16">
+        <f>AB24-Z24</f>
+        <v/>
+      </c>
+      <c r="AD24" s="15">
+        <f>AC24/C24</f>
+        <v/>
+      </c>
+      <c r="AE24" s="17">
+        <f>AC24/H24</f>
+        <v/>
+      </c>
+      <c r="AF24" s="10">
+        <f>(K24+M24+R24+T24+U24+H24)/(1-(I24+$C$4+(1-D24)*$C$3+$C$8+V24+X24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный укрепляющий тонер с бифидобактериями</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="7">
-        <f>(1.25*H25+K25+M25+R25+T25+U25)/(1-I25-$C$8-$C$4-(1-D25)*$C$3+AB25-V25-X25)</f>
-        <v/>
-      </c>
-      <c r="D25" s="8" t="n">
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="18">
+        <f>(1.25*H25+K25+M25+R25+T25+U25)/(1-I25-$C$8-$C$4-(1-D25)*$C$3-V25-X25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="10">
         <f>C25*(1-D25)</f>
         <v/>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="12">
         <f>$C$5</f>
         <v/>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="12">
         <f>F25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" s="9" t="n">
         <v>0.41</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="10">
         <f>C25*I25</f>
         <v/>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="K25" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="10">
         <f>C25*$C$8</f>
         <v/>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="10">
         <f>C25*$C$4</f>
         <v/>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="10">
         <f>E25*$C$3</f>
         <v/>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="P25" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="13">
         <f>K25</f>
         <v/>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="10">
         <f>Q25*(1-P25)</f>
         <v/>
       </c>
-      <c r="S25" s="13" t="n">
+      <c r="S25" s="14" t="n">
         <v>0.931</v>
       </c>
-      <c r="T25" s="9">
+      <c r="T25" s="10">
         <f>$C$6*$C$7*S25</f>
         <v/>
       </c>
-      <c r="U25" s="11">
+      <c r="U25" s="12">
         <f>S25*($C$9+$C$10)</f>
         <v/>
       </c>
-      <c r="V25" s="8" t="n">
+      <c r="V25" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W25" s="9">
+      <c r="W25" s="10">
         <f>C25*V25</f>
         <v/>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y25" s="9">
+      <c r="Y25" s="10">
         <f>C25*X25</f>
         <v/>
       </c>
-      <c r="Z25" s="9">
+      <c r="Z25" s="10">
         <f>W25+Y25</f>
         <v/>
       </c>
-      <c r="AA25" s="14">
+      <c r="AA25" s="15">
         <f>Z25/C25</f>
         <v/>
       </c>
-      <c r="AB25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="9">
-        <f>C25*AB25</f>
-        <v/>
-      </c>
-      <c r="AD25" s="9">
-        <f>C25-J25-K25-L25-M25-N25-O25-R25-T25-U25-H25+AC25</f>
-        <v/>
-      </c>
-      <c r="AE25" s="15">
-        <f>AD25-Z25</f>
-        <v/>
-      </c>
-      <c r="AF25" s="14">
-        <f>AE25/C25</f>
-        <v/>
-      </c>
-      <c r="AG25" s="16">
-        <f>AE25/H25</f>
-        <v/>
-      </c>
-      <c r="AH25" s="9">
-        <f>(K25+M25+R25+T25+U25+H25)/(1-(I25+$C$4+(1-D25)*$C$3+$C$8+V25+X25-AB25))</f>
+      <c r="AB25" s="10">
+        <f>C25-J25-K25-L25-M25-N25-O25-R25-T25-U25-H25</f>
+        <v/>
+      </c>
+      <c r="AC25" s="16">
+        <f>AB25-Z25</f>
+        <v/>
+      </c>
+      <c r="AD25" s="15">
+        <f>AC25/C25</f>
+        <v/>
+      </c>
+      <c r="AE25" s="17">
+        <f>AC25/H25</f>
+        <v/>
+      </c>
+      <c r="AF25" s="10">
+        <f>(K25+M25+R25+T25+U25+H25)/(1-(I25+$C$4+(1-D25)*$C$3+$C$8+V25+X25))</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="7">
-        <f>(1.25*H26+K26+M26+R26+T26+U26)/(1-I26-$C$8-$C$4-(1-D26)*$C$3+AB26-V26-X26)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E26" s="9">
-        <f>C26*(1-D26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>532.1</v>
-      </c>
-      <c r="G26" s="11">
-        <f>$C$5</f>
-        <v/>
-      </c>
-      <c r="H26" s="11">
-        <f>F26+G26</f>
-        <v/>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J26" s="9">
-        <f>C26*I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="L26" s="9">
-        <f>C26*$C$8</f>
-        <v/>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N26" s="9">
-        <f>C26*$C$4</f>
-        <v/>
-      </c>
-      <c r="O26" s="9">
-        <f>E26*$C$3</f>
-        <v/>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q26" s="12">
-        <f>K26</f>
-        <v/>
-      </c>
-      <c r="R26" s="9">
-        <f>Q26*(1-P26)</f>
-        <v/>
-      </c>
-      <c r="S26" s="13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="T26" s="9">
-        <f>$C$6*$C$7*S26</f>
-        <v/>
-      </c>
-      <c r="U26" s="11">
-        <f>S26*($C$9+$C$10)</f>
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W26" s="9">
-        <f>C26*V26</f>
-        <v/>
-      </c>
-      <c r="X26" s="8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Y26" s="9">
-        <f>C26*X26</f>
-        <v/>
-      </c>
-      <c r="Z26" s="9">
-        <f>W26+Y26</f>
-        <v/>
-      </c>
-      <c r="AA26" s="14">
-        <f>Z26/C26</f>
-        <v/>
-      </c>
-      <c r="AB26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="9">
-        <f>C26*AB26</f>
-        <v/>
-      </c>
-      <c r="AD26" s="9">
-        <f>C26-J26-K26-L26-M26-N26-O26-R26-T26-U26-H26+AC26</f>
-        <v/>
-      </c>
-      <c r="AE26" s="15">
-        <f>AD26-Z26</f>
-        <v/>
-      </c>
-      <c r="AF26" s="14">
-        <f>AE26/C26</f>
-        <v/>
-      </c>
-      <c r="AG26" s="16">
-        <f>AE26/H26</f>
-        <v/>
-      </c>
-      <c r="AH26" s="9">
-        <f>(K26+M26+R26+T26+U26+H26)/(1-(I26+$C$4+(1-D26)*$C$3+$C$8+V26+X26-AB26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="n"/>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Цена (C): оранжевая — формула под ROI 25%; жёлтая — задана вручную. Столбцы соинвеста убраны. Кроссдок = Объём×(C9+C10) после Хранения.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2353,8 +2353,130 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="18">
+        <f>(1.25*H26+K26+M26+R26+T26+U26)/(1-I26-$C$8-$C$4-(1-D26)*$C$3-V26-X26)</f>
+        <v/>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E26" s="10">
+        <f>C26*(1-D26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="G26" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="H26" s="12">
+        <f>F26+G26</f>
+        <v/>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J26" s="10">
+        <f>C26*I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="L26" s="10">
+        <f>C26*$C$8</f>
+        <v/>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="N26" s="10">
+        <f>C26*$C$4</f>
+        <v/>
+      </c>
+      <c r="O26" s="10">
+        <f>E26*$C$3</f>
+        <v/>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q26" s="13">
+        <f>K26</f>
+        <v/>
+      </c>
+      <c r="R26" s="10">
+        <f>Q26*(1-P26)</f>
+        <v/>
+      </c>
+      <c r="S26" s="14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T26" s="10">
+        <f>$C$6*$C$7*S26</f>
+        <v/>
+      </c>
+      <c r="U26" s="12">
+        <f>S26*($C$9+$C$10)</f>
+        <v/>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W26" s="10">
+        <f>C26*V26</f>
+        <v/>
+      </c>
+      <c r="X26" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y26" s="10">
+        <f>C26*X26</f>
+        <v/>
+      </c>
+      <c r="Z26" s="10">
+        <f>W26+Y26</f>
+        <v/>
+      </c>
+      <c r="AA26" s="15">
+        <f>Z26/C26</f>
+        <v/>
+      </c>
+      <c r="AB26" s="10">
+        <f>C26-J26-K26-L26-M26-N26-O26-R26-T26-U26-H26</f>
+        <v/>
+      </c>
+      <c r="AC26" s="16">
+        <f>AB26-Z26</f>
+        <v/>
+      </c>
+      <c r="AD26" s="15">
+        <f>AC26/C26</f>
+        <v/>
+      </c>
+      <c r="AE26" s="17">
+        <f>AC26/H26</f>
+        <v/>
+      </c>
+      <c r="AF26" s="10">
+        <f>(K26+M26+R26+T26+U26+H26)/(1-(I26+$C$4+(1-D26)*$C$3+$C$8+V26+X26))</f>
+        <v/>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Цена (C): оранжевая — формула под ROI 25%; жёлтая — задана вручную. Столбцы соинвеста убраны. Кроссдок = Объём×(C9+C10) после Хранения.</t>
         </is>

--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тариф логистики" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -115,6 +116,9 @@
       <family val="2"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -160,7 +164,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -358,11 +362,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -474,6 +492,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1173,8 +1193,9 @@
         <f>F13*L13</f>
         <v/>
       </c>
-      <c r="N13" s="29" t="n">
-        <v>67</v>
+      <c r="N13" s="65">
+        <f>VLOOKUP(V13,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O13" s="28">
         <f>F13*$F$8</f>
@@ -1295,8 +1316,9 @@
         <f>F14*L14</f>
         <v/>
       </c>
-      <c r="N14" s="29" t="n">
-        <v>67</v>
+      <c r="N14" s="65">
+        <f>VLOOKUP(V14,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O14" s="28">
         <f>F14*$F$8</f>
@@ -1417,8 +1439,9 @@
         <f>F15*L15</f>
         <v/>
       </c>
-      <c r="N15" s="29" t="n">
-        <v>67</v>
+      <c r="N15" s="65">
+        <f>VLOOKUP(V15,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O15" s="28">
         <f>F15*$F$8</f>
@@ -1539,8 +1562,9 @@
         <f>F16*L16</f>
         <v/>
       </c>
-      <c r="N16" s="29" t="n">
-        <v>67</v>
+      <c r="N16" s="65">
+        <f>VLOOKUP(V16,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O16" s="28">
         <f>F16*$F$8</f>
@@ -1661,8 +1685,9 @@
         <f>F17*L17</f>
         <v/>
       </c>
-      <c r="N17" s="29" t="n">
-        <v>67</v>
+      <c r="N17" s="65">
+        <f>VLOOKUP(V17,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O17" s="28">
         <f>F17*$F$8</f>
@@ -1787,8 +1812,9 @@
         <f>F18*L18</f>
         <v/>
       </c>
-      <c r="N18" s="29" t="n">
-        <v>74</v>
+      <c r="N18" s="65">
+        <f>VLOOKUP(V18,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O18" s="28">
         <f>F18*$F$8</f>
@@ -1913,8 +1939,9 @@
         <f>F19*L19</f>
         <v/>
       </c>
-      <c r="N19" s="29" t="n">
-        <v>67</v>
+      <c r="N19" s="65">
+        <f>VLOOKUP(V19,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O19" s="28">
         <f>F19*$F$8</f>
@@ -2039,8 +2066,9 @@
         <f>F20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="29" t="n">
-        <v>67</v>
+      <c r="N20" s="65">
+        <f>VLOOKUP(V20,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O20" s="28">
         <f>F20*$F$8</f>
@@ -2165,8 +2193,9 @@
         <f>F21*L21</f>
         <v/>
       </c>
-      <c r="N21" s="29" t="n">
-        <v>67</v>
+      <c r="N21" s="65">
+        <f>VLOOKUP(V21,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O21" s="28">
         <f>F21*$F$8</f>
@@ -2291,8 +2320,9 @@
         <f>F22*L22</f>
         <v/>
       </c>
-      <c r="N22" s="29" t="n">
-        <v>75</v>
+      <c r="N22" s="65">
+        <f>VLOOKUP(V22,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O22" s="28">
         <f>F22*$F$8</f>
@@ -2417,8 +2447,9 @@
         <f>F23*L23</f>
         <v/>
       </c>
-      <c r="N23" s="29" t="n">
-        <v>67</v>
+      <c r="N23" s="65">
+        <f>VLOOKUP(V23,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O23" s="28">
         <f>F23*$F$8</f>
@@ -2543,8 +2574,9 @@
         <f>F24*L24</f>
         <v/>
       </c>
-      <c r="N24" s="29" t="n">
-        <v>67</v>
+      <c r="N24" s="65">
+        <f>VLOOKUP(V24,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O24" s="28">
         <f>F24*$F$8</f>
@@ -2670,8 +2702,9 @@
         <f>F25*L25</f>
         <v/>
       </c>
-      <c r="N25" s="29" t="n">
-        <v>63</v>
+      <c r="N25" s="65">
+        <f>VLOOKUP(V25,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O25" s="28">
         <f>F25*$F$8</f>
@@ -2797,8 +2830,9 @@
         <f>F26*L26</f>
         <v/>
       </c>
-      <c r="N26" s="29" t="n">
-        <v>63</v>
+      <c r="N26" s="65">
+        <f>VLOOKUP(V26,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O26" s="28">
         <f>F26*$F$8</f>
@@ -2928,8 +2962,9 @@
         <f>F27*L27</f>
         <v/>
       </c>
-      <c r="N27" s="29" t="n">
-        <v>56</v>
+      <c r="N27" s="65">
+        <f>VLOOKUP(V27,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O27" s="28">
         <f>F27*$F$8</f>
@@ -3059,8 +3094,9 @@
         <f>F28*L28</f>
         <v/>
       </c>
-      <c r="N28" s="29" t="n">
-        <v>67</v>
+      <c r="N28" s="65">
+        <f>VLOOKUP(V28,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O28" s="28">
         <f>F28*$F$8</f>
@@ -3190,8 +3226,9 @@
         <f>F29*L29</f>
         <v/>
       </c>
-      <c r="N29" s="29" t="n">
-        <v>67</v>
+      <c r="N29" s="65">
+        <f>VLOOKUP(V29,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O29" s="28">
         <f>F29*$F$8</f>
@@ -3317,8 +3354,9 @@
         <f>F30*L30</f>
         <v/>
       </c>
-      <c r="N30" s="29" t="n">
-        <v>75</v>
+      <c r="N30" s="65">
+        <f>VLOOKUP(V30,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O30" s="28">
         <f>F30*$F$8</f>
@@ -3443,8 +3481,9 @@
         <f>F31*L31</f>
         <v/>
       </c>
-      <c r="N31" s="51" t="n">
-        <v>63</v>
+      <c r="N31" s="65">
+        <f>VLOOKUP(V31,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O31" s="50">
         <f>F31*$F$8</f>
@@ -9383,4 +9422,497 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Объём от, л</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="inlineStr">
+        <is>
+          <t>Тариф &gt;300₽</t>
+        </is>
+      </c>
+      <c r="C1" s="66" t="inlineStr">
+        <is>
+          <t>Тариф до300₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="B6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.000999999999999</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9.000999999999999</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102</v>
+      </c>
+      <c r="C19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>11.001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>12.001</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>13.001</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>14.001</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111</v>
+      </c>
+      <c r="C23" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>15.001</v>
+      </c>
+      <c r="B24" t="n">
+        <v>119</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17.001</v>
+      </c>
+      <c r="B25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20.001</v>
+      </c>
+      <c r="B26" t="n">
+        <v>143</v>
+      </c>
+      <c r="C26" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25.001</v>
+      </c>
+      <c r="B27" t="n">
+        <v>162</v>
+      </c>
+      <c r="C27" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>177</v>
+      </c>
+      <c r="C28" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>35.001</v>
+      </c>
+      <c r="B29" t="n">
+        <v>195</v>
+      </c>
+      <c r="C29" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40.001</v>
+      </c>
+      <c r="B30" t="n">
+        <v>209</v>
+      </c>
+      <c r="C30" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>45.001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>228</v>
+      </c>
+      <c r="C31" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>50.001</v>
+      </c>
+      <c r="B32" t="n">
+        <v>244</v>
+      </c>
+      <c r="C32" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>60.001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>279</v>
+      </c>
+      <c r="C33" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>70.001</v>
+      </c>
+      <c r="B34" t="n">
+        <v>299</v>
+      </c>
+      <c r="C34" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80.001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>344</v>
+      </c>
+      <c r="C35" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>90.001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>371</v>
+      </c>
+      <c r="C36" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>100.001</v>
+      </c>
+      <c r="B37" t="n">
+        <v>436</v>
+      </c>
+      <c r="C37" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125.001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>503</v>
+      </c>
+      <c r="C38" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>150.001</v>
+      </c>
+      <c r="B39" t="n">
+        <v>578</v>
+      </c>
+      <c r="C39" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>175.001</v>
+      </c>
+      <c r="B40" t="n">
+        <v>692</v>
+      </c>
+      <c r="C40" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>200.001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1026</v>
+      </c>
+      <c r="C41" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>400.001</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1457</v>
+      </c>
+      <c r="C42" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>600.001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1891</v>
+      </c>
+      <c r="C43" t="n">
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -7,9 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тариф логистики" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -120,6 +121,9 @@
       <color theme="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -165,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -408,11 +412,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -539,6 +557,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1716,8 +1736,9 @@
         <f>F13*L13</f>
         <v/>
       </c>
-      <c r="N13" s="29" t="n">
-        <v>67</v>
+      <c r="N13" s="70">
+        <f>VLOOKUP(V13,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O13" s="28">
         <f>F13*$F$8</f>
@@ -1844,8 +1865,8 @@
         <f>F14*L14</f>
         <v/>
       </c>
-      <c r="N14" s="28">
-        <f>VLOOKUP(V14,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N14" s="70">
+        <f>VLOOKUP(V14,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O14" s="28">
@@ -1973,8 +1994,8 @@
         <f>F15*L15</f>
         <v/>
       </c>
-      <c r="N15" s="28">
-        <f>VLOOKUP(V15,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N15" s="70">
+        <f>VLOOKUP(V15,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O15" s="28">
@@ -2102,8 +2123,8 @@
         <f>F16*L16</f>
         <v/>
       </c>
-      <c r="N16" s="28">
-        <f>VLOOKUP(V16,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N16" s="70">
+        <f>VLOOKUP(V16,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O16" s="28">
@@ -2231,8 +2252,8 @@
         <f>F17*L17</f>
         <v/>
       </c>
-      <c r="N17" s="28">
-        <f>VLOOKUP(V17,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N17" s="70">
+        <f>VLOOKUP(V17,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O17" s="28">
@@ -2358,8 +2379,9 @@
         <f>F18*L18</f>
         <v/>
       </c>
-      <c r="N18" s="29" t="n">
-        <v>74</v>
+      <c r="N18" s="70">
+        <f>VLOOKUP(V18,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O18" s="28">
         <f>F18*$F$8</f>
@@ -2484,8 +2506,9 @@
         <f>F19*L19</f>
         <v/>
       </c>
-      <c r="N19" s="29" t="n">
-        <v>67</v>
+      <c r="N19" s="70">
+        <f>VLOOKUP(V19,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O19" s="28">
         <f>F19*$F$8</f>
@@ -2610,8 +2633,9 @@
         <f>F20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="29" t="n">
-        <v>67</v>
+      <c r="N20" s="70">
+        <f>VLOOKUP(V20,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O20" s="28">
         <f>F20*$F$8</f>
@@ -2736,8 +2760,9 @@
         <f>F21*L21</f>
         <v/>
       </c>
-      <c r="N21" s="29" t="n">
-        <v>67</v>
+      <c r="N21" s="70">
+        <f>VLOOKUP(V21,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O21" s="28">
         <f>F21*$F$8</f>
@@ -2862,8 +2887,9 @@
         <f>F22*L22</f>
         <v/>
       </c>
-      <c r="N22" s="29" t="n">
-        <v>75</v>
+      <c r="N22" s="70">
+        <f>VLOOKUP(V22,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O22" s="28">
         <f>F22*$F$8</f>
@@ -2988,8 +3014,9 @@
         <f>F23*L23</f>
         <v/>
       </c>
-      <c r="N23" s="29" t="n">
-        <v>67</v>
+      <c r="N23" s="70">
+        <f>VLOOKUP(V23,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O23" s="28">
         <f>F23*$F$8</f>
@@ -3114,8 +3141,9 @@
         <f>F24*L24</f>
         <v/>
       </c>
-      <c r="N24" s="29" t="n">
-        <v>67</v>
+      <c r="N24" s="70">
+        <f>VLOOKUP(V24,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O24" s="28">
         <f>F24*$F$8</f>
@@ -3241,8 +3269,9 @@
         <f>F25*L25</f>
         <v/>
       </c>
-      <c r="N25" s="29" t="n">
-        <v>63</v>
+      <c r="N25" s="70">
+        <f>VLOOKUP(V25,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O25" s="28">
         <f>F25*$F$8</f>
@@ -3368,8 +3397,9 @@
         <f>F26*L26</f>
         <v/>
       </c>
-      <c r="N26" s="29" t="n">
-        <v>63</v>
+      <c r="N26" s="70">
+        <f>VLOOKUP(V26,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O26" s="28">
         <f>F26*$F$8</f>
@@ -3499,8 +3529,9 @@
         <f>F27*L27</f>
         <v/>
       </c>
-      <c r="N27" s="29" t="n">
-        <v>56</v>
+      <c r="N27" s="70">
+        <f>VLOOKUP(V27,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O27" s="28">
         <f>F27*$F$8</f>
@@ -3630,8 +3661,9 @@
         <f>F28*L28</f>
         <v/>
       </c>
-      <c r="N28" s="29" t="n">
-        <v>67</v>
+      <c r="N28" s="70">
+        <f>VLOOKUP(V28,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O28" s="28">
         <f>F28*$F$8</f>
@@ -3761,8 +3793,9 @@
         <f>F29*L29</f>
         <v/>
       </c>
-      <c r="N29" s="29" t="n">
-        <v>67</v>
+      <c r="N29" s="70">
+        <f>VLOOKUP(V29,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O29" s="28">
         <f>F29*$F$8</f>
@@ -3888,8 +3921,9 @@
         <f>F30*L30</f>
         <v/>
       </c>
-      <c r="N30" s="29" t="n">
-        <v>75</v>
+      <c r="N30" s="70">
+        <f>VLOOKUP(V30,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O30" s="28">
         <f>F30*$F$8</f>
@@ -4014,8 +4048,9 @@
         <f>F31*L31</f>
         <v/>
       </c>
-      <c r="N31" s="51" t="n">
-        <v>63</v>
+      <c r="N31" s="70">
+        <f>VLOOKUP(V31,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O31" s="50">
         <f>F31*$F$8</f>
@@ -4142,8 +4177,9 @@
         <f>F33*L33</f>
         <v/>
       </c>
-      <c r="N33" s="51" t="n">
-        <v>67</v>
+      <c r="N33" s="70">
+        <f>VLOOKUP(V33,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O33" s="50">
         <f>F33*$F$8</f>
@@ -4264,8 +4300,9 @@
         <f>F34*L34</f>
         <v/>
       </c>
-      <c r="N34" s="51" t="n">
-        <v>67</v>
+      <c r="N34" s="70">
+        <f>VLOOKUP(V34,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O34" s="50">
         <f>F34*$F$8</f>
@@ -4386,8 +4423,9 @@
         <f>F35*L35</f>
         <v/>
       </c>
-      <c r="N35" s="51" t="n">
-        <v>67</v>
+      <c r="N35" s="70">
+        <f>VLOOKUP(V35,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O35" s="50">
         <f>F35*$F$8</f>
@@ -4508,8 +4546,9 @@
         <f>F36*L36</f>
         <v/>
       </c>
-      <c r="N36" s="51" t="n">
-        <v>67</v>
+      <c r="N36" s="70">
+        <f>VLOOKUP(V36,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O36" s="50">
         <f>F36*$F$8</f>
@@ -4630,8 +4669,9 @@
         <f>F37*L37</f>
         <v/>
       </c>
-      <c r="N37" s="51" t="n">
-        <v>67</v>
+      <c r="N37" s="70">
+        <f>VLOOKUP(V37,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O37" s="50">
         <f>F37*$F$8</f>
@@ -4752,8 +4792,9 @@
         <f>F38*L38</f>
         <v/>
       </c>
-      <c r="N38" s="51" t="n">
-        <v>67</v>
+      <c r="N38" s="70">
+        <f>VLOOKUP(V38,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O38" s="50">
         <f>F38*$F$8</f>
@@ -4874,8 +4915,9 @@
         <f>F39*L39</f>
         <v/>
       </c>
-      <c r="N39" s="51" t="n">
-        <v>67</v>
+      <c r="N39" s="70">
+        <f>VLOOKUP(V39,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O39" s="50">
         <f>F39*$F$8</f>
@@ -5033,8 +5075,9 @@
         <f>F41*L41</f>
         <v/>
       </c>
-      <c r="N41" s="51" t="n">
-        <v>67</v>
+      <c r="N41" s="70">
+        <f>VLOOKUP(V41,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O41" s="50">
         <f>F41*$F$8</f>
@@ -5155,8 +5198,9 @@
         <f>F42*L42</f>
         <v/>
       </c>
-      <c r="N42" s="51" t="n">
-        <v>67</v>
+      <c r="N42" s="70">
+        <f>VLOOKUP(V42,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O42" s="50">
         <f>F42*$F$8</f>
@@ -5277,8 +5321,9 @@
         <f>F43*L43</f>
         <v/>
       </c>
-      <c r="N43" s="51" t="n">
-        <v>67</v>
+      <c r="N43" s="70">
+        <f>VLOOKUP(V43,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O43" s="50">
         <f>F43*$F$8</f>
@@ -5399,8 +5444,9 @@
         <f>F44*L44</f>
         <v/>
       </c>
-      <c r="N44" s="51" t="n">
-        <v>67</v>
+      <c r="N44" s="70">
+        <f>VLOOKUP(V44,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O44" s="50">
         <f>F44*$F$8</f>
@@ -5558,8 +5604,9 @@
         <f>F46*L46</f>
         <v/>
       </c>
-      <c r="N46" s="51" t="n">
-        <v>72</v>
+      <c r="N46" s="70">
+        <f>VLOOKUP(V46,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O46" s="50">
         <f>F46*$F$8</f>
@@ -5680,8 +5727,9 @@
         <f>F47*L47</f>
         <v/>
       </c>
-      <c r="N47" s="51" t="n">
-        <v>72</v>
+      <c r="N47" s="70">
+        <f>VLOOKUP(V47,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O47" s="50">
         <f>F47*$F$8</f>
@@ -5802,8 +5850,9 @@
         <f>F48*L48</f>
         <v/>
       </c>
-      <c r="N48" s="51" t="n">
-        <v>72</v>
+      <c r="N48" s="70">
+        <f>VLOOKUP(V48,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O48" s="50">
         <f>F48*$F$8</f>
@@ -5924,8 +5973,9 @@
         <f>F49*L49</f>
         <v/>
       </c>
-      <c r="N49" s="51" t="n">
-        <v>72</v>
+      <c r="N49" s="70">
+        <f>VLOOKUP(V49,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O49" s="50">
         <f>F49*$F$8</f>
@@ -6046,8 +6096,9 @@
         <f>F50*L50</f>
         <v/>
       </c>
-      <c r="N50" s="51" t="n">
-        <v>72</v>
+      <c r="N50" s="70">
+        <f>VLOOKUP(V50,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O50" s="50">
         <f>F50*$F$8</f>
@@ -11868,4 +11919,497 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="71" t="inlineStr">
+        <is>
+          <t>Объём от, л</t>
+        </is>
+      </c>
+      <c r="B1" s="71" t="inlineStr">
+        <is>
+          <t>Тариф &gt;300₽</t>
+        </is>
+      </c>
+      <c r="C1" s="71" t="inlineStr">
+        <is>
+          <t>Тариф до300₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="B6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.000999999999999</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9.000999999999999</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102</v>
+      </c>
+      <c r="C19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>11.001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>12.001</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>13.001</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>14.001</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111</v>
+      </c>
+      <c r="C23" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>15.001</v>
+      </c>
+      <c r="B24" t="n">
+        <v>119</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17.001</v>
+      </c>
+      <c r="B25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20.001</v>
+      </c>
+      <c r="B26" t="n">
+        <v>143</v>
+      </c>
+      <c r="C26" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25.001</v>
+      </c>
+      <c r="B27" t="n">
+        <v>162</v>
+      </c>
+      <c r="C27" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>177</v>
+      </c>
+      <c r="C28" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>35.001</v>
+      </c>
+      <c r="B29" t="n">
+        <v>195</v>
+      </c>
+      <c r="C29" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40.001</v>
+      </c>
+      <c r="B30" t="n">
+        <v>209</v>
+      </c>
+      <c r="C30" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>45.001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>228</v>
+      </c>
+      <c r="C31" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>50.001</v>
+      </c>
+      <c r="B32" t="n">
+        <v>244</v>
+      </c>
+      <c r="C32" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>60.001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>279</v>
+      </c>
+      <c r="C33" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>70.001</v>
+      </c>
+      <c r="B34" t="n">
+        <v>299</v>
+      </c>
+      <c r="C34" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80.001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>344</v>
+      </c>
+      <c r="C35" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>90.001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>371</v>
+      </c>
+      <c r="C36" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>100.001</v>
+      </c>
+      <c r="B37" t="n">
+        <v>436</v>
+      </c>
+      <c r="C37" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125.001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>503</v>
+      </c>
+      <c r="C38" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>150.001</v>
+      </c>
+      <c r="B39" t="n">
+        <v>578</v>
+      </c>
+      <c r="C39" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>175.001</v>
+      </c>
+      <c r="B40" t="n">
+        <v>692</v>
+      </c>
+      <c r="C40" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>200.001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1026</v>
+      </c>
+      <c r="C41" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>400.001</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1457</v>
+      </c>
+      <c r="C42" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>600.001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1891</v>
+      </c>
+      <c r="C43" t="n">
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -7,10 +7,9 @@
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Тариф логистики" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -111,6 +110,13 @@
       <name val="Arial"/>
       <charset val="204"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
       <color rgb="FFFF0000"/>
       <sz val="9"/>
     </font>
@@ -122,10 +128,23 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -164,7 +183,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,6 +363,21 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFD0D0D0"/>
       </left>
       <right style="medium">
@@ -412,25 +464,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -531,34 +569,63 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1315,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1005"/>
+  <dimension ref="A1:AI1003"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="78" customWidth="1" style="59" min="1" max="1"/>
@@ -1477,41 +1544,41 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="H11" s="67" t="inlineStr">
+      <c r="H11" s="78" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I11" s="68" t="n"/>
-      <c r="J11" s="68" t="n"/>
-      <c r="K11" s="69" t="n"/>
-      <c r="L11" s="67" t="inlineStr">
+      <c r="I11" s="79" t="n"/>
+      <c r="J11" s="79" t="n"/>
+      <c r="K11" s="80" t="n"/>
+      <c r="L11" s="78" t="inlineStr">
         <is>
           <t>Комиссия ОЗОН</t>
         </is>
       </c>
-      <c r="M11" s="68" t="n"/>
-      <c r="N11" s="68" t="n"/>
-      <c r="O11" s="68" t="n"/>
-      <c r="P11" s="68" t="n"/>
-      <c r="Q11" s="68" t="n"/>
-      <c r="R11" s="68" t="n"/>
-      <c r="S11" s="68" t="n"/>
-      <c r="T11" s="68" t="n"/>
-      <c r="U11" s="68" t="n"/>
-      <c r="V11" s="68" t="n"/>
-      <c r="W11" s="68" t="n"/>
-      <c r="X11" s="69" t="n"/>
-      <c r="Y11" s="67" t="inlineStr">
+      <c r="M11" s="79" t="n"/>
+      <c r="N11" s="79" t="n"/>
+      <c r="O11" s="79" t="n"/>
+      <c r="P11" s="79" t="n"/>
+      <c r="Q11" s="79" t="n"/>
+      <c r="R11" s="79" t="n"/>
+      <c r="S11" s="79" t="n"/>
+      <c r="T11" s="79" t="n"/>
+      <c r="U11" s="79" t="n"/>
+      <c r="V11" s="79" t="n"/>
+      <c r="W11" s="79" t="n"/>
+      <c r="X11" s="80" t="n"/>
+      <c r="Y11" s="78" t="inlineStr">
         <is>
           <t>Реклама</t>
         </is>
       </c>
-      <c r="Z11" s="68" t="n"/>
-      <c r="AA11" s="68" t="n"/>
-      <c r="AB11" s="68" t="n"/>
-      <c r="AC11" s="68" t="n"/>
-      <c r="AD11" s="69" t="n"/>
+      <c r="Z11" s="79" t="n"/>
+      <c r="AA11" s="79" t="n"/>
+      <c r="AB11" s="79" t="n"/>
+      <c r="AC11" s="79" t="n"/>
+      <c r="AD11" s="80" t="n"/>
     </row>
     <row r="12" ht="46.5" customHeight="1" s="59">
       <c r="A12" s="13" t="inlineStr">
@@ -1736,9 +1803,8 @@
         <f>F13*L13</f>
         <v/>
       </c>
-      <c r="N13" s="70">
-        <f>VLOOKUP(V13,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N13" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O13" s="28">
         <f>F13*$F$8</f>
@@ -1865,8 +1931,8 @@
         <f>F14*L14</f>
         <v/>
       </c>
-      <c r="N14" s="70">
-        <f>VLOOKUP(V14,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N14" s="28">
+        <f>VLOOKUP(V14,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O14" s="28">
@@ -1994,8 +2060,8 @@
         <f>F15*L15</f>
         <v/>
       </c>
-      <c r="N15" s="70">
-        <f>VLOOKUP(V15,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N15" s="28">
+        <f>VLOOKUP(V15,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O15" s="28">
@@ -2123,8 +2189,8 @@
         <f>F16*L16</f>
         <v/>
       </c>
-      <c r="N16" s="70">
-        <f>VLOOKUP(V16,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N16" s="28">
+        <f>VLOOKUP(V16,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O16" s="28">
@@ -2252,8 +2318,8 @@
         <f>F17*L17</f>
         <v/>
       </c>
-      <c r="N17" s="70">
-        <f>VLOOKUP(V17,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N17" s="28">
+        <f>VLOOKUP(V17,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O17" s="28">
@@ -2379,9 +2445,8 @@
         <f>F18*L18</f>
         <v/>
       </c>
-      <c r="N18" s="70">
-        <f>VLOOKUP(V18,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N18" s="29" t="n">
+        <v>74</v>
       </c>
       <c r="O18" s="28">
         <f>F18*$F$8</f>
@@ -2506,9 +2571,8 @@
         <f>F19*L19</f>
         <v/>
       </c>
-      <c r="N19" s="70">
-        <f>VLOOKUP(V19,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N19" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O19" s="28">
         <f>F19*$F$8</f>
@@ -2633,9 +2697,8 @@
         <f>F20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="70">
-        <f>VLOOKUP(V20,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N20" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O20" s="28">
         <f>F20*$F$8</f>
@@ -2760,9 +2823,8 @@
         <f>F21*L21</f>
         <v/>
       </c>
-      <c r="N21" s="70">
-        <f>VLOOKUP(V21,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N21" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O21" s="28">
         <f>F21*$F$8</f>
@@ -2887,9 +2949,8 @@
         <f>F22*L22</f>
         <v/>
       </c>
-      <c r="N22" s="70">
-        <f>VLOOKUP(V22,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N22" s="29" t="n">
+        <v>75</v>
       </c>
       <c r="O22" s="28">
         <f>F22*$F$8</f>
@@ -3014,9 +3075,8 @@
         <f>F23*L23</f>
         <v/>
       </c>
-      <c r="N23" s="70">
-        <f>VLOOKUP(V23,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N23" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O23" s="28">
         <f>F23*$F$8</f>
@@ -3141,9 +3201,8 @@
         <f>F24*L24</f>
         <v/>
       </c>
-      <c r="N24" s="70">
-        <f>VLOOKUP(V24,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N24" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O24" s="28">
         <f>F24*$F$8</f>
@@ -3269,9 +3328,8 @@
         <f>F25*L25</f>
         <v/>
       </c>
-      <c r="N25" s="70">
-        <f>VLOOKUP(V25,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N25" s="29" t="n">
+        <v>63</v>
       </c>
       <c r="O25" s="28">
         <f>F25*$F$8</f>
@@ -3397,9 +3455,8 @@
         <f>F26*L26</f>
         <v/>
       </c>
-      <c r="N26" s="70">
-        <f>VLOOKUP(V26,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N26" s="29" t="n">
+        <v>63</v>
       </c>
       <c r="O26" s="28">
         <f>F26*$F$8</f>
@@ -3529,9 +3586,8 @@
         <f>F27*L27</f>
         <v/>
       </c>
-      <c r="N27" s="70">
-        <f>VLOOKUP(V27,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N27" s="29" t="n">
+        <v>56</v>
       </c>
       <c r="O27" s="28">
         <f>F27*$F$8</f>
@@ -3661,9 +3717,8 @@
         <f>F28*L28</f>
         <v/>
       </c>
-      <c r="N28" s="70">
-        <f>VLOOKUP(V28,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N28" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O28" s="28">
         <f>F28*$F$8</f>
@@ -3793,9 +3848,8 @@
         <f>F29*L29</f>
         <v/>
       </c>
-      <c r="N29" s="70">
-        <f>VLOOKUP(V29,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N29" s="29" t="n">
+        <v>67</v>
       </c>
       <c r="O29" s="28">
         <f>F29*$F$8</f>
@@ -3921,9 +3975,8 @@
         <f>F30*L30</f>
         <v/>
       </c>
-      <c r="N30" s="70">
-        <f>VLOOKUP(V30,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N30" s="29" t="n">
+        <v>75</v>
       </c>
       <c r="O30" s="28">
         <f>F30*$F$8</f>
@@ -4048,9 +4101,8 @@
         <f>F31*L31</f>
         <v/>
       </c>
-      <c r="N31" s="70">
-        <f>VLOOKUP(V31,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N31" s="51" t="n">
+        <v>63</v>
       </c>
       <c r="O31" s="50">
         <f>F31*$F$8</f>
@@ -4177,9 +4229,8 @@
         <f>F33*L33</f>
         <v/>
       </c>
-      <c r="N33" s="70">
-        <f>VLOOKUP(V33,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N33" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O33" s="50">
         <f>F33*$F$8</f>
@@ -4300,9 +4351,8 @@
         <f>F34*L34</f>
         <v/>
       </c>
-      <c r="N34" s="70">
-        <f>VLOOKUP(V34,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N34" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O34" s="50">
         <f>F34*$F$8</f>
@@ -4423,9 +4473,8 @@
         <f>F35*L35</f>
         <v/>
       </c>
-      <c r="N35" s="70">
-        <f>VLOOKUP(V35,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N35" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O35" s="50">
         <f>F35*$F$8</f>
@@ -4546,9 +4595,8 @@
         <f>F36*L36</f>
         <v/>
       </c>
-      <c r="N36" s="70">
-        <f>VLOOKUP(V36,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N36" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O36" s="50">
         <f>F36*$F$8</f>
@@ -4669,9 +4717,8 @@
         <f>F37*L37</f>
         <v/>
       </c>
-      <c r="N37" s="70">
-        <f>VLOOKUP(V37,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N37" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O37" s="50">
         <f>F37*$F$8</f>
@@ -4792,9 +4839,8 @@
         <f>F38*L38</f>
         <v/>
       </c>
-      <c r="N38" s="70">
-        <f>VLOOKUP(V38,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N38" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O38" s="50">
         <f>F38*$F$8</f>
@@ -4915,9 +4961,8 @@
         <f>F39*L39</f>
         <v/>
       </c>
-      <c r="N39" s="70">
-        <f>VLOOKUP(V39,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N39" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O39" s="50">
         <f>F39*$F$8</f>
@@ -5021,7 +5066,7 @@
       <c r="S40" s="61" t="n"/>
       <c r="T40" s="61" t="n"/>
       <c r="U40" s="61" t="n"/>
-      <c r="V40" s="61" t="n"/>
+      <c r="V40" s="77" t="n"/>
       <c r="W40" s="61" t="n"/>
       <c r="X40" s="61" t="n"/>
       <c r="Y40" s="61" t="n"/>
@@ -5075,9 +5120,8 @@
         <f>F41*L41</f>
         <v/>
       </c>
-      <c r="N41" s="70">
-        <f>VLOOKUP(V41,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N41" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O41" s="50">
         <f>F41*$F$8</f>
@@ -5198,9 +5242,8 @@
         <f>F42*L42</f>
         <v/>
       </c>
-      <c r="N42" s="70">
-        <f>VLOOKUP(V42,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N42" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O42" s="50">
         <f>F42*$F$8</f>
@@ -5321,9 +5364,8 @@
         <f>F43*L43</f>
         <v/>
       </c>
-      <c r="N43" s="70">
-        <f>VLOOKUP(V43,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N43" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O43" s="50">
         <f>F43*$F$8</f>
@@ -5444,9 +5486,8 @@
         <f>F44*L44</f>
         <v/>
       </c>
-      <c r="N44" s="70">
-        <f>VLOOKUP(V44,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N44" s="51" t="n">
+        <v>67</v>
       </c>
       <c r="O44" s="50">
         <f>F44*$F$8</f>
@@ -5550,7 +5591,7 @@
       <c r="S45" s="61" t="n"/>
       <c r="T45" s="61" t="n"/>
       <c r="U45" s="61" t="n"/>
-      <c r="V45" s="61" t="n"/>
+      <c r="V45" s="77" t="n"/>
       <c r="W45" s="61" t="n"/>
       <c r="X45" s="61" t="n"/>
       <c r="Y45" s="61" t="n"/>
@@ -5604,9 +5645,8 @@
         <f>F46*L46</f>
         <v/>
       </c>
-      <c r="N46" s="70">
-        <f>VLOOKUP(V46,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N46" s="51" t="n">
+        <v>72</v>
       </c>
       <c r="O46" s="50">
         <f>F46*$F$8</f>
@@ -5727,9 +5767,8 @@
         <f>F47*L47</f>
         <v/>
       </c>
-      <c r="N47" s="70">
-        <f>VLOOKUP(V47,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N47" s="51" t="n">
+        <v>72</v>
       </c>
       <c r="O47" s="50">
         <f>F47*$F$8</f>
@@ -5850,9 +5889,8 @@
         <f>F48*L48</f>
         <v/>
       </c>
-      <c r="N48" s="70">
-        <f>VLOOKUP(V48,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N48" s="51" t="n">
+        <v>72</v>
       </c>
       <c r="O48" s="50">
         <f>F48*$F$8</f>
@@ -5973,9 +6011,8 @@
         <f>F49*L49</f>
         <v/>
       </c>
-      <c r="N49" s="70">
-        <f>VLOOKUP(V49,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N49" s="51" t="n">
+        <v>72</v>
       </c>
       <c r="O49" s="50">
         <f>F49*$F$8</f>
@@ -6096,9 +6133,8 @@
         <f>F50*L50</f>
         <v/>
       </c>
-      <c r="N50" s="70">
-        <f>VLOOKUP(V50,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
-        <v/>
+      <c r="N50" s="51" t="n">
+        <v>72</v>
       </c>
       <c r="O50" s="50">
         <f>F50*$F$8</f>
@@ -6180,71 +6216,1262 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1" s="59">
-      <c r="A51" s="3" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1" s="59">
-      <c r="A52" s="3" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="14.25" customHeight="1" s="59">
-      <c r="A53" s="3" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1" s="59">
-      <c r="A54" s="3" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="14.25" customHeight="1" s="59">
-      <c r="A55" s="3" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1" s="59">
-      <c r="A56" s="3" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="14.25" customHeight="1" s="59">
-      <c r="A57" s="3" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1" s="59">
-      <c r="A58" s="3" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="14.25" customHeight="1" s="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="14.25" customHeight="1" s="59">
-      <c r="A60" s="3" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="14.25" customHeight="1" s="59">
-      <c r="A61" s="3" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
+    <row r="51" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="n"/>
+      <c r="C51" s="41" t="n"/>
+      <c r="D51" s="41" t="n"/>
+      <c r="E51" s="41" t="n"/>
+      <c r="F51" s="40">
+        <f>(1.25*K51+N51+P51+U51+W51+X51)/(1-L51-$F$8-$F$4-(1-G51)*$F$3-Y51-AA51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H51" s="45">
+        <f>F51*(1-G51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="46" t="n">
+        <v>478.05</v>
+      </c>
+      <c r="J51" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K51" s="48">
+        <f>I51+J51</f>
+        <v/>
+      </c>
+      <c r="L51" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M51" s="50">
+        <f>F51*L51</f>
+        <v/>
+      </c>
+      <c r="N51" s="51" t="n">
+        <v>72</v>
+      </c>
+      <c r="O51" s="50">
+        <f>F51*$F$8</f>
+        <v/>
+      </c>
+      <c r="P51" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q51" s="50">
+        <f>F51*$F$4</f>
+        <v/>
+      </c>
+      <c r="R51" s="50">
+        <f>H51*$F$3</f>
+        <v/>
+      </c>
+      <c r="S51" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T51" s="51">
+        <f>N51</f>
+        <v/>
+      </c>
+      <c r="U51" s="50">
+        <f>T51*(1-S51)</f>
+        <v/>
+      </c>
+      <c r="V51" s="53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W51" s="50">
+        <f>$F$6*$F$7*V51</f>
+        <v/>
+      </c>
+      <c r="X51" s="48">
+        <f>V51*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y51" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z51" s="50">
+        <f>F51*Y51</f>
+        <v/>
+      </c>
+      <c r="AA51" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB51" s="50">
+        <f>F51*AA51</f>
+        <v/>
+      </c>
+      <c r="AC51" s="50">
+        <f>Z51+AB51</f>
+        <v/>
+      </c>
+      <c r="AD51" s="54">
+        <f>AC51/F51</f>
+        <v/>
+      </c>
+      <c r="AE51" s="33">
+        <f>F51-M51-N51-O51-P51-Q51-R51-U51-W51-X51-K51</f>
+        <v/>
+      </c>
+      <c r="AF51" s="34">
+        <f>AE51-AC51</f>
+        <v/>
+      </c>
+      <c r="AG51" s="35">
+        <f>AF51/F51</f>
+        <v/>
+      </c>
+      <c r="AH51" s="36">
+        <f>AF51/K51</f>
+        <v/>
+      </c>
+      <c r="AI51" s="28">
+        <f>(N51+P51+U51+W51+X51+K51)/(1-(L51+$F$4+(1-G51)*$F$3+$F$8+Y51+AA51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A52" s="65" t="n"/>
+      <c r="B52" s="61" t="n"/>
+      <c r="C52" s="61" t="n"/>
+      <c r="D52" s="61" t="n"/>
+      <c r="E52" s="61" t="n"/>
+      <c r="F52" s="61" t="n"/>
+      <c r="G52" s="61" t="n"/>
+      <c r="H52" s="61" t="n"/>
+      <c r="I52" s="65" t="n"/>
+      <c r="J52" s="61" t="n"/>
+      <c r="K52" s="61" t="n"/>
+      <c r="L52" s="61" t="n"/>
+      <c r="M52" s="61" t="n"/>
+      <c r="N52" s="61" t="n"/>
+      <c r="O52" s="61" t="n"/>
+      <c r="P52" s="61" t="n"/>
+      <c r="Q52" s="61" t="n"/>
+      <c r="R52" s="61" t="n"/>
+      <c r="S52" s="61" t="n"/>
+      <c r="T52" s="61" t="n"/>
+      <c r="U52" s="61" t="n"/>
+      <c r="V52" s="61" t="n"/>
+      <c r="W52" s="61" t="n"/>
+      <c r="X52" s="61" t="n"/>
+      <c r="Y52" s="61" t="n"/>
+      <c r="Z52" s="61" t="n"/>
+      <c r="AA52" s="61" t="n"/>
+      <c r="AB52" s="61" t="n"/>
+      <c r="AC52" s="61" t="n"/>
+      <c r="AD52" s="61" t="n"/>
+      <c r="AE52" s="61" t="n"/>
+      <c r="AF52" s="61" t="n"/>
+      <c r="AG52" s="61" t="n"/>
+      <c r="AH52" s="61" t="n"/>
+      <c r="AI52" s="61" t="n"/>
+    </row>
+    <row r="53" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="41" t="n"/>
+      <c r="D53" s="41" t="n"/>
+      <c r="E53" s="41" t="n"/>
+      <c r="F53" s="40">
+        <f>(1.25*K53+N53+P53+U53+W53+X53)/(1-L53-$F$8-$F$4-(1-G53)*$F$3-Y53-AA53)</f>
+        <v/>
+      </c>
+      <c r="G53" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H53" s="45">
+        <f>F53*(1-G53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="46" t="n">
+        <v>151.13</v>
+      </c>
+      <c r="J53" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K53" s="48">
+        <f>I53+J53</f>
+        <v/>
+      </c>
+      <c r="L53" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M53" s="50">
+        <f>F53*L53</f>
+        <v/>
+      </c>
+      <c r="N53" s="51" t="n">
+        <v>67</v>
+      </c>
+      <c r="O53" s="50">
+        <f>F53*$F$8</f>
+        <v/>
+      </c>
+      <c r="P53" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="50">
+        <f>F53*$F$4</f>
+        <v/>
+      </c>
+      <c r="R53" s="50">
+        <f>H53*$F$3</f>
+        <v/>
+      </c>
+      <c r="S53" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T53" s="51">
+        <f>N53</f>
+        <v/>
+      </c>
+      <c r="U53" s="50">
+        <f>T53*(1-S53)</f>
+        <v/>
+      </c>
+      <c r="V53" s="53" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="W53" s="50">
+        <f>$F$6*$F$7*V53</f>
+        <v/>
+      </c>
+      <c r="X53" s="48">
+        <f>V53*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y53" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z53" s="50">
+        <f>F53*Y53</f>
+        <v/>
+      </c>
+      <c r="AA53" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB53" s="50">
+        <f>F53*AA53</f>
+        <v/>
+      </c>
+      <c r="AC53" s="50">
+        <f>Z53+AB53</f>
+        <v/>
+      </c>
+      <c r="AD53" s="54">
+        <f>AC53/F53</f>
+        <v/>
+      </c>
+      <c r="AE53" s="33">
+        <f>F53-M53-N53-O53-P53-Q53-R53-U53-W53-X53-K53</f>
+        <v/>
+      </c>
+      <c r="AF53" s="34">
+        <f>AE53-AC53</f>
+        <v/>
+      </c>
+      <c r="AG53" s="35">
+        <f>AF53/F53</f>
+        <v/>
+      </c>
+      <c r="AH53" s="36">
+        <f>AF53/K53</f>
+        <v/>
+      </c>
+      <c r="AI53" s="28">
+        <f>(N53+P53+U53+W53+X53+K53)/(1-(L53+$F$4+(1-G53)*$F$3+$F$8+Y53+AA53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
+        </is>
+      </c>
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="41" t="n"/>
+      <c r="D54" s="41" t="n"/>
+      <c r="E54" s="41" t="n"/>
+      <c r="F54" s="40">
+        <f>(1.25*K54+N54+P54+U54+W54+X54)/(1-L54-$F$8-$F$4-(1-G54)*$F$3-Y54-AA54)</f>
+        <v/>
+      </c>
+      <c r="G54" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H54" s="45">
+        <f>F54*(1-G54)</f>
+        <v/>
+      </c>
+      <c r="I54" s="46" t="n">
+        <v>292.89</v>
+      </c>
+      <c r="J54" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K54" s="48">
+        <f>I54+J54</f>
+        <v/>
+      </c>
+      <c r="L54" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M54" s="50">
+        <f>F54*L54</f>
+        <v/>
+      </c>
+      <c r="N54" s="51" t="n">
+        <v>67</v>
+      </c>
+      <c r="O54" s="50">
+        <f>F54*$F$8</f>
+        <v/>
+      </c>
+      <c r="P54" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q54" s="50">
+        <f>F54*$F$4</f>
+        <v/>
+      </c>
+      <c r="R54" s="50">
+        <f>H54*$F$3</f>
+        <v/>
+      </c>
+      <c r="S54" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T54" s="51">
+        <f>N54</f>
+        <v/>
+      </c>
+      <c r="U54" s="50">
+        <f>T54*(1-S54)</f>
+        <v/>
+      </c>
+      <c r="V54" s="53" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W54" s="50">
+        <f>$F$6*$F$7*V54</f>
+        <v/>
+      </c>
+      <c r="X54" s="48">
+        <f>V54*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y54" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z54" s="50">
+        <f>F54*Y54</f>
+        <v/>
+      </c>
+      <c r="AA54" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB54" s="50">
+        <f>F54*AA54</f>
+        <v/>
+      </c>
+      <c r="AC54" s="50">
+        <f>Z54+AB54</f>
+        <v/>
+      </c>
+      <c r="AD54" s="54">
+        <f>AC54/F54</f>
+        <v/>
+      </c>
+      <c r="AE54" s="33">
+        <f>F54-M54-N54-O54-P54-Q54-R54-U54-W54-X54-K54</f>
+        <v/>
+      </c>
+      <c r="AF54" s="34">
+        <f>AE54-AC54</f>
+        <v/>
+      </c>
+      <c r="AG54" s="35">
+        <f>AF54/F54</f>
+        <v/>
+      </c>
+      <c r="AH54" s="36">
+        <f>AF54/K54</f>
+        <v/>
+      </c>
+      <c r="AI54" s="28">
+        <f>(N54+P54+U54+W54+X54+K54)/(1-(L54+$F$4+(1-G54)*$F$3+$F$8+Y54+AA54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="n"/>
+      <c r="C55" s="41" t="n"/>
+      <c r="D55" s="41" t="n"/>
+      <c r="E55" s="41" t="n"/>
+      <c r="F55" s="40">
+        <f>(1.25*K55+N55+P55+U55+W55+X55)/(1-L55-$F$8-$F$4-(1-G55)*$F$3-Y55-AA55)</f>
+        <v/>
+      </c>
+      <c r="G55" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H55" s="45">
+        <f>F55*(1-G55)</f>
+        <v/>
+      </c>
+      <c r="I55" s="46" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="J55" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K55" s="48">
+        <f>I55+J55</f>
+        <v/>
+      </c>
+      <c r="L55" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M55" s="50">
+        <f>F55*L55</f>
+        <v/>
+      </c>
+      <c r="N55" s="51" t="n">
+        <v>72</v>
+      </c>
+      <c r="O55" s="50">
+        <f>F55*$F$8</f>
+        <v/>
+      </c>
+      <c r="P55" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q55" s="50">
+        <f>F55*$F$4</f>
+        <v/>
+      </c>
+      <c r="R55" s="50">
+        <f>H55*$F$3</f>
+        <v/>
+      </c>
+      <c r="S55" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T55" s="51">
+        <f>N55</f>
+        <v/>
+      </c>
+      <c r="U55" s="50">
+        <f>T55*(1-S55)</f>
+        <v/>
+      </c>
+      <c r="V55" s="53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W55" s="50">
+        <f>$F$6*$F$7*V55</f>
+        <v/>
+      </c>
+      <c r="X55" s="48">
+        <f>V55*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y55" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z55" s="50">
+        <f>F55*Y55</f>
+        <v/>
+      </c>
+      <c r="AA55" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB55" s="50">
+        <f>F55*AA55</f>
+        <v/>
+      </c>
+      <c r="AC55" s="50">
+        <f>Z55+AB55</f>
+        <v/>
+      </c>
+      <c r="AD55" s="54">
+        <f>AC55/F55</f>
+        <v/>
+      </c>
+      <c r="AE55" s="33">
+        <f>F55-M55-N55-O55-P55-Q55-R55-U55-W55-X55-K55</f>
+        <v/>
+      </c>
+      <c r="AF55" s="34">
+        <f>AE55-AC55</f>
+        <v/>
+      </c>
+      <c r="AG55" s="35">
+        <f>AF55/F55</f>
+        <v/>
+      </c>
+      <c r="AH55" s="36">
+        <f>AF55/K55</f>
+        <v/>
+      </c>
+      <c r="AI55" s="28">
+        <f>(N55+P55+U55+W55+X55+K55)/(1-(L55+$F$4+(1-G55)*$F$3+$F$8+Y55+AA55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+        </is>
+      </c>
+      <c r="B56" s="44" t="n"/>
+      <c r="C56" s="41" t="n"/>
+      <c r="D56" s="41" t="n"/>
+      <c r="E56" s="41" t="n"/>
+      <c r="F56" s="40">
+        <f>(1.25*K56+N56+P56+U56+W56+X56)/(1-L56-$F$8-$F$4-(1-G56)*$F$3-Y56-AA56)</f>
+        <v/>
+      </c>
+      <c r="G56" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H56" s="45">
+        <f>F56*(1-G56)</f>
+        <v/>
+      </c>
+      <c r="I56" s="46" t="n">
+        <v>770.48</v>
+      </c>
+      <c r="J56" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K56" s="48">
+        <f>I56+J56</f>
+        <v/>
+      </c>
+      <c r="L56" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M56" s="50">
+        <f>F56*L56</f>
+        <v/>
+      </c>
+      <c r="N56" s="51" t="n">
+        <v>56</v>
+      </c>
+      <c r="O56" s="50">
+        <f>F56*$F$8</f>
+        <v/>
+      </c>
+      <c r="P56" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="50">
+        <f>F56*$F$4</f>
+        <v/>
+      </c>
+      <c r="R56" s="50">
+        <f>H56*$F$3</f>
+        <v/>
+      </c>
+      <c r="S56" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T56" s="51">
+        <f>N56</f>
+        <v/>
+      </c>
+      <c r="U56" s="50">
+        <f>T56*(1-S56)</f>
+        <v/>
+      </c>
+      <c r="V56" s="53" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W56" s="50">
+        <f>$F$6*$F$7*V56</f>
+        <v/>
+      </c>
+      <c r="X56" s="48">
+        <f>V56*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y56" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z56" s="50">
+        <f>F56*Y56</f>
+        <v/>
+      </c>
+      <c r="AA56" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB56" s="50">
+        <f>F56*AA56</f>
+        <v/>
+      </c>
+      <c r="AC56" s="50">
+        <f>Z56+AB56</f>
+        <v/>
+      </c>
+      <c r="AD56" s="54">
+        <f>AC56/F56</f>
+        <v/>
+      </c>
+      <c r="AE56" s="33">
+        <f>F56-M56-N56-O56-P56-Q56-R56-U56-W56-X56-K56</f>
+        <v/>
+      </c>
+      <c r="AF56" s="34">
+        <f>AE56-AC56</f>
+        <v/>
+      </c>
+      <c r="AG56" s="35">
+        <f>AF56/F56</f>
+        <v/>
+      </c>
+      <c r="AH56" s="36">
+        <f>AF56/K56</f>
+        <v/>
+      </c>
+      <c r="AI56" s="28">
+        <f>(N56+P56+U56+W56+X56+K56)/(1-(L56+$F$4+(1-G56)*$F$3+$F$8+Y56+AA56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - MASK PACK BLACK [30ml*10ea] - ассорти набор 10шт в упаковке</t>
+        </is>
+      </c>
+      <c r="B57" s="44" t="n"/>
+      <c r="C57" s="41" t="n"/>
+      <c r="D57" s="41" t="n"/>
+      <c r="E57" s="41" t="n"/>
+      <c r="F57" s="40">
+        <f>(1.25*K57+N57+P57+U57+W57+X57)/(1-L57-$F$8-$F$4-(1-G57)*$F$3-Y57-AA57)</f>
+        <v/>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H57" s="45">
+        <f>F57*(1-G57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="46" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="J57" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K57" s="48">
+        <f>I57+J57</f>
+        <v/>
+      </c>
+      <c r="L57" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M57" s="50">
+        <f>F57*L57</f>
+        <v/>
+      </c>
+      <c r="N57" s="51" t="n">
+        <v>72</v>
+      </c>
+      <c r="O57" s="50">
+        <f>F57*$F$8</f>
+        <v/>
+      </c>
+      <c r="P57" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q57" s="50">
+        <f>F57*$F$4</f>
+        <v/>
+      </c>
+      <c r="R57" s="50">
+        <f>H57*$F$3</f>
+        <v/>
+      </c>
+      <c r="S57" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T57" s="51">
+        <f>N57</f>
+        <v/>
+      </c>
+      <c r="U57" s="50">
+        <f>T57*(1-S57)</f>
+        <v/>
+      </c>
+      <c r="V57" s="53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W57" s="50">
+        <f>$F$6*$F$7*V57</f>
+        <v/>
+      </c>
+      <c r="X57" s="48">
+        <f>V57*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y57" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z57" s="50">
+        <f>F57*Y57</f>
+        <v/>
+      </c>
+      <c r="AA57" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB57" s="50">
+        <f>F57*AA57</f>
+        <v/>
+      </c>
+      <c r="AC57" s="50">
+        <f>Z57+AB57</f>
+        <v/>
+      </c>
+      <c r="AD57" s="54">
+        <f>AC57/F57</f>
+        <v/>
+      </c>
+      <c r="AE57" s="33">
+        <f>F57-M57-N57-O57-P57-Q57-R57-U57-W57-X57-K57</f>
+        <v/>
+      </c>
+      <c r="AF57" s="34">
+        <f>AE57-AC57</f>
+        <v/>
+      </c>
+      <c r="AG57" s="35">
+        <f>AF57/F57</f>
+        <v/>
+      </c>
+      <c r="AH57" s="36">
+        <f>AF57/K57</f>
+        <v/>
+      </c>
+      <c r="AI57" s="28">
+        <f>(N57+P57+U57+W57+X57+K57)/(1-(L57+$F$4+(1-G57)*$F$3+$F$8+Y57+AA57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="n"/>
+      <c r="C58" s="41" t="n"/>
+      <c r="D58" s="41" t="n"/>
+      <c r="E58" s="41" t="n"/>
+      <c r="F58" s="40">
+        <f>(1.25*K58+N58+P58+U58+W58+X58)/(1-L58-$F$8-$F$4-(1-G58)*$F$3-Y58-AA58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H58" s="45">
+        <f>F58*(1-G58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="46" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="J58" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K58" s="48">
+        <f>I58+J58</f>
+        <v/>
+      </c>
+      <c r="L58" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M58" s="50">
+        <f>F58*L58</f>
+        <v/>
+      </c>
+      <c r="N58" s="51" t="n">
+        <v>72</v>
+      </c>
+      <c r="O58" s="50">
+        <f>F58*$F$8</f>
+        <v/>
+      </c>
+      <c r="P58" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q58" s="50">
+        <f>F58*$F$4</f>
+        <v/>
+      </c>
+      <c r="R58" s="50">
+        <f>H58*$F$3</f>
+        <v/>
+      </c>
+      <c r="S58" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T58" s="51">
+        <f>N58</f>
+        <v/>
+      </c>
+      <c r="U58" s="50">
+        <f>T58*(1-S58)</f>
+        <v/>
+      </c>
+      <c r="V58" s="53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W58" s="50">
+        <f>$F$6*$F$7*V58</f>
+        <v/>
+      </c>
+      <c r="X58" s="48">
+        <f>V58*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y58" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z58" s="50">
+        <f>F58*Y58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB58" s="50">
+        <f>F58*AA58</f>
+        <v/>
+      </c>
+      <c r="AC58" s="50">
+        <f>Z58+AB58</f>
+        <v/>
+      </c>
+      <c r="AD58" s="54">
+        <f>AC58/F58</f>
+        <v/>
+      </c>
+      <c r="AE58" s="33">
+        <f>F58-M58-N58-O58-P58-Q58-R58-U58-W58-X58-K58</f>
+        <v/>
+      </c>
+      <c r="AF58" s="34">
+        <f>AE58-AC58</f>
+        <v/>
+      </c>
+      <c r="AG58" s="35">
+        <f>AF58/F58</f>
+        <v/>
+      </c>
+      <c r="AH58" s="36">
+        <f>AF58/K58</f>
+        <v/>
+      </c>
+      <c r="AI58" s="28">
+        <f>(N58+P58+U58+W58+X58+K58)/(1-(L58+$F$4+(1-G58)*$F$3+$F$8+Y58+AA58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="n"/>
+      <c r="C59" s="41" t="n"/>
+      <c r="D59" s="41" t="n"/>
+      <c r="E59" s="41" t="n"/>
+      <c r="F59" s="40">
+        <f>(1.25*K59+N59+P59+U59+W59+X59)/(1-L59-$F$8-$F$4-(1-G59)*$F$3-Y59-AA59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H59" s="45">
+        <f>F59*(1-G59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="46" t="n">
+        <v>484.93</v>
+      </c>
+      <c r="J59" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K59" s="48">
+        <f>I59+J59</f>
+        <v/>
+      </c>
+      <c r="L59" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M59" s="50">
+        <f>F59*L59</f>
+        <v/>
+      </c>
+      <c r="N59" s="51" t="n">
+        <v>67</v>
+      </c>
+      <c r="O59" s="50">
+        <f>F59*$F$8</f>
+        <v/>
+      </c>
+      <c r="P59" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="50">
+        <f>F59*$F$4</f>
+        <v/>
+      </c>
+      <c r="R59" s="50">
+        <f>H59*$F$3</f>
+        <v/>
+      </c>
+      <c r="S59" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T59" s="51">
+        <f>N59</f>
+        <v/>
+      </c>
+      <c r="U59" s="50">
+        <f>T59*(1-S59)</f>
+        <v/>
+      </c>
+      <c r="V59" s="53" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="W59" s="50">
+        <f>$F$6*$F$7*V59</f>
+        <v/>
+      </c>
+      <c r="X59" s="48">
+        <f>V59*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y59" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z59" s="50">
+        <f>F59*Y59</f>
+        <v/>
+      </c>
+      <c r="AA59" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB59" s="50">
+        <f>F59*AA59</f>
+        <v/>
+      </c>
+      <c r="AC59" s="50">
+        <f>Z59+AB59</f>
+        <v/>
+      </c>
+      <c r="AD59" s="54">
+        <f>AC59/F59</f>
+        <v/>
+      </c>
+      <c r="AE59" s="33">
+        <f>F59-M59-N59-O59-P59-Q59-R59-U59-W59-X59-K59</f>
+        <v/>
+      </c>
+      <c r="AF59" s="34">
+        <f>AE59-AC59</f>
+        <v/>
+      </c>
+      <c r="AG59" s="35">
+        <f>AF59/F59</f>
+        <v/>
+      </c>
+      <c r="AH59" s="36">
+        <f>AF59/K59</f>
+        <v/>
+      </c>
+      <c r="AI59" s="28">
+        <f>(N59+P59+U59+W59+X59+K59)/(1-(L59+$F$4+(1-G59)*$F$3+$F$8+Y59+AA59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A60" s="39" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="B60" s="44" t="n"/>
+      <c r="C60" s="41" t="n"/>
+      <c r="D60" s="41" t="n"/>
+      <c r="E60" s="41" t="n"/>
+      <c r="F60" s="40">
+        <f>(1.25*K60+N60+P60+U60+W60+X60)/(1-L60-$F$8-$F$4-(1-G60)*$F$3-Y60-AA60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H60" s="45">
+        <f>F60*(1-G60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="46" t="n">
+        <v>1335.95</v>
+      </c>
+      <c r="J60" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K60" s="48">
+        <f>I60+J60</f>
+        <v/>
+      </c>
+      <c r="L60" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M60" s="50">
+        <f>F60*L60</f>
+        <v/>
+      </c>
+      <c r="N60" s="51" t="n">
+        <v>63</v>
+      </c>
+      <c r="O60" s="50">
+        <f>F60*$F$8</f>
+        <v/>
+      </c>
+      <c r="P60" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q60" s="50">
+        <f>F60*$F$4</f>
+        <v/>
+      </c>
+      <c r="R60" s="50">
+        <f>H60*$F$3</f>
+        <v/>
+      </c>
+      <c r="S60" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T60" s="51">
+        <f>N60</f>
+        <v/>
+      </c>
+      <c r="U60" s="50">
+        <f>T60*(1-S60)</f>
+        <v/>
+      </c>
+      <c r="V60" s="53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W60" s="50">
+        <f>$F$6*$F$7*V60</f>
+        <v/>
+      </c>
+      <c r="X60" s="48">
+        <f>V60*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y60" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z60" s="50">
+        <f>F60*Y60</f>
+        <v/>
+      </c>
+      <c r="AA60" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB60" s="50">
+        <f>F60*AA60</f>
+        <v/>
+      </c>
+      <c r="AC60" s="50">
+        <f>Z60+AB60</f>
+        <v/>
+      </c>
+      <c r="AD60" s="54">
+        <f>AC60/F60</f>
+        <v/>
+      </c>
+      <c r="AE60" s="33">
+        <f>F60-M60-N60-O60-P60-Q60-R60-U60-W60-X60-K60</f>
+        <v/>
+      </c>
+      <c r="AF60" s="34">
+        <f>AE60-AC60</f>
+        <v/>
+      </c>
+      <c r="AG60" s="35">
+        <f>AF60/F60</f>
+        <v/>
+      </c>
+      <c r="AH60" s="36">
+        <f>AF60/K60</f>
+        <v/>
+      </c>
+      <c r="AI60" s="28">
+        <f>(N60+P60+U60+W60+X60+K60)/(1-(L60+$F$4+(1-G60)*$F$3+$F$8+Y60+AA60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1" s="59" thickBot="1">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="n"/>
+      <c r="C61" s="41" t="n"/>
+      <c r="D61" s="41" t="n"/>
+      <c r="E61" s="41" t="n"/>
+      <c r="F61" s="40">
+        <f>(1.25*K61+N61+P61+U61+W61+X61)/(1-L61-$F$8-$F$4-(1-G61)*$F$3-Y61-AA61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H61" s="45">
+        <f>F61*(1-G61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="46" t="n">
+        <v>974.04</v>
+      </c>
+      <c r="J61" s="47">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="K61" s="48">
+        <f>I61+J61</f>
+        <v/>
+      </c>
+      <c r="L61" s="49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M61" s="50">
+        <f>F61*L61</f>
+        <v/>
+      </c>
+      <c r="N61" s="51" t="n">
+        <v>63</v>
+      </c>
+      <c r="O61" s="50">
+        <f>F61*$F$8</f>
+        <v/>
+      </c>
+      <c r="P61" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q61" s="50">
+        <f>F61*$F$4</f>
+        <v/>
+      </c>
+      <c r="R61" s="50">
+        <f>H61*$F$3</f>
+        <v/>
+      </c>
+      <c r="S61" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T61" s="51">
+        <f>N61</f>
+        <v/>
+      </c>
+      <c r="U61" s="50">
+        <f>T61*(1-S61)</f>
+        <v/>
+      </c>
+      <c r="V61" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W61" s="50">
+        <f>$F$6*$F$7*V61</f>
+        <v/>
+      </c>
+      <c r="X61" s="48">
+        <f>V61*($F$9+$F$10)</f>
+        <v/>
+      </c>
+      <c r="Y61" s="49" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Z61" s="50">
+        <f>F61*Y61</f>
+        <v/>
+      </c>
+      <c r="AA61" s="52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB61" s="50">
+        <f>F61*AA61</f>
+        <v/>
+      </c>
+      <c r="AC61" s="50">
+        <f>Z61+AB61</f>
+        <v/>
+      </c>
+      <c r="AD61" s="54">
+        <f>AC61/F61</f>
+        <v/>
+      </c>
+      <c r="AE61" s="33">
+        <f>F61-M61-N61-O61-P61-Q61-R61-U61-W61-X61-K61</f>
+        <v/>
+      </c>
+      <c r="AF61" s="34">
+        <f>AE61-AC61</f>
+        <v/>
+      </c>
+      <c r="AG61" s="35">
+        <f>AF61/F61</f>
+        <v/>
+      </c>
+      <c r="AH61" s="36">
+        <f>AF61/K61</f>
+        <v/>
+      </c>
+      <c r="AI61" s="28">
+        <f>(N61+P61+U61+W61+X61+K61)/(1-(L61+$F$4+(1-G61)*$F$3+$F$8+Y61+AA61))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" s="59">
       <c r="A62" s="3" t="n"/>
@@ -11897,18 +13124,6 @@
       <c r="C1003" s="2" t="n"/>
       <c r="D1003" s="2" t="n"/>
       <c r="E1003" s="2" t="n"/>
-    </row>
-    <row r="1004" ht="14.25" customHeight="1" s="59">
-      <c r="A1004" s="3" t="n"/>
-      <c r="C1004" s="2" t="n"/>
-      <c r="D1004" s="2" t="n"/>
-      <c r="E1004" s="2" t="n"/>
-    </row>
-    <row r="1005" ht="14.25" customHeight="1" s="59">
-      <c r="A1005" s="3" t="n"/>
-      <c r="C1005" s="2" t="n"/>
-      <c r="D1005" s="2" t="n"/>
-      <c r="E1005" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11919,497 +13134,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="71" t="inlineStr">
-        <is>
-          <t>Объём от, л</t>
-        </is>
-      </c>
-      <c r="B1" s="71" t="inlineStr">
-        <is>
-          <t>Тариф &gt;300₽</t>
-        </is>
-      </c>
-      <c r="C1" s="71" t="inlineStr">
-        <is>
-          <t>Тариф до300₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>56</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="B3" t="n">
-        <v>63</v>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="B4" t="n">
-        <v>67</v>
-      </c>
-      <c r="C4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="B5" t="n">
-        <v>67</v>
-      </c>
-      <c r="C5" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="B6" t="n">
-        <v>67</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="B7" t="n">
-        <v>72</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1.251</v>
-      </c>
-      <c r="B8" t="n">
-        <v>75</v>
-      </c>
-      <c r="C8" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1.501</v>
-      </c>
-      <c r="B9" t="n">
-        <v>75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1.751</v>
-      </c>
-      <c r="B10" t="n">
-        <v>75</v>
-      </c>
-      <c r="C10" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2.001</v>
-      </c>
-      <c r="B11" t="n">
-        <v>75</v>
-      </c>
-      <c r="C11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3.001</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78</v>
-      </c>
-      <c r="C12" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>4.001</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89</v>
-      </c>
-      <c r="C13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>5.001</v>
-      </c>
-      <c r="B14" t="n">
-        <v>89</v>
-      </c>
-      <c r="C14" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>6.001</v>
-      </c>
-      <c r="B15" t="n">
-        <v>99</v>
-      </c>
-      <c r="C15" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>7.001</v>
-      </c>
-      <c r="B16" t="n">
-        <v>99</v>
-      </c>
-      <c r="C16" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>8.000999999999999</v>
-      </c>
-      <c r="B17" t="n">
-        <v>100</v>
-      </c>
-      <c r="C17" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>9.000999999999999</v>
-      </c>
-      <c r="B18" t="n">
-        <v>100</v>
-      </c>
-      <c r="C18" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>10.001</v>
-      </c>
-      <c r="B19" t="n">
-        <v>102</v>
-      </c>
-      <c r="C19" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>11.001</v>
-      </c>
-      <c r="B20" t="n">
-        <v>102</v>
-      </c>
-      <c r="C20" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>12.001</v>
-      </c>
-      <c r="B21" t="n">
-        <v>102</v>
-      </c>
-      <c r="C21" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>13.001</v>
-      </c>
-      <c r="B22" t="n">
-        <v>106</v>
-      </c>
-      <c r="C22" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>14.001</v>
-      </c>
-      <c r="B23" t="n">
-        <v>111</v>
-      </c>
-      <c r="C23" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>15.001</v>
-      </c>
-      <c r="B24" t="n">
-        <v>119</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>17.001</v>
-      </c>
-      <c r="B25" t="n">
-        <v>131</v>
-      </c>
-      <c r="C25" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20.001</v>
-      </c>
-      <c r="B26" t="n">
-        <v>143</v>
-      </c>
-      <c r="C26" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25.001</v>
-      </c>
-      <c r="B27" t="n">
-        <v>162</v>
-      </c>
-      <c r="C27" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>30.001</v>
-      </c>
-      <c r="B28" t="n">
-        <v>177</v>
-      </c>
-      <c r="C28" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>35.001</v>
-      </c>
-      <c r="B29" t="n">
-        <v>195</v>
-      </c>
-      <c r="C29" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>40.001</v>
-      </c>
-      <c r="B30" t="n">
-        <v>209</v>
-      </c>
-      <c r="C30" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>45.001</v>
-      </c>
-      <c r="B31" t="n">
-        <v>228</v>
-      </c>
-      <c r="C31" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>50.001</v>
-      </c>
-      <c r="B32" t="n">
-        <v>244</v>
-      </c>
-      <c r="C32" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>60.001</v>
-      </c>
-      <c r="B33" t="n">
-        <v>279</v>
-      </c>
-      <c r="C33" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>70.001</v>
-      </c>
-      <c r="B34" t="n">
-        <v>299</v>
-      </c>
-      <c r="C34" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>80.001</v>
-      </c>
-      <c r="B35" t="n">
-        <v>344</v>
-      </c>
-      <c r="C35" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>90.001</v>
-      </c>
-      <c r="B36" t="n">
-        <v>371</v>
-      </c>
-      <c r="C36" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>100.001</v>
-      </c>
-      <c r="B37" t="n">
-        <v>436</v>
-      </c>
-      <c r="C37" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>125.001</v>
-      </c>
-      <c r="B38" t="n">
-        <v>503</v>
-      </c>
-      <c r="C38" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>150.001</v>
-      </c>
-      <c r="B39" t="n">
-        <v>578</v>
-      </c>
-      <c r="C39" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>175.001</v>
-      </c>
-      <c r="B40" t="n">
-        <v>692</v>
-      </c>
-      <c r="C40" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>200.001</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1026</v>
-      </c>
-      <c r="C41" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>400.001</v>
-      </c>
-      <c r="B42" t="n">
-        <v>1457</v>
-      </c>
-      <c r="C42" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>600.001</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1891</v>
-      </c>
-      <c r="C43" t="n">
-        <v>577</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -7,9 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Юнитка Ozon (live)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тариф логистики" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -143,6 +144,9 @@
       <color theme="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -206,7 +210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -464,11 +468,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -626,6 +644,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1803,8 +1823,9 @@
         <f>F13*L13</f>
         <v/>
       </c>
-      <c r="N13" s="29" t="n">
-        <v>67</v>
+      <c r="N13" s="81">
+        <f>VLOOKUP(V13,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O13" s="28">
         <f>F13*$F$8</f>
@@ -1931,8 +1952,8 @@
         <f>F14*L14</f>
         <v/>
       </c>
-      <c r="N14" s="28">
-        <f>VLOOKUP(V14,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N14" s="81">
+        <f>VLOOKUP(V14,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O14" s="28">
@@ -2060,8 +2081,8 @@
         <f>F15*L15</f>
         <v/>
       </c>
-      <c r="N15" s="28">
-        <f>VLOOKUP(V15,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N15" s="81">
+        <f>VLOOKUP(V15,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O15" s="28">
@@ -2189,8 +2210,8 @@
         <f>F16*L16</f>
         <v/>
       </c>
-      <c r="N16" s="28">
-        <f>VLOOKUP(V16,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N16" s="81">
+        <f>VLOOKUP(V16,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O16" s="28">
@@ -2318,8 +2339,8 @@
         <f>F17*L17</f>
         <v/>
       </c>
-      <c r="N17" s="28">
-        <f>VLOOKUP(V17,'[1]Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+      <c r="N17" s="81">
+        <f>VLOOKUP(V17,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
         <v/>
       </c>
       <c r="O17" s="28">
@@ -2445,8 +2466,9 @@
         <f>F18*L18</f>
         <v/>
       </c>
-      <c r="N18" s="29" t="n">
-        <v>74</v>
+      <c r="N18" s="81">
+        <f>VLOOKUP(V18,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O18" s="28">
         <f>F18*$F$8</f>
@@ -2571,8 +2593,9 @@
         <f>F19*L19</f>
         <v/>
       </c>
-      <c r="N19" s="29" t="n">
-        <v>67</v>
+      <c r="N19" s="81">
+        <f>VLOOKUP(V19,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O19" s="28">
         <f>F19*$F$8</f>
@@ -2697,8 +2720,9 @@
         <f>F20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="29" t="n">
-        <v>67</v>
+      <c r="N20" s="81">
+        <f>VLOOKUP(V20,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O20" s="28">
         <f>F20*$F$8</f>
@@ -2823,8 +2847,9 @@
         <f>F21*L21</f>
         <v/>
       </c>
-      <c r="N21" s="29" t="n">
-        <v>67</v>
+      <c r="N21" s="81">
+        <f>VLOOKUP(V21,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O21" s="28">
         <f>F21*$F$8</f>
@@ -2949,8 +2974,9 @@
         <f>F22*L22</f>
         <v/>
       </c>
-      <c r="N22" s="29" t="n">
-        <v>75</v>
+      <c r="N22" s="81">
+        <f>VLOOKUP(V22,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O22" s="28">
         <f>F22*$F$8</f>
@@ -3075,8 +3101,9 @@
         <f>F23*L23</f>
         <v/>
       </c>
-      <c r="N23" s="29" t="n">
-        <v>67</v>
+      <c r="N23" s="81">
+        <f>VLOOKUP(V23,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O23" s="28">
         <f>F23*$F$8</f>
@@ -3201,8 +3228,9 @@
         <f>F24*L24</f>
         <v/>
       </c>
-      <c r="N24" s="29" t="n">
-        <v>67</v>
+      <c r="N24" s="81">
+        <f>VLOOKUP(V24,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O24" s="28">
         <f>F24*$F$8</f>
@@ -3328,8 +3356,9 @@
         <f>F25*L25</f>
         <v/>
       </c>
-      <c r="N25" s="29" t="n">
-        <v>63</v>
+      <c r="N25" s="81">
+        <f>VLOOKUP(V25,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O25" s="28">
         <f>F25*$F$8</f>
@@ -3455,8 +3484,9 @@
         <f>F26*L26</f>
         <v/>
       </c>
-      <c r="N26" s="29" t="n">
-        <v>63</v>
+      <c r="N26" s="81">
+        <f>VLOOKUP(V26,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O26" s="28">
         <f>F26*$F$8</f>
@@ -3586,8 +3616,9 @@
         <f>F27*L27</f>
         <v/>
       </c>
-      <c r="N27" s="29" t="n">
-        <v>56</v>
+      <c r="N27" s="81">
+        <f>VLOOKUP(V27,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O27" s="28">
         <f>F27*$F$8</f>
@@ -3717,8 +3748,9 @@
         <f>F28*L28</f>
         <v/>
       </c>
-      <c r="N28" s="29" t="n">
-        <v>67</v>
+      <c r="N28" s="81">
+        <f>VLOOKUP(V28,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O28" s="28">
         <f>F28*$F$8</f>
@@ -3848,8 +3880,9 @@
         <f>F29*L29</f>
         <v/>
       </c>
-      <c r="N29" s="29" t="n">
-        <v>67</v>
+      <c r="N29" s="81">
+        <f>VLOOKUP(V29,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O29" s="28">
         <f>F29*$F$8</f>
@@ -3975,8 +4008,9 @@
         <f>F30*L30</f>
         <v/>
       </c>
-      <c r="N30" s="29" t="n">
-        <v>75</v>
+      <c r="N30" s="81">
+        <f>VLOOKUP(V30,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O30" s="28">
         <f>F30*$F$8</f>
@@ -4101,8 +4135,9 @@
         <f>F31*L31</f>
         <v/>
       </c>
-      <c r="N31" s="51" t="n">
-        <v>63</v>
+      <c r="N31" s="81">
+        <f>VLOOKUP(V31,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O31" s="50">
         <f>F31*$F$8</f>
@@ -4229,8 +4264,9 @@
         <f>F33*L33</f>
         <v/>
       </c>
-      <c r="N33" s="51" t="n">
-        <v>67</v>
+      <c r="N33" s="81">
+        <f>VLOOKUP(V33,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O33" s="50">
         <f>F33*$F$8</f>
@@ -4351,8 +4387,9 @@
         <f>F34*L34</f>
         <v/>
       </c>
-      <c r="N34" s="51" t="n">
-        <v>67</v>
+      <c r="N34" s="81">
+        <f>VLOOKUP(V34,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O34" s="50">
         <f>F34*$F$8</f>
@@ -4473,8 +4510,9 @@
         <f>F35*L35</f>
         <v/>
       </c>
-      <c r="N35" s="51" t="n">
-        <v>67</v>
+      <c r="N35" s="81">
+        <f>VLOOKUP(V35,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O35" s="50">
         <f>F35*$F$8</f>
@@ -4595,8 +4633,9 @@
         <f>F36*L36</f>
         <v/>
       </c>
-      <c r="N36" s="51" t="n">
-        <v>67</v>
+      <c r="N36" s="81">
+        <f>VLOOKUP(V36,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O36" s="50">
         <f>F36*$F$8</f>
@@ -4717,8 +4756,9 @@
         <f>F37*L37</f>
         <v/>
       </c>
-      <c r="N37" s="51" t="n">
-        <v>67</v>
+      <c r="N37" s="81">
+        <f>VLOOKUP(V37,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O37" s="50">
         <f>F37*$F$8</f>
@@ -4839,8 +4879,9 @@
         <f>F38*L38</f>
         <v/>
       </c>
-      <c r="N38" s="51" t="n">
-        <v>67</v>
+      <c r="N38" s="81">
+        <f>VLOOKUP(V38,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O38" s="50">
         <f>F38*$F$8</f>
@@ -4961,8 +5002,9 @@
         <f>F39*L39</f>
         <v/>
       </c>
-      <c r="N39" s="51" t="n">
-        <v>67</v>
+      <c r="N39" s="81">
+        <f>VLOOKUP(V39,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O39" s="50">
         <f>F39*$F$8</f>
@@ -5120,8 +5162,9 @@
         <f>F41*L41</f>
         <v/>
       </c>
-      <c r="N41" s="51" t="n">
-        <v>67</v>
+      <c r="N41" s="81">
+        <f>VLOOKUP(V41,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O41" s="50">
         <f>F41*$F$8</f>
@@ -5242,8 +5285,9 @@
         <f>F42*L42</f>
         <v/>
       </c>
-      <c r="N42" s="51" t="n">
-        <v>67</v>
+      <c r="N42" s="81">
+        <f>VLOOKUP(V42,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O42" s="50">
         <f>F42*$F$8</f>
@@ -5364,8 +5408,9 @@
         <f>F43*L43</f>
         <v/>
       </c>
-      <c r="N43" s="51" t="n">
-        <v>67</v>
+      <c r="N43" s="81">
+        <f>VLOOKUP(V43,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O43" s="50">
         <f>F43*$F$8</f>
@@ -5486,8 +5531,9 @@
         <f>F44*L44</f>
         <v/>
       </c>
-      <c r="N44" s="51" t="n">
-        <v>67</v>
+      <c r="N44" s="81">
+        <f>VLOOKUP(V44,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O44" s="50">
         <f>F44*$F$8</f>
@@ -5645,8 +5691,9 @@
         <f>F46*L46</f>
         <v/>
       </c>
-      <c r="N46" s="51" t="n">
-        <v>72</v>
+      <c r="N46" s="81">
+        <f>VLOOKUP(V46,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O46" s="50">
         <f>F46*$F$8</f>
@@ -5767,8 +5814,9 @@
         <f>F47*L47</f>
         <v/>
       </c>
-      <c r="N47" s="51" t="n">
-        <v>72</v>
+      <c r="N47" s="81">
+        <f>VLOOKUP(V47,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O47" s="50">
         <f>F47*$F$8</f>
@@ -5889,8 +5937,9 @@
         <f>F48*L48</f>
         <v/>
       </c>
-      <c r="N48" s="51" t="n">
-        <v>72</v>
+      <c r="N48" s="81">
+        <f>VLOOKUP(V48,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O48" s="50">
         <f>F48*$F$8</f>
@@ -6011,8 +6060,9 @@
         <f>F49*L49</f>
         <v/>
       </c>
-      <c r="N49" s="51" t="n">
-        <v>72</v>
+      <c r="N49" s="81">
+        <f>VLOOKUP(V49,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O49" s="50">
         <f>F49*$F$8</f>
@@ -6133,8 +6183,9 @@
         <f>F50*L50</f>
         <v/>
       </c>
-      <c r="N50" s="51" t="n">
-        <v>72</v>
+      <c r="N50" s="81">
+        <f>VLOOKUP(V50,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O50" s="50">
         <f>F50*$F$8</f>
@@ -6255,8 +6306,9 @@
         <f>F51*L51</f>
         <v/>
       </c>
-      <c r="N51" s="51" t="n">
-        <v>72</v>
+      <c r="N51" s="81">
+        <f>VLOOKUP(V51,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O51" s="50">
         <f>F51*$F$8</f>
@@ -6414,8 +6466,9 @@
         <f>F53*L53</f>
         <v/>
       </c>
-      <c r="N53" s="51" t="n">
-        <v>67</v>
+      <c r="N53" s="81">
+        <f>VLOOKUP(V53,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O53" s="50">
         <f>F53*$F$8</f>
@@ -6536,8 +6589,9 @@
         <f>F54*L54</f>
         <v/>
       </c>
-      <c r="N54" s="51" t="n">
-        <v>67</v>
+      <c r="N54" s="81">
+        <f>VLOOKUP(V54,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O54" s="50">
         <f>F54*$F$8</f>
@@ -6658,8 +6712,9 @@
         <f>F55*L55</f>
         <v/>
       </c>
-      <c r="N55" s="51" t="n">
-        <v>72</v>
+      <c r="N55" s="81">
+        <f>VLOOKUP(V55,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O55" s="50">
         <f>F55*$F$8</f>
@@ -6780,8 +6835,9 @@
         <f>F56*L56</f>
         <v/>
       </c>
-      <c r="N56" s="51" t="n">
-        <v>56</v>
+      <c r="N56" s="81">
+        <f>VLOOKUP(V56,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O56" s="50">
         <f>F56*$F$8</f>
@@ -6902,8 +6958,9 @@
         <f>F57*L57</f>
         <v/>
       </c>
-      <c r="N57" s="51" t="n">
-        <v>72</v>
+      <c r="N57" s="81">
+        <f>VLOOKUP(V57,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O57" s="50">
         <f>F57*$F$8</f>
@@ -7024,8 +7081,9 @@
         <f>F58*L58</f>
         <v/>
       </c>
-      <c r="N58" s="51" t="n">
-        <v>72</v>
+      <c r="N58" s="81">
+        <f>VLOOKUP(V58,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O58" s="50">
         <f>F58*$F$8</f>
@@ -7146,8 +7204,9 @@
         <f>F59*L59</f>
         <v/>
       </c>
-      <c r="N59" s="51" t="n">
-        <v>67</v>
+      <c r="N59" s="81">
+        <f>VLOOKUP(V59,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O59" s="50">
         <f>F59*$F$8</f>
@@ -7268,8 +7327,9 @@
         <f>F60*L60</f>
         <v/>
       </c>
-      <c r="N60" s="51" t="n">
-        <v>63</v>
+      <c r="N60" s="81">
+        <f>VLOOKUP(V60,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O60" s="50">
         <f>F60*$F$8</f>
@@ -7390,8 +7450,9 @@
         <f>F61*L61</f>
         <v/>
       </c>
-      <c r="N61" s="51" t="n">
-        <v>63</v>
+      <c r="N61" s="81">
+        <f>VLOOKUP(V61,'Тариф логистики'!$A$2:$C$43,2,TRUE)</f>
+        <v/>
       </c>
       <c r="O61" s="50">
         <f>F61*$F$8</f>
@@ -13134,4 +13195,497 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="82" t="inlineStr">
+        <is>
+          <t>Объём от, л</t>
+        </is>
+      </c>
+      <c r="B1" s="82" t="inlineStr">
+        <is>
+          <t>Тариф &gt;300₽</t>
+        </is>
+      </c>
+      <c r="C1" s="82" t="inlineStr">
+        <is>
+          <t>Тариф до300₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="B6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4.001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5.001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.000999999999999</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9.000999999999999</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102</v>
+      </c>
+      <c r="C19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>11.001</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>12.001</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>13.001</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>14.001</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111</v>
+      </c>
+      <c r="C23" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>15.001</v>
+      </c>
+      <c r="B24" t="n">
+        <v>119</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17.001</v>
+      </c>
+      <c r="B25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20.001</v>
+      </c>
+      <c r="B26" t="n">
+        <v>143</v>
+      </c>
+      <c r="C26" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25.001</v>
+      </c>
+      <c r="B27" t="n">
+        <v>162</v>
+      </c>
+      <c r="C27" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30.001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>177</v>
+      </c>
+      <c r="C28" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>35.001</v>
+      </c>
+      <c r="B29" t="n">
+        <v>195</v>
+      </c>
+      <c r="C29" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40.001</v>
+      </c>
+      <c r="B30" t="n">
+        <v>209</v>
+      </c>
+      <c r="C30" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>45.001</v>
+      </c>
+      <c r="B31" t="n">
+        <v>228</v>
+      </c>
+      <c r="C31" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>50.001</v>
+      </c>
+      <c r="B32" t="n">
+        <v>244</v>
+      </c>
+      <c r="C32" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>60.001</v>
+      </c>
+      <c r="B33" t="n">
+        <v>279</v>
+      </c>
+      <c r="C33" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>70.001</v>
+      </c>
+      <c r="B34" t="n">
+        <v>299</v>
+      </c>
+      <c r="C34" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80.001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>344</v>
+      </c>
+      <c r="C35" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>90.001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>371</v>
+      </c>
+      <c r="C36" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>100.001</v>
+      </c>
+      <c r="B37" t="n">
+        <v>436</v>
+      </c>
+      <c r="C37" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125.001</v>
+      </c>
+      <c r="B38" t="n">
+        <v>503</v>
+      </c>
+      <c r="C38" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>150.001</v>
+      </c>
+      <c r="B39" t="n">
+        <v>578</v>
+      </c>
+      <c r="C39" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>175.001</v>
+      </c>
+      <c r="B40" t="n">
+        <v>692</v>
+      </c>
+      <c r="C40" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>200.001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1026</v>
+      </c>
+      <c r="C41" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>400.001</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1457</v>
+      </c>
+      <c r="C42" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>600.001</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1891</v>
+      </c>
+      <c r="C43" t="n">
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
+++ b/outputs/ozon/ozon_unit_model_live_2026-08-03.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -147,8 +147,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -207,6 +211,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD0E0E3"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -486,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -646,6 +665,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="13" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1402,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1003"/>
+  <dimension ref="A1:AK1003"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="78" customWidth="1" style="59" min="1" max="1"/>
@@ -1437,6 +1461,8 @@
     <col width="9.7265625" customWidth="1" style="59" min="33" max="33"/>
     <col width="6.453125" customWidth="1" style="59" min="34" max="34"/>
     <col width="9.08984375" customWidth="1" style="59" min="35" max="35"/>
+    <col width="13" customWidth="1" style="59" min="36" max="36"/>
+    <col width="14" customWidth="1" style="59" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="59">
@@ -1776,6 +1802,16 @@
           <t>Цена безубыт.</t>
         </is>
       </c>
+      <c r="AJ12" s="83" t="inlineStr">
+        <is>
+          <t>Цена с СПП (ввод)</t>
+        </is>
+      </c>
+      <c r="AK12" s="83" t="inlineStr">
+        <is>
+          <t>Цена без СПП (÷0,55)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="59">
       <c r="A13" s="39" t="inlineStr">
@@ -1906,6 +1942,11 @@
         <f>(N13+P13+U13+W13+X13+K13)/(1-(L13+$F$4+(1-G13)*$F$3+$F$8+Y13+AA13))</f>
         <v/>
       </c>
+      <c r="AJ13" s="84" t="n"/>
+      <c r="AK13" s="85">
+        <f>IF(AJ13="","",AJ13/(1-G13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" s="59">
       <c r="A14" s="39" t="inlineStr">
@@ -2035,6 +2076,11 @@
         <f>(N14+P14+U14+W14+X14+K14)/(1-(L14+$F$4+(1-G14)*$F$3+$F$8+Y14+AA14))</f>
         <v/>
       </c>
+      <c r="AJ14" s="84" t="n"/>
+      <c r="AK14" s="85">
+        <f>IF(AJ14="","",AJ14/(1-G14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="59">
       <c r="A15" s="39" t="inlineStr">
@@ -2164,6 +2210,11 @@
         <f>(N15+P15+U15+W15+X15+K15)/(1-(L15+$F$4+(1-G15)*$F$3+$F$8+Y15+AA15))</f>
         <v/>
       </c>
+      <c r="AJ15" s="84" t="n"/>
+      <c r="AK15" s="85">
+        <f>IF(AJ15="","",AJ15/(1-G15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="59">
       <c r="A16" s="39" t="inlineStr">
@@ -2293,6 +2344,11 @@
         <f>(N16+P16+U16+W16+X16+K16)/(1-(L16+$F$4+(1-G16)*$F$3+$F$8+Y16+AA16))</f>
         <v/>
       </c>
+      <c r="AJ16" s="84" t="n"/>
+      <c r="AK16" s="85">
+        <f>IF(AJ16="","",AJ16/(1-G16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" s="59">
       <c r="A17" s="39" t="inlineStr">
@@ -2422,6 +2478,11 @@
         <f>(N17+P17+U17+W17+X17+K17)/(1-(L17+$F$4+(1-G17)*$F$3+$F$8+Y17+AA17))</f>
         <v/>
       </c>
+      <c r="AJ17" s="84" t="n"/>
+      <c r="AK17" s="85">
+        <f>IF(AJ17="","",AJ17/(1-G17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" s="59">
       <c r="A18" s="39" t="inlineStr">
@@ -2549,6 +2610,11 @@
         <f>(N18+P18+U18+W18+X18+K18)/(1-(L18+$F$4+(1-G18)*$F$3+$F$8+Y18+AA18))</f>
         <v/>
       </c>
+      <c r="AJ18" s="84" t="n"/>
+      <c r="AK18" s="85">
+        <f>IF(AJ18="","",AJ18/(1-G18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" s="59">
       <c r="A19" s="39" t="inlineStr">
@@ -2676,6 +2742,11 @@
         <f>(N19+P19+U19+W19+X19+K19)/(1-(L19+$F$4+(1-G19)*$F$3+$F$8+Y19+AA19))</f>
         <v/>
       </c>
+      <c r="AJ19" s="84" t="n"/>
+      <c r="AK19" s="85">
+        <f>IF(AJ19="","",AJ19/(1-G19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="14.25" customHeight="1" s="59">
       <c r="A20" s="39" t="inlineStr">
@@ -2803,6 +2874,11 @@
         <f>(N20+P20+U20+W20+X20+K20)/(1-(L20+$F$4+(1-G20)*$F$3+$F$8+Y20+AA20))</f>
         <v/>
       </c>
+      <c r="AJ20" s="84" t="n"/>
+      <c r="AK20" s="85">
+        <f>IF(AJ20="","",AJ20/(1-G20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" s="59">
       <c r="A21" s="39" t="inlineStr">
@@ -2930,6 +3006,11 @@
         <f>(N21+P21+U21+W21+X21+K21)/(1-(L21+$F$4+(1-G21)*$F$3+$F$8+Y21+AA21))</f>
         <v/>
       </c>
+      <c r="AJ21" s="84" t="n"/>
+      <c r="AK21" s="85">
+        <f>IF(AJ21="","",AJ21/(1-G21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" s="59">
       <c r="A22" s="39" t="inlineStr">
@@ -3057,6 +3138,11 @@
         <f>(N22+P22+U22+W22+X22+K22)/(1-(L22+$F$4+(1-G22)*$F$3+$F$8+Y22+AA22))</f>
         <v/>
       </c>
+      <c r="AJ22" s="84" t="n"/>
+      <c r="AK22" s="85">
+        <f>IF(AJ22="","",AJ22/(1-G22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" s="59">
       <c r="A23" s="39" t="inlineStr">
@@ -3184,6 +3270,11 @@
         <f>(N23+P23+U23+W23+X23+K23)/(1-(L23+$F$4+(1-G23)*$F$3+$F$8+Y23+AA23))</f>
         <v/>
       </c>
+      <c r="AJ23" s="84" t="n"/>
+      <c r="AK23" s="85">
+        <f>IF(AJ23="","",AJ23/(1-G23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="59">
       <c r="A24" s="39" t="inlineStr">
@@ -3311,6 +3402,11 @@
         <f>(N24+P24+U24+W24+X24+K24)/(1-(L24+$F$4+(1-G24)*$F$3+$F$8+Y24+AA24))</f>
         <v/>
       </c>
+      <c r="AJ24" s="84" t="n"/>
+      <c r="AK24" s="85">
+        <f>IF(AJ24="","",AJ24/(1-G24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="59">
       <c r="A25" s="39" t="inlineStr">
@@ -3439,6 +3535,11 @@
         <f>(N25+P25+U25+W25+X25+K25)/(1-(L25+$F$4+(1-G25)*$F$3+$F$8+Y25+AA25))</f>
         <v/>
       </c>
+      <c r="AJ25" s="84" t="n"/>
+      <c r="AK25" s="85">
+        <f>IF(AJ25="","",AJ25/(1-G25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="59">
       <c r="A26" s="39" t="inlineStr">
@@ -3567,6 +3668,11 @@
         <f>(N26+P26+U26+W26+X26+K26)/(1-(L26+$F$4+(1-G26)*$F$3+$F$8+Y26+AA26))</f>
         <v/>
       </c>
+      <c r="AJ26" s="84" t="n"/>
+      <c r="AK26" s="85">
+        <f>IF(AJ26="","",AJ26/(1-G26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="59">
       <c r="A27" s="39" t="inlineStr">
@@ -3699,6 +3805,11 @@
         <f>(N27+P27+U27+W27+X27+K27)/(1-(L27+$F$4+(1-G27)*$F$3+$F$8+Y27+AA27))</f>
         <v/>
       </c>
+      <c r="AJ27" s="84" t="n"/>
+      <c r="AK27" s="85">
+        <f>IF(AJ27="","",AJ27/(1-G27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" s="59">
       <c r="A28" s="39" t="inlineStr">
@@ -3831,6 +3942,11 @@
         <f>(N28+P28+U28+W28+X28+K28)/(1-(L28+$F$4+(1-G28)*$F$3+$F$8+Y28+AA28))</f>
         <v/>
       </c>
+      <c r="AJ28" s="84" t="n"/>
+      <c r="AK28" s="85">
+        <f>IF(AJ28="","",AJ28/(1-G28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="14.25" customHeight="1" s="59">
       <c r="A29" s="39" t="inlineStr">
@@ -3963,6 +4079,11 @@
         <f>(N29+P29+U29+W29+X29+K29)/(1-(L29+$F$4+(1-G29)*$F$3+$F$8+Y29+AA29))</f>
         <v/>
       </c>
+      <c r="AJ29" s="84" t="n"/>
+      <c r="AK29" s="85">
+        <f>IF(AJ29="","",AJ29/(1-G29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="14.25" customHeight="1" s="59">
       <c r="A30" s="39" t="inlineStr">
@@ -4091,6 +4212,11 @@
         <f>(N30+P30+U30+W30+X30+K30)/(1-(L30+$F$4+(1-G30)*$F$3+$F$8+Y30+AA30))</f>
         <v/>
       </c>
+      <c r="AJ30" s="84" t="n"/>
+      <c r="AK30" s="85">
+        <f>IF(AJ30="","",AJ30/(1-G30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="59">
       <c r="A31" s="39" t="inlineStr">
@@ -4216,6 +4342,11 @@
       </c>
       <c r="AI31" s="28">
         <f>(N31+P31+U31+W31+X31+K31)/(1-(L31+$F$4+(1-G31)*$F$3+$F$8+Y31+AA31))</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="84" t="n"/>
+      <c r="AK31" s="85">
+        <f>IF(AJ31="","",AJ31/(1-G31))</f>
         <v/>
       </c>
     </row>
@@ -4347,6 +4478,11 @@
         <f>(N33+P33+U33+W33+X33+K33)/(1-(L33+$F$4+(1-G33)*$F$3+$F$8+Y33+AA33))</f>
         <v/>
       </c>
+      <c r="AJ33" s="84" t="n"/>
+      <c r="AK33" s="85">
+        <f>IF(AJ33="","",AJ33/(1-G33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A34" s="39" t="inlineStr">
@@ -4470,6 +4606,11 @@
         <f>(N34+P34+U34+W34+X34+K34)/(1-(L34+$F$4+(1-G34)*$F$3+$F$8+Y34+AA34))</f>
         <v/>
       </c>
+      <c r="AJ34" s="84" t="n"/>
+      <c r="AK34" s="85">
+        <f>IF(AJ34="","",AJ34/(1-G34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A35" s="39" t="inlineStr">
@@ -4593,6 +4734,11 @@
         <f>(N35+P35+U35+W35+X35+K35)/(1-(L35+$F$4+(1-G35)*$F$3+$F$8+Y35+AA35))</f>
         <v/>
       </c>
+      <c r="AJ35" s="84" t="n"/>
+      <c r="AK35" s="85">
+        <f>IF(AJ35="","",AJ35/(1-G35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A36" s="39" t="inlineStr">
@@ -4716,6 +4862,11 @@
         <f>(N36+P36+U36+W36+X36+K36)/(1-(L36+$F$4+(1-G36)*$F$3+$F$8+Y36+AA36))</f>
         <v/>
       </c>
+      <c r="AJ36" s="84" t="n"/>
+      <c r="AK36" s="85">
+        <f>IF(AJ36="","",AJ36/(1-G36))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A37" s="39" t="inlineStr">
@@ -4839,6 +4990,11 @@
         <f>(N37+P37+U37+W37+X37+K37)/(1-(L37+$F$4+(1-G37)*$F$3+$F$8+Y37+AA37))</f>
         <v/>
       </c>
+      <c r="AJ37" s="84" t="n"/>
+      <c r="AK37" s="85">
+        <f>IF(AJ37="","",AJ37/(1-G37))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A38" s="39" t="inlineStr">
@@ -4962,6 +5118,11 @@
         <f>(N38+P38+U38+W38+X38+K38)/(1-(L38+$F$4+(1-G38)*$F$3+$F$8+Y38+AA38))</f>
         <v/>
       </c>
+      <c r="AJ38" s="84" t="n"/>
+      <c r="AK38" s="85">
+        <f>IF(AJ38="","",AJ38/(1-G38))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A39" s="39" t="inlineStr">
@@ -5083,6 +5244,11 @@
       </c>
       <c r="AI39" s="28">
         <f>(N39+P39+U39+W39+X39+K39)/(1-(L39+$F$4+(1-G39)*$F$3+$F$8+Y39+AA39))</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="84" t="n"/>
+      <c r="AK39" s="85">
+        <f>IF(AJ39="","",AJ39/(1-G39))</f>
         <v/>
       </c>
     </row>
@@ -5245,6 +5411,11 @@
         <f>(N41+P41+U41+W41+X41+K41)/(1-(L41+$F$4+(1-G41)*$F$3+$F$8+Y41+AA41))</f>
         <v/>
       </c>
+      <c r="AJ41" s="84" t="n"/>
+      <c r="AK41" s="85">
+        <f>IF(AJ41="","",AJ41/(1-G41))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A42" s="39" t="inlineStr">
@@ -5368,6 +5539,11 @@
         <f>(N42+P42+U42+W42+X42+K42)/(1-(L42+$F$4+(1-G42)*$F$3+$F$8+Y42+AA42))</f>
         <v/>
       </c>
+      <c r="AJ42" s="84" t="n"/>
+      <c r="AK42" s="85">
+        <f>IF(AJ42="","",AJ42/(1-G42))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A43" s="39" t="inlineStr">
@@ -5491,6 +5667,11 @@
         <f>(N43+P43+U43+W43+X43+K43)/(1-(L43+$F$4+(1-G43)*$F$3+$F$8+Y43+AA43))</f>
         <v/>
       </c>
+      <c r="AJ43" s="84" t="n"/>
+      <c r="AK43" s="85">
+        <f>IF(AJ43="","",AJ43/(1-G43))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A44" s="39" t="inlineStr">
@@ -5612,6 +5793,11 @@
       </c>
       <c r="AI44" s="28">
         <f>(N44+P44+U44+W44+X44+K44)/(1-(L44+$F$4+(1-G44)*$F$3+$F$8+Y44+AA44))</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="84" t="n"/>
+      <c r="AK44" s="85">
+        <f>IF(AJ44="","",AJ44/(1-G44))</f>
         <v/>
       </c>
     </row>
@@ -5774,6 +5960,11 @@
         <f>(N46+P46+U46+W46+X46+K46)/(1-(L46+$F$4+(1-G46)*$F$3+$F$8+Y46+AA46))</f>
         <v/>
       </c>
+      <c r="AJ46" s="84" t="n"/>
+      <c r="AK46" s="85">
+        <f>IF(AJ46="","",AJ46/(1-G46))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A47" s="39" t="inlineStr">
@@ -5897,6 +6088,11 @@
         <f>(N47+P47+U47+W47+X47+K47)/(1-(L47+$F$4+(1-G47)*$F$3+$F$8+Y47+AA47))</f>
         <v/>
       </c>
+      <c r="AJ47" s="84" t="n"/>
+      <c r="AK47" s="85">
+        <f>IF(AJ47="","",AJ47/(1-G47))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A48" s="39" t="inlineStr">
@@ -6020,6 +6216,11 @@
         <f>(N48+P48+U48+W48+X48+K48)/(1-(L48+$F$4+(1-G48)*$F$3+$F$8+Y48+AA48))</f>
         <v/>
       </c>
+      <c r="AJ48" s="84" t="n"/>
+      <c r="AK48" s="85">
+        <f>IF(AJ48="","",AJ48/(1-G48))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A49" s="39" t="inlineStr">
@@ -6143,6 +6344,11 @@
         <f>(N49+P49+U49+W49+X49+K49)/(1-(L49+$F$4+(1-G49)*$F$3+$F$8+Y49+AA49))</f>
         <v/>
       </c>
+      <c r="AJ49" s="84" t="n"/>
+      <c r="AK49" s="85">
+        <f>IF(AJ49="","",AJ49/(1-G49))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A50" s="39" t="inlineStr">
@@ -6266,6 +6472,11 @@
         <f>(N50+P50+U50+W50+X50+K50)/(1-(L50+$F$4+(1-G50)*$F$3+$F$8+Y50+AA50))</f>
         <v/>
       </c>
+      <c r="AJ50" s="84" t="n"/>
+      <c r="AK50" s="85">
+        <f>IF(AJ50="","",AJ50/(1-G50))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A51" s="39" t="inlineStr">
@@ -6387,6 +6598,11 @@
       </c>
       <c r="AI51" s="28">
         <f>(N51+P51+U51+W51+X51+K51)/(1-(L51+$F$4+(1-G51)*$F$3+$F$8+Y51+AA51))</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="84" t="n"/>
+      <c r="AK51" s="85">
+        <f>IF(AJ51="","",AJ51/(1-G51))</f>
         <v/>
       </c>
     </row>
@@ -6549,6 +6765,11 @@
         <f>(N53+P53+U53+W53+X53+K53)/(1-(L53+$F$4+(1-G53)*$F$3+$F$8+Y53+AA53))</f>
         <v/>
       </c>
+      <c r="AJ53" s="84" t="n"/>
+      <c r="AK53" s="85">
+        <f>IF(AJ53="","",AJ53/(1-G53))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A54" s="39" t="inlineStr">
@@ -6672,6 +6893,11 @@
         <f>(N54+P54+U54+W54+X54+K54)/(1-(L54+$F$4+(1-G54)*$F$3+$F$8+Y54+AA54))</f>
         <v/>
       </c>
+      <c r="AJ54" s="84" t="n"/>
+      <c r="AK54" s="85">
+        <f>IF(AJ54="","",AJ54/(1-G54))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A55" s="39" t="inlineStr">
@@ -6795,6 +7021,11 @@
         <f>(N55+P55+U55+W55+X55+K55)/(1-(L55+$F$4+(1-G55)*$F$3+$F$8+Y55+AA55))</f>
         <v/>
       </c>
+      <c r="AJ55" s="84" t="n"/>
+      <c r="AK55" s="85">
+        <f>IF(AJ55="","",AJ55/(1-G55))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A56" s="39" t="inlineStr">
@@ -6918,6 +7149,11 @@
         <f>(N56+P56+U56+W56+X56+K56)/(1-(L56+$F$4+(1-G56)*$F$3+$F$8+Y56+AA56))</f>
         <v/>
       </c>
+      <c r="AJ56" s="84" t="n"/>
+      <c r="AK56" s="85">
+        <f>IF(AJ56="","",AJ56/(1-G56))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A57" s="39" t="inlineStr">
@@ -7041,6 +7277,11 @@
         <f>(N57+P57+U57+W57+X57+K57)/(1-(L57+$F$4+(1-G57)*$F$3+$F$8+Y57+AA57))</f>
         <v/>
       </c>
+      <c r="AJ57" s="84" t="n"/>
+      <c r="AK57" s="85">
+        <f>IF(AJ57="","",AJ57/(1-G57))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A58" s="39" t="inlineStr">
@@ -7164,6 +7405,11 @@
         <f>(N58+P58+U58+W58+X58+K58)/(1-(L58+$F$4+(1-G58)*$F$3+$F$8+Y58+AA58))</f>
         <v/>
       </c>
+      <c r="AJ58" s="84" t="n"/>
+      <c r="AK58" s="85">
+        <f>IF(AJ58="","",AJ58/(1-G58))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A59" s="39" t="inlineStr">
@@ -7287,6 +7533,11 @@
         <f>(N59+P59+U59+W59+X59+K59)/(1-(L59+$F$4+(1-G59)*$F$3+$F$8+Y59+AA59))</f>
         <v/>
       </c>
+      <c r="AJ59" s="84" t="n"/>
+      <c r="AK59" s="85">
+        <f>IF(AJ59="","",AJ59/(1-G59))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A60" s="39" t="inlineStr">
@@ -7410,6 +7661,11 @@
         <f>(N60+P60+U60+W60+X60+K60)/(1-(L60+$F$4+(1-G60)*$F$3+$F$8+Y60+AA60))</f>
         <v/>
       </c>
+      <c r="AJ60" s="84" t="n"/>
+      <c r="AK60" s="85">
+        <f>IF(AJ60="","",AJ60/(1-G60))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="59" thickBot="1">
       <c r="A61" s="39" t="inlineStr">
@@ -7531,6 +7787,11 @@
       </c>
       <c r="AI61" s="28">
         <f>(N61+P61+U61+W61+X61+K61)/(1-(L61+$F$4+(1-G61)*$F$3+$F$8+Y61+AA61))</f>
+        <v/>
+      </c>
+      <c r="AJ61" s="84" t="n"/>
+      <c r="AK61" s="85">
+        <f>IF(AJ61="","",AJ61/(1-G61))</f>
         <v/>
       </c>
     </row>
